--- a/dist/xlsx/counties.xlsx
+++ b/dist/xlsx/counties.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D483"/>
+  <dimension ref="A1:D485"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1000001</v>
+        <v>10000001</v>
       </c>
       <c r="B2" t="str">
         <v>اراک</v>
@@ -429,7 +429,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>1000002</v>
+        <v>10000002</v>
       </c>
       <c r="B3" t="str">
         <v>آشتیان</v>
@@ -443,7 +443,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>1000003</v>
+        <v>10000003</v>
       </c>
       <c r="B4" t="str">
         <v>تفرش</v>
@@ -457,7 +457,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1000004</v>
+        <v>10000004</v>
       </c>
       <c r="B5" t="str">
         <v>خمین</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>1000005</v>
+        <v>10000005</v>
       </c>
       <c r="B6" t="str">
         <v>دلیجان</v>
@@ -485,7 +485,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1000006</v>
+        <v>10000006</v>
       </c>
       <c r="B7" t="str">
         <v>ساوه</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>1000007</v>
+        <v>10000007</v>
       </c>
       <c r="B8" t="str">
         <v>شازند</v>
@@ -513,7 +513,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>1000009</v>
+        <v>10000009</v>
       </c>
       <c r="B9" t="str">
         <v>محلات</v>
@@ -527,69 +527,69 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>1010001</v>
+        <v>10000010</v>
       </c>
       <c r="B10" t="str">
-        <v>آستارا</v>
+        <v>زرندیه</v>
       </c>
       <c r="C10" t="str">
-        <v>آستارا</v>
+        <v>زرندیه</v>
       </c>
       <c r="D10">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>1010002</v>
+        <v>10000011</v>
       </c>
       <c r="B11" t="str">
-        <v>آستانه اشرفیه</v>
+        <v>کمیجان</v>
       </c>
       <c r="C11" t="str">
-        <v>آستانه-اشرفیه</v>
+        <v>کمیجان</v>
       </c>
       <c r="D11">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>1010003</v>
+        <v>10000012</v>
       </c>
       <c r="B12" t="str">
-        <v>بندرانزلی</v>
+        <v>خنداب</v>
       </c>
       <c r="C12" t="str">
-        <v>بندرانزلی</v>
+        <v>خنداب</v>
       </c>
       <c r="D12">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>1010004</v>
+        <v>10000013</v>
       </c>
       <c r="B13" t="str">
-        <v>طوالش</v>
+        <v>فراهان</v>
       </c>
       <c r="C13" t="str">
-        <v>طوالش</v>
+        <v>فراهان</v>
       </c>
       <c r="D13">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>1010005</v>
+        <v>10100001</v>
       </c>
       <c r="B14" t="str">
-        <v>رشت</v>
+        <v>آستارا</v>
       </c>
       <c r="C14" t="str">
-        <v>رشت</v>
+        <v>آستارا</v>
       </c>
       <c r="D14">
         <v>101</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>1010006</v>
+        <v>10100002</v>
       </c>
       <c r="B15" t="str">
-        <v>رودبار</v>
+        <v>آستانه اشرفیه</v>
       </c>
       <c r="C15" t="str">
-        <v>رودبار</v>
+        <v>آستانه-اشرفیه</v>
       </c>
       <c r="D15">
         <v>101</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>1010007</v>
+        <v>10100003</v>
       </c>
       <c r="B16" t="str">
-        <v>رودسر</v>
+        <v>بندرانزلی</v>
       </c>
       <c r="C16" t="str">
-        <v>رودسر</v>
+        <v>بندرانزلی</v>
       </c>
       <c r="D16">
         <v>101</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>1010008</v>
+        <v>10100004</v>
       </c>
       <c r="B17" t="str">
-        <v>صومعه سرا</v>
+        <v>طوالش</v>
       </c>
       <c r="C17" t="str">
-        <v>صومعه-سرا</v>
+        <v>طوالش</v>
       </c>
       <c r="D17">
         <v>101</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>1010009</v>
+        <v>10100005</v>
       </c>
       <c r="B18" t="str">
-        <v>فومن</v>
+        <v>رشت</v>
       </c>
       <c r="C18" t="str">
-        <v>فومن</v>
+        <v>رشت</v>
       </c>
       <c r="D18">
         <v>101</v>
@@ -653,6517 +653,6545 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>1020001</v>
+        <v>10100006</v>
       </c>
       <c r="B19" t="str">
-        <v>آمل</v>
+        <v>رودبار</v>
       </c>
       <c r="C19" t="str">
-        <v>آمل</v>
+        <v>رودبار</v>
       </c>
       <c r="D19">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>1020002</v>
+        <v>10100007</v>
       </c>
       <c r="B20" t="str">
-        <v>بابل</v>
+        <v>رودسر</v>
       </c>
       <c r="C20" t="str">
-        <v>بابل</v>
+        <v>رودسر</v>
       </c>
       <c r="D20">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>1020004</v>
+        <v>10100008</v>
       </c>
       <c r="B21" t="str">
-        <v>بهشهر</v>
+        <v>صومعه سرا</v>
       </c>
       <c r="C21" t="str">
-        <v>بهشهر</v>
+        <v>صومعه-سرا</v>
       </c>
       <c r="D21">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>1020005</v>
+        <v>10100009</v>
       </c>
       <c r="B22" t="str">
-        <v>تنکابن</v>
+        <v>فومن</v>
       </c>
       <c r="C22" t="str">
-        <v>تنکابن</v>
+        <v>فومن</v>
       </c>
       <c r="D22">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>1020006</v>
+        <v>10100010</v>
       </c>
       <c r="B23" t="str">
-        <v>رامسر</v>
+        <v>لنگرود</v>
       </c>
       <c r="C23" t="str">
-        <v>رامسر</v>
+        <v>لنگرود</v>
       </c>
       <c r="D23">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>1020007</v>
+        <v>10100011</v>
       </c>
       <c r="B24" t="str">
-        <v>ساری</v>
+        <v>لاهیجان</v>
       </c>
       <c r="C24" t="str">
-        <v>ساری</v>
+        <v>لاهیجان</v>
       </c>
       <c r="D24">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>1020008</v>
+        <v>10100012</v>
       </c>
       <c r="B25" t="str">
-        <v>سوادکوه</v>
+        <v>شفت</v>
       </c>
       <c r="C25" t="str">
-        <v>سوادکوه</v>
+        <v>شفت</v>
       </c>
       <c r="D25">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>1030002</v>
+        <v>10100013</v>
       </c>
       <c r="B26" t="str">
-        <v>اهر</v>
+        <v>املش</v>
       </c>
       <c r="C26" t="str">
-        <v>اهر</v>
+        <v>املش</v>
       </c>
       <c r="D26">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>1030003</v>
+        <v>10100014</v>
       </c>
       <c r="B27" t="str">
-        <v>تبریز</v>
+        <v>رضوانشهر</v>
       </c>
       <c r="C27" t="str">
-        <v>تبریز</v>
+        <v>رضوانشهر</v>
       </c>
       <c r="D27">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>1030005</v>
+        <v>10100015</v>
       </c>
       <c r="B28" t="str">
-        <v>سراب</v>
+        <v>سیاهکل</v>
       </c>
       <c r="C28" t="str">
-        <v>سراب</v>
+        <v>سیاهکل</v>
       </c>
       <c r="D28">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>1030006</v>
+        <v>10100016</v>
       </c>
       <c r="B29" t="str">
-        <v>مراغه</v>
+        <v>ماسال</v>
       </c>
       <c r="C29" t="str">
-        <v>مراغه</v>
+        <v>ماسال</v>
       </c>
       <c r="D29">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>1030007</v>
+        <v>10100017</v>
       </c>
       <c r="B30" t="str">
-        <v>مرند</v>
+        <v>خمام</v>
       </c>
       <c r="C30" t="str">
-        <v>مرند</v>
+        <v>خمام</v>
       </c>
       <c r="D30">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>1040001</v>
+        <v>10200001</v>
       </c>
       <c r="B31" t="str">
-        <v>ارومیه</v>
+        <v>آمل</v>
       </c>
       <c r="C31" t="str">
-        <v>ارومیه</v>
+        <v>آمل</v>
       </c>
       <c r="D31">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>1040002</v>
+        <v>10200002</v>
       </c>
       <c r="B32" t="str">
-        <v>پیرانشهر</v>
+        <v>بابل</v>
       </c>
       <c r="C32" t="str">
-        <v>پیرانشهر</v>
+        <v>بابل</v>
       </c>
       <c r="D32">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>1040003</v>
+        <v>10200004</v>
       </c>
       <c r="B33" t="str">
-        <v>خوی</v>
+        <v>بهشهر</v>
       </c>
       <c r="C33" t="str">
-        <v>خوی</v>
+        <v>بهشهر</v>
       </c>
       <c r="D33">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>1040004</v>
+        <v>10200005</v>
       </c>
       <c r="B34" t="str">
-        <v>سردشت</v>
+        <v>تنکابن</v>
       </c>
       <c r="C34" t="str">
-        <v>سردشت</v>
+        <v>تنکابن</v>
       </c>
       <c r="D34">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>1040005</v>
+        <v>10200006</v>
       </c>
       <c r="B35" t="str">
-        <v>سلماس</v>
+        <v>رامسر</v>
       </c>
       <c r="C35" t="str">
-        <v>سلماس</v>
+        <v>رامسر</v>
       </c>
       <c r="D35">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>1040006</v>
+        <v>10200007</v>
       </c>
       <c r="B36" t="str">
-        <v>ماکو</v>
+        <v>ساری</v>
       </c>
       <c r="C36" t="str">
-        <v>ماکو</v>
+        <v>ساری</v>
       </c>
       <c r="D36">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>1040007</v>
+        <v>10200008</v>
       </c>
       <c r="B37" t="str">
-        <v>مهاباد</v>
+        <v>سوادکوه</v>
       </c>
       <c r="C37" t="str">
-        <v>مهاباد</v>
+        <v>سوادکوه</v>
       </c>
       <c r="D37">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>1040008</v>
+        <v>10200010</v>
       </c>
       <c r="B38" t="str">
-        <v>میاندوآب</v>
+        <v>قایم شهر</v>
       </c>
       <c r="C38" t="str">
-        <v>میاندوآب</v>
+        <v>قایم-شهر</v>
       </c>
       <c r="D38">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>1040009</v>
+        <v>10200014</v>
       </c>
       <c r="B39" t="str">
-        <v>نقده</v>
+        <v>نور</v>
       </c>
       <c r="C39" t="str">
-        <v>نقده</v>
+        <v>نور</v>
       </c>
       <c r="D39">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>1050001</v>
+        <v>10200015</v>
       </c>
       <c r="B40" t="str">
-        <v>اسلام آبادغرب</v>
+        <v>نوشهر</v>
       </c>
       <c r="C40" t="str">
-        <v>اسلام-آبادغرب</v>
+        <v>نوشهر</v>
       </c>
       <c r="D40">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>1050002</v>
+        <v>10200016</v>
       </c>
       <c r="B41" t="str">
-        <v>کرمانشاه</v>
+        <v>بابلسر</v>
       </c>
       <c r="C41" t="str">
-        <v>کرمانشاه</v>
+        <v>بابلسر</v>
       </c>
       <c r="D41">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>1050003</v>
+        <v>10200018</v>
       </c>
       <c r="B42" t="str">
-        <v>پاوه</v>
+        <v>محمودآباد</v>
       </c>
       <c r="C42" t="str">
-        <v>پاوه</v>
+        <v>محمودآباد</v>
       </c>
       <c r="D42">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>1050004</v>
+        <v>10200019</v>
       </c>
       <c r="B43" t="str">
-        <v>سرپل ذهاب</v>
+        <v>نکا</v>
       </c>
       <c r="C43" t="str">
-        <v>سرپل-ذهاب</v>
+        <v>نکا</v>
       </c>
       <c r="D43">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>1050005</v>
+        <v>10200020</v>
       </c>
       <c r="B44" t="str">
-        <v>سنقر</v>
+        <v>چالوس</v>
       </c>
       <c r="C44" t="str">
-        <v>سنقر</v>
+        <v>چالوس</v>
       </c>
       <c r="D44">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>1050006</v>
+        <v>10200021</v>
       </c>
       <c r="B45" t="str">
-        <v>قصرشیرین</v>
+        <v>جویبار</v>
       </c>
       <c r="C45" t="str">
-        <v>قصرشیرین</v>
+        <v>جویبار</v>
       </c>
       <c r="D45">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>1050007</v>
+        <v>10200022</v>
       </c>
       <c r="B46" t="str">
-        <v>کنگاور</v>
+        <v>گلوگاه</v>
       </c>
       <c r="C46" t="str">
-        <v>کنگاور</v>
+        <v>گلوگاه</v>
       </c>
       <c r="D46">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>1050008</v>
+        <v>10200023</v>
       </c>
       <c r="B47" t="str">
-        <v>گیلانغرب</v>
+        <v>فریدونکنار</v>
       </c>
       <c r="C47" t="str">
-        <v>گیلانغرب</v>
+        <v>فریدونکنار</v>
       </c>
       <c r="D47">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>1050009</v>
+        <v>10200024</v>
       </c>
       <c r="B48" t="str">
-        <v>جوانرود</v>
+        <v>عباس آباد</v>
       </c>
       <c r="C48" t="str">
-        <v>جوانرود</v>
+        <v>عباس-آباد</v>
       </c>
       <c r="D48">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>1060001</v>
+        <v>10200025</v>
       </c>
       <c r="B49" t="str">
-        <v>آبادان</v>
+        <v>میاندورود</v>
       </c>
       <c r="C49" t="str">
-        <v>آبادان</v>
+        <v>میاندورود</v>
       </c>
       <c r="D49">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>1060002</v>
+        <v>10200026</v>
       </c>
       <c r="B50" t="str">
-        <v>اندیمشک</v>
+        <v>سیمرغ</v>
       </c>
       <c r="C50" t="str">
-        <v>اندیمشک</v>
+        <v>سیمرغ</v>
       </c>
       <c r="D50">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>1060003</v>
+        <v>10200027</v>
       </c>
       <c r="B51" t="str">
-        <v>اهواز</v>
+        <v>سوادکوه شمالی</v>
       </c>
       <c r="C51" t="str">
-        <v>اهواز</v>
+        <v>سوادکوه-شمالی</v>
       </c>
       <c r="D51">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>1060004</v>
+        <v>10200028</v>
       </c>
       <c r="B52" t="str">
-        <v>ایذه</v>
+        <v>کلاردشت</v>
       </c>
       <c r="C52" t="str">
-        <v>ایذه</v>
+        <v>کلاردشت</v>
       </c>
       <c r="D52">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>1060005</v>
+        <v>10300002</v>
       </c>
       <c r="B53" t="str">
-        <v>بندرماهشهر</v>
+        <v>اهر</v>
       </c>
       <c r="C53" t="str">
-        <v>بندرماهشهر</v>
+        <v>اهر</v>
       </c>
       <c r="D53">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>1060006</v>
+        <v>10300003</v>
       </c>
       <c r="B54" t="str">
-        <v>بهبهان</v>
+        <v>تبریز</v>
       </c>
       <c r="C54" t="str">
-        <v>بهبهان</v>
+        <v>تبریز</v>
       </c>
       <c r="D54">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>1060007</v>
+        <v>10300005</v>
       </c>
       <c r="B55" t="str">
-        <v>خرمشهر</v>
+        <v>سراب</v>
       </c>
       <c r="C55" t="str">
-        <v>خرمشهر</v>
+        <v>سراب</v>
       </c>
       <c r="D55">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>1060008</v>
+        <v>10300006</v>
       </c>
       <c r="B56" t="str">
-        <v>دزفول</v>
+        <v>مراغه</v>
       </c>
       <c r="C56" t="str">
-        <v>دزفول</v>
+        <v>مراغه</v>
       </c>
       <c r="D56">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>1060009</v>
+        <v>10300007</v>
       </c>
       <c r="B57" t="str">
-        <v>دشت آزادگان</v>
+        <v>مرند</v>
       </c>
       <c r="C57" t="str">
-        <v>دشت-آزادگان</v>
+        <v>مرند</v>
       </c>
       <c r="D57">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>1070001</v>
+        <v>10300010</v>
       </c>
       <c r="B58" t="str">
-        <v>آباده</v>
+        <v>میانه</v>
       </c>
       <c r="C58" t="str">
-        <v>آباده</v>
+        <v>میانه</v>
       </c>
       <c r="D58">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>1070002</v>
+        <v>10300011</v>
       </c>
       <c r="B59" t="str">
-        <v>استهبان</v>
+        <v>هشترود</v>
       </c>
       <c r="C59" t="str">
-        <v>استهبان</v>
+        <v>هشترود</v>
       </c>
       <c r="D59">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>1070003</v>
+        <v>10300012</v>
       </c>
       <c r="B60" t="str">
-        <v>اقلید</v>
+        <v>بناب</v>
       </c>
       <c r="C60" t="str">
-        <v>اقلید</v>
+        <v>بناب</v>
       </c>
       <c r="D60">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>1070004</v>
+        <v>10300013</v>
       </c>
       <c r="B61" t="str">
-        <v>جهرم</v>
+        <v>بستان آباد</v>
       </c>
       <c r="C61" t="str">
-        <v>جهرم</v>
+        <v>بستان-آباد</v>
       </c>
       <c r="D61">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>1070005</v>
+        <v>10300014</v>
       </c>
       <c r="B62" t="str">
-        <v>داراب</v>
+        <v>شبستر</v>
       </c>
       <c r="C62" t="str">
-        <v>داراب</v>
+        <v>شبستر</v>
       </c>
       <c r="D62">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>1070006</v>
+        <v>10300015</v>
       </c>
       <c r="B63" t="str">
-        <v>سپیدان</v>
+        <v>کلیبر</v>
       </c>
       <c r="C63" t="str">
-        <v>سپیدان</v>
+        <v>کلیبر</v>
       </c>
       <c r="D63">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>1070007</v>
+        <v>10300016</v>
       </c>
       <c r="B64" t="str">
-        <v>شیراز</v>
+        <v>هریس</v>
       </c>
       <c r="C64" t="str">
-        <v>شیراز</v>
+        <v>هریس</v>
       </c>
       <c r="D64">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>1070008</v>
+        <v>10300019</v>
       </c>
       <c r="B65" t="str">
-        <v>فسا</v>
+        <v>جلفا</v>
       </c>
       <c r="C65" t="str">
-        <v>فسا</v>
+        <v>جلفا</v>
       </c>
       <c r="D65">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>1070009</v>
+        <v>10300020</v>
       </c>
       <c r="B66" t="str">
-        <v>فیروزآباد</v>
+        <v>ملکان</v>
       </c>
       <c r="C66" t="str">
-        <v>فیروزآباد</v>
+        <v>ملکان</v>
       </c>
       <c r="D66">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>1080001</v>
+        <v>10300021</v>
       </c>
       <c r="B67" t="str">
-        <v>بافت</v>
+        <v>آذرشهر</v>
       </c>
       <c r="C67" t="str">
-        <v>بافت</v>
+        <v>آذرشهر</v>
       </c>
       <c r="D67">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>1080002</v>
+        <v>10300022</v>
       </c>
       <c r="B68" t="str">
-        <v>بم</v>
+        <v>اسکو</v>
       </c>
       <c r="C68" t="str">
-        <v>بم</v>
+        <v>اسکو</v>
       </c>
       <c r="D68">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>1080003</v>
+        <v>10300023</v>
       </c>
       <c r="B69" t="str">
-        <v>جیرفت</v>
+        <v>چاراویماق</v>
       </c>
       <c r="C69" t="str">
-        <v>جیرفت</v>
+        <v>چاراویماق</v>
       </c>
       <c r="D69">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>1080004</v>
+        <v>10300024</v>
       </c>
       <c r="B70" t="str">
-        <v>رفسنجان</v>
+        <v>ورزقان</v>
       </c>
       <c r="C70" t="str">
-        <v>رفسنجان</v>
+        <v>ورزقان</v>
       </c>
       <c r="D70">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>1080005</v>
+        <v>10300025</v>
       </c>
       <c r="B71" t="str">
-        <v>زرند</v>
+        <v>عجب شیر</v>
       </c>
       <c r="C71" t="str">
-        <v>زرند</v>
+        <v>عجب-شیر</v>
       </c>
       <c r="D71">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>1080006</v>
+        <v>10300026</v>
       </c>
       <c r="B72" t="str">
-        <v>سیرجان</v>
+        <v>خدا آفرین</v>
       </c>
       <c r="C72" t="str">
-        <v>سیرجان</v>
+        <v>خدا-آفرین</v>
       </c>
       <c r="D72">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>1080007</v>
+        <v>10300027</v>
       </c>
       <c r="B73" t="str">
-        <v>شهربابک</v>
+        <v>هوراند</v>
       </c>
       <c r="C73" t="str">
-        <v>شهربابک</v>
+        <v>هوراند</v>
       </c>
       <c r="D73">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>1080008</v>
+        <v>10300028</v>
       </c>
       <c r="B74" t="str">
-        <v>کرمان</v>
+        <v>لیلان</v>
       </c>
       <c r="C74" t="str">
-        <v>کرمان</v>
+        <v>لیلان</v>
       </c>
       <c r="D74">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>1080009</v>
+        <v>10300029</v>
       </c>
       <c r="B75" t="str">
-        <v>کهنوج</v>
+        <v>ترکمانچای</v>
       </c>
       <c r="C75" t="str">
-        <v>کهنوج</v>
+        <v>ترکمانچای</v>
       </c>
       <c r="D75">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>1090004</v>
+        <v>10400001</v>
       </c>
       <c r="B76" t="str">
-        <v>تایباد</v>
+        <v>ارومیه</v>
       </c>
       <c r="C76" t="str">
-        <v>تایباد</v>
+        <v>ارومیه</v>
       </c>
       <c r="D76">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>1090005</v>
+        <v>10400002</v>
       </c>
       <c r="B77" t="str">
-        <v>تربت حیدریه</v>
+        <v>پیرانشهر</v>
       </c>
       <c r="C77" t="str">
-        <v>تربت-حیدریه</v>
+        <v>پیرانشهر</v>
       </c>
       <c r="D77">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>1090006</v>
+        <v>10400003</v>
       </c>
       <c r="B78" t="str">
-        <v>تربت جام</v>
+        <v>خوی</v>
       </c>
       <c r="C78" t="str">
-        <v>تربت-جام</v>
+        <v>خوی</v>
       </c>
       <c r="D78">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>1090007</v>
+        <v>10400004</v>
       </c>
       <c r="B79" t="str">
-        <v>درگز</v>
+        <v>سردشت</v>
       </c>
       <c r="C79" t="str">
-        <v>درگز</v>
+        <v>سردشت</v>
       </c>
       <c r="D79">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>1090008</v>
+        <v>10400005</v>
       </c>
       <c r="B80" t="str">
-        <v>سبزوار</v>
+        <v>سلماس</v>
       </c>
       <c r="C80" t="str">
-        <v>سبزوار</v>
+        <v>سلماس</v>
       </c>
       <c r="D80">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>1100001</v>
+        <v>10400006</v>
       </c>
       <c r="B81" t="str">
-        <v>اردستان</v>
+        <v>ماکو</v>
       </c>
       <c r="C81" t="str">
-        <v>اردستان</v>
+        <v>ماکو</v>
       </c>
       <c r="D81">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>1100002</v>
+        <v>10400007</v>
       </c>
       <c r="B82" t="str">
-        <v>اصفهان</v>
+        <v>مهاباد</v>
       </c>
       <c r="C82" t="str">
-        <v>اصفهان</v>
+        <v>مهاباد</v>
       </c>
       <c r="D82">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>1100003</v>
+        <v>10400008</v>
       </c>
       <c r="B83" t="str">
-        <v>خمینی شهر</v>
+        <v>میاندوآب</v>
       </c>
       <c r="C83" t="str">
-        <v>خمینی-شهر</v>
+        <v>میاندوآب</v>
       </c>
       <c r="D83">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>1100004</v>
+        <v>10400009</v>
       </c>
       <c r="B84" t="str">
-        <v>خوانسار</v>
+        <v>نقده</v>
       </c>
       <c r="C84" t="str">
-        <v>خوانسار</v>
+        <v>نقده</v>
       </c>
       <c r="D84">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>1100005</v>
+        <v>10400010</v>
       </c>
       <c r="B85" t="str">
-        <v>سمیرم</v>
+        <v>بوکان</v>
       </c>
       <c r="C85" t="str">
-        <v>سمیرم</v>
+        <v>بوکان</v>
       </c>
       <c r="D85">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>1100006</v>
+        <v>10400011</v>
       </c>
       <c r="B86" t="str">
-        <v>فریدن</v>
+        <v>شاهین دژ</v>
       </c>
       <c r="C86" t="str">
-        <v>فریدن</v>
+        <v>شاهین-دژ</v>
       </c>
       <c r="D86">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>1100007</v>
+        <v>10400012</v>
       </c>
       <c r="B87" t="str">
-        <v>فریدونشهر</v>
+        <v>تکاب</v>
       </c>
       <c r="C87" t="str">
-        <v>فریدونشهر</v>
+        <v>تکاب</v>
       </c>
       <c r="D87">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>1100008</v>
+        <v>10400013</v>
       </c>
       <c r="B88" t="str">
-        <v>فلاورجان</v>
+        <v>اشنویه</v>
       </c>
       <c r="C88" t="str">
-        <v>فلاورجان</v>
+        <v>اشنویه</v>
       </c>
       <c r="D88">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>1100009</v>
+        <v>10400014</v>
       </c>
       <c r="B89" t="str">
-        <v>شهرضا</v>
+        <v>چالدران</v>
       </c>
       <c r="C89" t="str">
-        <v>شهرضا</v>
+        <v>چالدران</v>
       </c>
       <c r="D89">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>1110001</v>
+        <v>10400015</v>
       </c>
       <c r="B90" t="str">
-        <v>ایرانشهر</v>
+        <v>پلدشت</v>
       </c>
       <c r="C90" t="str">
-        <v>ایرانشهر</v>
+        <v>پلدشت</v>
       </c>
       <c r="D90">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>1110002</v>
+        <v>10400016</v>
       </c>
       <c r="B91" t="str">
-        <v>چاه بهار</v>
+        <v>چایپاره</v>
       </c>
       <c r="C91" t="str">
-        <v>چاه-بهار</v>
+        <v>چایپاره</v>
       </c>
       <c r="D91">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>1110003</v>
+        <v>10400017</v>
       </c>
       <c r="B92" t="str">
-        <v>خاش</v>
+        <v>شوط</v>
       </c>
       <c r="C92" t="str">
-        <v>خاش</v>
+        <v>شوط</v>
       </c>
       <c r="D92">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>1110004</v>
+        <v>10400018</v>
       </c>
       <c r="B93" t="str">
-        <v>زابل</v>
+        <v>چهاربرج</v>
       </c>
       <c r="C93" t="str">
-        <v>زابل</v>
+        <v>چهاربرج</v>
       </c>
       <c r="D93">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>1110005</v>
+        <v>10400019</v>
       </c>
       <c r="B94" t="str">
-        <v>زاهدان</v>
+        <v>باروق</v>
       </c>
       <c r="C94" t="str">
-        <v>زاهدان</v>
+        <v>باروق</v>
       </c>
       <c r="D94">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>1110006</v>
+        <v>10400020</v>
       </c>
       <c r="B95" t="str">
-        <v>سراوان</v>
+        <v>میرآباد</v>
       </c>
       <c r="C95" t="str">
-        <v>سراوان</v>
+        <v>میرآباد</v>
       </c>
       <c r="D95">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>1110007</v>
+        <v>10500001</v>
       </c>
       <c r="B96" t="str">
-        <v>نیک شهر</v>
+        <v>اسلام آبادغرب</v>
       </c>
       <c r="C96" t="str">
-        <v>نیک-شهر</v>
+        <v>اسلام-آبادغرب</v>
       </c>
       <c r="D96">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>1110008</v>
+        <v>10500002</v>
       </c>
       <c r="B97" t="str">
-        <v>راسک</v>
+        <v>کرمانشاه</v>
       </c>
       <c r="C97" t="str">
-        <v>راسک</v>
+        <v>کرمانشاه</v>
       </c>
       <c r="D97">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>1110009</v>
+        <v>10500003</v>
       </c>
       <c r="B98" t="str">
-        <v>کنارک</v>
+        <v>پاوه</v>
       </c>
       <c r="C98" t="str">
-        <v>کنارک</v>
+        <v>پاوه</v>
       </c>
       <c r="D98">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>1120001</v>
+        <v>10500004</v>
       </c>
       <c r="B99" t="str">
-        <v>بانه</v>
+        <v>سرپل ذهاب</v>
       </c>
       <c r="C99" t="str">
-        <v>بانه</v>
+        <v>سرپل-ذهاب</v>
       </c>
       <c r="D99">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>1120002</v>
+        <v>10500005</v>
       </c>
       <c r="B100" t="str">
-        <v>بیجار</v>
+        <v>سنقر</v>
       </c>
       <c r="C100" t="str">
-        <v>بیجار</v>
+        <v>سنقر</v>
       </c>
       <c r="D100">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>1120003</v>
+        <v>10500006</v>
       </c>
       <c r="B101" t="str">
-        <v>سقز</v>
+        <v>قصرشیرین</v>
       </c>
       <c r="C101" t="str">
-        <v>سقز</v>
+        <v>قصرشیرین</v>
       </c>
       <c r="D101">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>1120004</v>
+        <v>10500007</v>
       </c>
       <c r="B102" t="str">
-        <v>سنندج</v>
+        <v>کنگاور</v>
       </c>
       <c r="C102" t="str">
-        <v>سنندج</v>
+        <v>کنگاور</v>
       </c>
       <c r="D102">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>1120005</v>
+        <v>10500008</v>
       </c>
       <c r="B103" t="str">
-        <v>قروه</v>
+        <v>گیلانغرب</v>
       </c>
       <c r="C103" t="str">
-        <v>قروه</v>
+        <v>گیلانغرب</v>
       </c>
       <c r="D103">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>1120006</v>
+        <v>10500009</v>
       </c>
       <c r="B104" t="str">
-        <v>مریوان</v>
+        <v>جوانرود</v>
       </c>
       <c r="C104" t="str">
-        <v>مریوان</v>
+        <v>جوانرود</v>
       </c>
       <c r="D104">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>1120007</v>
+        <v>10500010</v>
       </c>
       <c r="B105" t="str">
-        <v>دیواندره</v>
+        <v>صحنه</v>
       </c>
       <c r="C105" t="str">
-        <v>دیواندره</v>
+        <v>صحنه</v>
       </c>
       <c r="D105">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>1120008</v>
+        <v>10500011</v>
       </c>
       <c r="B106" t="str">
-        <v>کامیاران</v>
+        <v>هرسین</v>
       </c>
       <c r="C106" t="str">
-        <v>کامیاران</v>
+        <v>هرسین</v>
       </c>
       <c r="D106">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>1120009</v>
+        <v>10500012</v>
       </c>
       <c r="B107" t="str">
-        <v>سروآباد</v>
+        <v>ثلاث باباجانی</v>
       </c>
       <c r="C107" t="str">
-        <v>سروآباد</v>
+        <v>ثلاث-باباجانی</v>
       </c>
       <c r="D107">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>1130001</v>
+        <v>10500013</v>
       </c>
       <c r="B108" t="str">
-        <v>تویسرکان</v>
+        <v>دالاهو</v>
       </c>
       <c r="C108" t="str">
-        <v>تویسرکان</v>
+        <v>دالاهو</v>
       </c>
       <c r="D108">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>1130002</v>
+        <v>10500014</v>
       </c>
       <c r="B109" t="str">
-        <v>ملایر</v>
+        <v>روانسر</v>
       </c>
       <c r="C109" t="str">
-        <v>ملایر</v>
+        <v>روانسر</v>
       </c>
       <c r="D109">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>1130003</v>
+        <v>10600001</v>
       </c>
       <c r="B110" t="str">
-        <v>نهاوند</v>
+        <v>آبادان</v>
       </c>
       <c r="C110" t="str">
-        <v>نهاوند</v>
+        <v>آبادان</v>
       </c>
       <c r="D110">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>1130004</v>
+        <v>10600002</v>
       </c>
       <c r="B111" t="str">
-        <v>همدان</v>
+        <v>اندیمشک</v>
       </c>
       <c r="C111" t="str">
-        <v>همدان</v>
+        <v>اندیمشک</v>
       </c>
       <c r="D111">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <v>1130005</v>
+        <v>10600003</v>
       </c>
       <c r="B112" t="str">
-        <v>کبودرآهنگ</v>
+        <v>اهواز</v>
       </c>
       <c r="C112" t="str">
-        <v>کبودرآهنگ</v>
+        <v>اهواز</v>
       </c>
       <c r="D112">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>1130006</v>
+        <v>10600004</v>
       </c>
       <c r="B113" t="str">
-        <v>اسدآباد</v>
+        <v>ایذه</v>
       </c>
       <c r="C113" t="str">
-        <v>اسدآباد</v>
+        <v>ایذه</v>
       </c>
       <c r="D113">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>1130007</v>
+        <v>10600005</v>
       </c>
       <c r="B114" t="str">
-        <v>بهار</v>
+        <v>بندر ماهشهر</v>
       </c>
       <c r="C114" t="str">
-        <v>بهار</v>
+        <v>بندر-ماهشهر</v>
       </c>
       <c r="D114">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>1130008</v>
+        <v>10600006</v>
       </c>
       <c r="B115" t="str">
-        <v>رزن</v>
+        <v>بهبهان</v>
       </c>
       <c r="C115" t="str">
-        <v>رزن</v>
+        <v>بهبهان</v>
       </c>
       <c r="D115">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>1130009</v>
+        <v>10600007</v>
       </c>
       <c r="B116" t="str">
-        <v>فامنین</v>
+        <v>خرمشهر</v>
       </c>
       <c r="C116" t="str">
-        <v>فامنین</v>
+        <v>خرمشهر</v>
       </c>
       <c r="D116">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>1140001</v>
+        <v>10600008</v>
       </c>
       <c r="B117" t="str">
-        <v>بروجن</v>
+        <v>دزفول</v>
       </c>
       <c r="C117" t="str">
-        <v>بروجن</v>
+        <v>دزفول</v>
       </c>
       <c r="D117">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>1140002</v>
+        <v>10600009</v>
       </c>
       <c r="B118" t="str">
-        <v>شهرکرد</v>
+        <v>دشت آزادگان</v>
       </c>
       <c r="C118" t="str">
-        <v>شهرکرد</v>
+        <v>دشت-آزادگان</v>
       </c>
       <c r="D118">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>1140003</v>
+        <v>10600010</v>
       </c>
       <c r="B119" t="str">
-        <v>فارسان</v>
+        <v>رامهرمز</v>
       </c>
       <c r="C119" t="str">
-        <v>فارسان</v>
+        <v>رامهرمز</v>
       </c>
       <c r="D119">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>1140004</v>
+        <v>10600011</v>
       </c>
       <c r="B120" t="str">
-        <v>لردگان</v>
+        <v>شادگان</v>
       </c>
       <c r="C120" t="str">
-        <v>لردگان</v>
+        <v>شادگان</v>
       </c>
       <c r="D120">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>1140005</v>
+        <v>10600012</v>
       </c>
       <c r="B121" t="str">
-        <v>اردل</v>
+        <v>شوشتر</v>
       </c>
       <c r="C121" t="str">
-        <v>اردل</v>
+        <v>شوشتر</v>
       </c>
       <c r="D121">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>1140006</v>
+        <v>10600013</v>
       </c>
       <c r="B122" t="str">
-        <v>کوهرنگ</v>
+        <v>مسجدسلیمان</v>
       </c>
       <c r="C122" t="str">
-        <v>کوهرنگ</v>
+        <v>مسجدسلیمان</v>
       </c>
       <c r="D122">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>1140007</v>
+        <v>10600014</v>
       </c>
       <c r="B123" t="str">
-        <v>کیار</v>
+        <v>شوش</v>
       </c>
       <c r="C123" t="str">
-        <v>کیار</v>
+        <v>شوش</v>
       </c>
       <c r="D123">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="124">
       <c r="A124">
-        <v>1140008</v>
+        <v>10600015</v>
       </c>
       <c r="B124" t="str">
-        <v>سامان</v>
+        <v>باغ ملک</v>
       </c>
       <c r="C124" t="str">
-        <v>سامان</v>
+        <v>باغ-ملک</v>
       </c>
       <c r="D124">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>1140009</v>
+        <v>10600016</v>
       </c>
       <c r="B125" t="str">
-        <v>بن</v>
+        <v>امیدیه</v>
       </c>
       <c r="C125" t="str">
-        <v>بن</v>
+        <v>امیدیه</v>
       </c>
       <c r="D125">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="126">
       <c r="A126">
-        <v>1150001</v>
+        <v>10600017</v>
       </c>
       <c r="B126" t="str">
-        <v>الیگودرز</v>
+        <v>لالی</v>
       </c>
       <c r="C126" t="str">
-        <v>الیگودرز</v>
+        <v>لالی</v>
       </c>
       <c r="D126">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="127">
       <c r="A127">
-        <v>1150002</v>
+        <v>10600018</v>
       </c>
       <c r="B127" t="str">
-        <v>بروجرد</v>
+        <v>هندیجان</v>
       </c>
       <c r="C127" t="str">
-        <v>بروجرد</v>
+        <v>هندیجان</v>
       </c>
       <c r="D127">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
-        <v>1150003</v>
+        <v>10600019</v>
       </c>
       <c r="B128" t="str">
-        <v>خرم آباد</v>
+        <v>رامشیر</v>
       </c>
       <c r="C128" t="str">
-        <v>خرم-آباد</v>
+        <v>رامشیر</v>
       </c>
       <c r="D128">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>1150004</v>
+        <v>10600020</v>
       </c>
       <c r="B129" t="str">
-        <v>دلفان</v>
+        <v>گتوند</v>
       </c>
       <c r="C129" t="str">
-        <v>دلفان</v>
+        <v>گتوند</v>
       </c>
       <c r="D129">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>1150005</v>
+        <v>10600021</v>
       </c>
       <c r="B130" t="str">
-        <v>دورود</v>
+        <v>اندیکا</v>
       </c>
       <c r="C130" t="str">
-        <v>دورود</v>
+        <v>اندیکا</v>
       </c>
       <c r="D130">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>1150006</v>
+        <v>10600022</v>
       </c>
       <c r="B131" t="str">
-        <v>کوهدشت</v>
+        <v>هفتکل</v>
       </c>
       <c r="C131" t="str">
-        <v>کوهدشت</v>
+        <v>هفتکل</v>
       </c>
       <c r="D131">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>1150007</v>
+        <v>10600023</v>
       </c>
       <c r="B132" t="str">
-        <v>ازنا</v>
+        <v>هویزه</v>
       </c>
       <c r="C132" t="str">
-        <v>ازنا</v>
+        <v>هویزه</v>
       </c>
       <c r="D132">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>1150008</v>
+        <v>10600024</v>
       </c>
       <c r="B133" t="str">
-        <v>پلدختر</v>
+        <v>باوی</v>
       </c>
       <c r="C133" t="str">
-        <v>پلدختر</v>
+        <v>باوی</v>
       </c>
       <c r="D133">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>1150009</v>
+        <v>10600025</v>
       </c>
       <c r="B134" t="str">
-        <v>سلسله</v>
+        <v>حمیدیه</v>
       </c>
       <c r="C134" t="str">
-        <v>سلسله</v>
+        <v>حمیدیه</v>
       </c>
       <c r="D134">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>1160001</v>
+        <v>10600026</v>
       </c>
       <c r="B135" t="str">
-        <v>ایلام</v>
+        <v>آغاجاری</v>
       </c>
       <c r="C135" t="str">
-        <v>ایلام</v>
+        <v>آغاجاری</v>
       </c>
       <c r="D135">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>1160002</v>
+        <v>10600027</v>
       </c>
       <c r="B136" t="str">
-        <v>دره شهر</v>
+        <v>کارون</v>
       </c>
       <c r="C136" t="str">
-        <v>دره-شهر</v>
+        <v>کارون</v>
       </c>
       <c r="D136">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>1160003</v>
+        <v>10600028</v>
       </c>
       <c r="B137" t="str">
-        <v>دهلران</v>
+        <v>کرخه</v>
       </c>
       <c r="C137" t="str">
-        <v>دهلران</v>
+        <v>کرخه</v>
       </c>
       <c r="D137">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>1160004</v>
+        <v>10600029</v>
       </c>
       <c r="B138" t="str">
-        <v>چرداول</v>
+        <v>دزپارت</v>
       </c>
       <c r="C138" t="str">
-        <v>چرداول</v>
+        <v>دزپارت</v>
       </c>
       <c r="D138">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>1160005</v>
+        <v>10600030</v>
       </c>
       <c r="B139" t="str">
-        <v>مهران</v>
+        <v>صیدون</v>
       </c>
       <c r="C139" t="str">
-        <v>مهران</v>
+        <v>صیدون</v>
       </c>
       <c r="D139">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>1160006</v>
+        <v>10700001</v>
       </c>
       <c r="B140" t="str">
-        <v>آبدانان</v>
+        <v>آباده</v>
       </c>
       <c r="C140" t="str">
-        <v>آبدانان</v>
+        <v>آباده</v>
       </c>
       <c r="D140">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="141">
       <c r="A141">
-        <v>1160007</v>
+        <v>10700002</v>
       </c>
       <c r="B141" t="str">
-        <v>ایوان</v>
+        <v>استهبان</v>
       </c>
       <c r="C141" t="str">
-        <v>ایوان</v>
+        <v>استهبان</v>
       </c>
       <c r="D141">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>1160008</v>
+        <v>10700003</v>
       </c>
       <c r="B142" t="str">
-        <v>ملکشاهی</v>
+        <v>اقلید</v>
       </c>
       <c r="C142" t="str">
-        <v>ملکشاهی</v>
+        <v>اقلید</v>
       </c>
       <c r="D142">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>1160009</v>
+        <v>10700004</v>
       </c>
       <c r="B143" t="str">
-        <v>سیروان</v>
+        <v>جهرم</v>
       </c>
       <c r="C143" t="str">
-        <v>سیروان</v>
+        <v>جهرم</v>
       </c>
       <c r="D143">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>1170001</v>
+        <v>10700005</v>
       </c>
       <c r="B144" t="str">
-        <v>بویراحمد</v>
+        <v>داراب</v>
       </c>
       <c r="C144" t="str">
-        <v>بویراحمد</v>
+        <v>داراب</v>
       </c>
       <c r="D144">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="145">
       <c r="A145">
-        <v>1170002</v>
+        <v>10700006</v>
       </c>
       <c r="B145" t="str">
-        <v>کهگیلویه</v>
+        <v>سپیدان</v>
       </c>
       <c r="C145" t="str">
-        <v>کهگیلویه</v>
+        <v>سپیدان</v>
       </c>
       <c r="D145">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="146">
       <c r="A146">
-        <v>1170003</v>
+        <v>10700007</v>
       </c>
       <c r="B146" t="str">
-        <v>گچساران</v>
+        <v>شیراز</v>
       </c>
       <c r="C146" t="str">
-        <v>گچساران</v>
+        <v>شیراز</v>
       </c>
       <c r="D146">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>1170004</v>
+        <v>10700008</v>
       </c>
       <c r="B147" t="str">
-        <v>دنا</v>
+        <v>فسا</v>
       </c>
       <c r="C147" t="str">
-        <v>دنا</v>
+        <v>فسا</v>
       </c>
       <c r="D147">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>1170005</v>
+        <v>10700009</v>
       </c>
       <c r="B148" t="str">
-        <v>بهمیی</v>
+        <v>فیروزآباد</v>
       </c>
       <c r="C148" t="str">
-        <v>بهمیی</v>
+        <v>فیروزآباد</v>
       </c>
       <c r="D148">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="149">
       <c r="A149">
-        <v>1170006</v>
+        <v>10700010</v>
       </c>
       <c r="B149" t="str">
-        <v>چرام</v>
+        <v>کازرون</v>
       </c>
       <c r="C149" t="str">
-        <v>چرام</v>
+        <v>کازرون</v>
       </c>
       <c r="D149">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>1170007</v>
+        <v>10700011</v>
       </c>
       <c r="B150" t="str">
-        <v>باشت</v>
+        <v>لارستان</v>
       </c>
       <c r="C150" t="str">
-        <v>باشت</v>
+        <v>لارستان</v>
       </c>
       <c r="D150">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>1170008</v>
+        <v>10700012</v>
       </c>
       <c r="B151" t="str">
-        <v>لنده</v>
+        <v>مرودشت</v>
       </c>
       <c r="C151" t="str">
-        <v>لنده</v>
+        <v>مرودشت</v>
       </c>
       <c r="D151">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>1170009</v>
+        <v>10700013</v>
       </c>
       <c r="B152" t="str">
-        <v>مارگون</v>
+        <v>ممسنی</v>
       </c>
       <c r="C152" t="str">
-        <v>مارگون</v>
+        <v>ممسنی</v>
       </c>
       <c r="D152">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>1180001</v>
+        <v>10700014</v>
       </c>
       <c r="B153" t="str">
-        <v>بوشهر</v>
+        <v>نی ریز</v>
       </c>
       <c r="C153" t="str">
-        <v>بوشهر</v>
+        <v>نی-ریز</v>
       </c>
       <c r="D153">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="154">
       <c r="A154">
-        <v>1180002</v>
+        <v>10700015</v>
       </c>
       <c r="B154" t="str">
-        <v>تنگستان</v>
+        <v>لامرد</v>
       </c>
       <c r="C154" t="str">
-        <v>تنگستان</v>
+        <v>لامرد</v>
       </c>
       <c r="D154">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>1180003</v>
+        <v>10700016</v>
       </c>
       <c r="B155" t="str">
-        <v>دشتستان</v>
+        <v>بوانات</v>
       </c>
       <c r="C155" t="str">
-        <v>دشتستان</v>
+        <v>بوانات</v>
       </c>
       <c r="D155">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="156">
       <c r="A156">
-        <v>1180004</v>
+        <v>10700017</v>
       </c>
       <c r="B156" t="str">
-        <v>دشتی</v>
+        <v>ارسنجان</v>
       </c>
       <c r="C156" t="str">
-        <v>دشتی</v>
+        <v>ارسنجان</v>
       </c>
       <c r="D156">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="157">
       <c r="A157">
-        <v>1180005</v>
+        <v>10700018</v>
       </c>
       <c r="B157" t="str">
-        <v>دیر</v>
+        <v>خرم بید</v>
       </c>
       <c r="C157" t="str">
-        <v>دیر</v>
+        <v>خرم-بید</v>
       </c>
       <c r="D157">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="158">
       <c r="A158">
-        <v>1180006</v>
+        <v>10700019</v>
       </c>
       <c r="B158" t="str">
-        <v>کنگان</v>
+        <v>زرین دشت</v>
       </c>
       <c r="C158" t="str">
-        <v>کنگان</v>
+        <v>زرین-دشت</v>
       </c>
       <c r="D158">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="159">
       <c r="A159">
-        <v>1180007</v>
+        <v>10700020</v>
       </c>
       <c r="B159" t="str">
-        <v>گناوه</v>
+        <v>قیرو کارزین</v>
       </c>
       <c r="C159" t="str">
-        <v>گناوه</v>
+        <v>قیرو-کارزین</v>
       </c>
       <c r="D159">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="160">
       <c r="A160">
-        <v>1180008</v>
+        <v>10700021</v>
       </c>
       <c r="B160" t="str">
-        <v>دیلم</v>
+        <v>مهر</v>
       </c>
       <c r="C160" t="str">
-        <v>دیلم</v>
+        <v>مهر</v>
       </c>
       <c r="D160">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>1180009</v>
+        <v>10700022</v>
       </c>
       <c r="B161" t="str">
-        <v>جم</v>
+        <v>فراشبند</v>
       </c>
       <c r="C161" t="str">
-        <v>جم</v>
+        <v>فراشبند</v>
       </c>
       <c r="D161">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="162">
       <c r="A162">
-        <v>1190001</v>
+        <v>10700023</v>
       </c>
       <c r="B162" t="str">
-        <v>ابهر</v>
+        <v>پاسارگاد</v>
       </c>
       <c r="C162" t="str">
-        <v>ابهر</v>
+        <v>پاسارگاد</v>
       </c>
       <c r="D162">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>1190003</v>
+        <v>10700024</v>
       </c>
       <c r="B163" t="str">
-        <v>خدابنده</v>
+        <v>خنج</v>
       </c>
       <c r="C163" t="str">
-        <v>خدابنده</v>
+        <v>خنج</v>
       </c>
       <c r="D163">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>1190004</v>
+        <v>10700025</v>
       </c>
       <c r="B164" t="str">
-        <v>زنجان</v>
+        <v>سروستان</v>
       </c>
       <c r="C164" t="str">
-        <v>زنجان</v>
+        <v>سروستان</v>
       </c>
       <c r="D164">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="165">
       <c r="A165">
-        <v>1190006</v>
+        <v>10700026</v>
       </c>
       <c r="B165" t="str">
-        <v>ایجرود</v>
+        <v>رستم</v>
       </c>
       <c r="C165" t="str">
-        <v>ایجرود</v>
+        <v>رستم</v>
       </c>
       <c r="D165">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>1190007</v>
+        <v>10700027</v>
       </c>
       <c r="B166" t="str">
-        <v>خرمدره</v>
+        <v>گراش</v>
       </c>
       <c r="C166" t="str">
-        <v>خرمدره</v>
+        <v>گراش</v>
       </c>
       <c r="D166">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="167">
       <c r="A167">
-        <v>1190008</v>
+        <v>10700028</v>
       </c>
       <c r="B167" t="str">
-        <v>طارم</v>
+        <v>کوار</v>
       </c>
       <c r="C167" t="str">
-        <v>طارم</v>
+        <v>کوار</v>
       </c>
       <c r="D167">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="168">
       <c r="A168">
-        <v>1190009</v>
+        <v>10700029</v>
       </c>
       <c r="B168" t="str">
-        <v>ماهنشان</v>
+        <v>خرامه</v>
       </c>
       <c r="C168" t="str">
-        <v>ماهنشان</v>
+        <v>خرامه</v>
       </c>
       <c r="D168">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="169">
       <c r="A169">
-        <v>1200001</v>
+        <v>10700030</v>
       </c>
       <c r="B169" t="str">
-        <v>دامغان</v>
+        <v>زرقان</v>
       </c>
       <c r="C169" t="str">
-        <v>دامغان</v>
+        <v>زرقان</v>
       </c>
       <c r="D169">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="170">
       <c r="A170">
-        <v>1200002</v>
+        <v>10700031</v>
       </c>
       <c r="B170" t="str">
-        <v>سمنان</v>
+        <v>بیضاء</v>
       </c>
       <c r="C170" t="str">
-        <v>سمنان</v>
+        <v>بیضاء</v>
       </c>
       <c r="D170">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="171">
       <c r="A171">
-        <v>1200003</v>
+        <v>10700032</v>
       </c>
       <c r="B171" t="str">
-        <v>شاهرود</v>
+        <v>سرچهان</v>
       </c>
       <c r="C171" t="str">
-        <v>شاهرود</v>
+        <v>سرچهان</v>
       </c>
       <c r="D171">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="172">
       <c r="A172">
-        <v>1200004</v>
+        <v>10700033</v>
       </c>
       <c r="B172" t="str">
-        <v>گرمسار</v>
+        <v>کوه چنار</v>
       </c>
       <c r="C172" t="str">
-        <v>گرمسار</v>
+        <v>کوه-چنار</v>
       </c>
       <c r="D172">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>1200005</v>
+        <v>10700034</v>
       </c>
       <c r="B173" t="str">
-        <v>مهدی شهر</v>
+        <v>خفر</v>
       </c>
       <c r="C173" t="str">
-        <v>مهدی-شهر</v>
+        <v>خفر</v>
       </c>
       <c r="D173">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="174">
       <c r="A174">
-        <v>1200006</v>
+        <v>10700035</v>
       </c>
       <c r="B174" t="str">
-        <v>آرادان</v>
+        <v>بختگان</v>
       </c>
       <c r="C174" t="str">
-        <v>آرادان</v>
+        <v>بختگان</v>
       </c>
       <c r="D174">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="175">
       <c r="A175">
-        <v>1200007</v>
+        <v>10700036</v>
       </c>
       <c r="B175" t="str">
-        <v>میامی</v>
+        <v>اوز</v>
       </c>
       <c r="C175" t="str">
-        <v>میامی</v>
+        <v>اوز</v>
       </c>
       <c r="D175">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="176">
       <c r="A176">
-        <v>1200008</v>
+        <v>10700037</v>
       </c>
       <c r="B176" t="str">
-        <v>سرخه</v>
+        <v>جویم</v>
       </c>
       <c r="C176" t="str">
-        <v>سرخه</v>
+        <v>جویم</v>
       </c>
       <c r="D176">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="177">
       <c r="A177">
-        <v>1210001</v>
+        <v>10800001</v>
       </c>
       <c r="B177" t="str">
-        <v>اردکان</v>
+        <v>بافت</v>
       </c>
       <c r="C177" t="str">
-        <v>اردکان</v>
+        <v>بافت</v>
       </c>
       <c r="D177">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>1210002</v>
+        <v>10800002</v>
       </c>
       <c r="B178" t="str">
-        <v>بافق</v>
+        <v>بم</v>
       </c>
       <c r="C178" t="str">
-        <v>بافق</v>
+        <v>بم</v>
       </c>
       <c r="D178">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>1210003</v>
+        <v>10800003</v>
       </c>
       <c r="B179" t="str">
-        <v>تفت</v>
+        <v>جیرفت</v>
       </c>
       <c r="C179" t="str">
-        <v>تفت</v>
+        <v>جیرفت</v>
       </c>
       <c r="D179">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>1210004</v>
+        <v>10800004</v>
       </c>
       <c r="B180" t="str">
-        <v>مهریز</v>
+        <v>رفسنجان</v>
       </c>
       <c r="C180" t="str">
-        <v>مهریز</v>
+        <v>رفسنجان</v>
       </c>
       <c r="D180">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="181">
       <c r="A181">
-        <v>1210005</v>
+        <v>10800005</v>
       </c>
       <c r="B181" t="str">
-        <v>یزد</v>
+        <v>زرند</v>
       </c>
       <c r="C181" t="str">
-        <v>یزد</v>
+        <v>زرند</v>
       </c>
       <c r="D181">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="182">
       <c r="A182">
-        <v>1210006</v>
+        <v>10800006</v>
       </c>
       <c r="B182" t="str">
-        <v>میبد</v>
+        <v>سیرجان</v>
       </c>
       <c r="C182" t="str">
-        <v>میبد</v>
+        <v>سیرجان</v>
       </c>
       <c r="D182">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="183">
       <c r="A183">
-        <v>1210007</v>
+        <v>10800007</v>
       </c>
       <c r="B183" t="str">
-        <v>ابرکوه</v>
+        <v>شهربابک</v>
       </c>
       <c r="C183" t="str">
-        <v>ابرکوه</v>
+        <v>شهربابک</v>
       </c>
       <c r="D183">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="184">
       <c r="A184">
-        <v>1210008</v>
+        <v>10800008</v>
       </c>
       <c r="B184" t="str">
-        <v>اشکذر</v>
+        <v>کرمان</v>
       </c>
       <c r="C184" t="str">
-        <v>اشکذر</v>
+        <v>کرمان</v>
       </c>
       <c r="D184">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="185">
       <c r="A185">
-        <v>1210009</v>
+        <v>10800009</v>
       </c>
       <c r="B185" t="str">
-        <v>خاتم</v>
+        <v>کهنوج</v>
       </c>
       <c r="C185" t="str">
-        <v>خاتم</v>
+        <v>کهنوج</v>
       </c>
       <c r="D185">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="186">
       <c r="A186">
-        <v>1220001</v>
+        <v>10800010</v>
       </c>
       <c r="B186" t="str">
-        <v>ابوموسی</v>
+        <v>بردسیر</v>
       </c>
       <c r="C186" t="str">
-        <v>ابوموسی</v>
+        <v>بردسیر</v>
       </c>
       <c r="D186">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="187">
       <c r="A187">
-        <v>1220002</v>
+        <v>10800011</v>
       </c>
       <c r="B187" t="str">
-        <v>بندر عباس</v>
+        <v>راور</v>
       </c>
       <c r="C187" t="str">
-        <v>بندر-عباس</v>
+        <v>راور</v>
       </c>
       <c r="D187">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>1220003</v>
+        <v>10800012</v>
       </c>
       <c r="B188" t="str">
-        <v>بندر لنگه</v>
+        <v>عنبرآباد</v>
       </c>
       <c r="C188" t="str">
-        <v>بندر-لنگه</v>
+        <v>عنبرآباد</v>
       </c>
       <c r="D188">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>1220004</v>
+        <v>10800013</v>
       </c>
       <c r="B189" t="str">
-        <v>قشم</v>
+        <v>منوجان</v>
       </c>
       <c r="C189" t="str">
-        <v>قشم</v>
+        <v>منوجان</v>
       </c>
       <c r="D189">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="190">
       <c r="A190">
-        <v>1220005</v>
+        <v>10800014</v>
       </c>
       <c r="B190" t="str">
-        <v>میناب</v>
+        <v>کوهبنان</v>
       </c>
       <c r="C190" t="str">
-        <v>میناب</v>
+        <v>کوهبنان</v>
       </c>
       <c r="D190">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>1220006</v>
+        <v>10800015</v>
       </c>
       <c r="B191" t="str">
-        <v>جاسک</v>
+        <v>رودبارجنوب</v>
       </c>
       <c r="C191" t="str">
-        <v>جاسک</v>
+        <v>رودبارجنوب</v>
       </c>
       <c r="D191">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>1220007</v>
+        <v>10800016</v>
       </c>
       <c r="B192" t="str">
-        <v>رودان</v>
+        <v>قلعه گنج</v>
       </c>
       <c r="C192" t="str">
-        <v>رودان</v>
+        <v>قلعه-گنج</v>
       </c>
       <c r="D192">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>1220008</v>
+        <v>10800017</v>
       </c>
       <c r="B193" t="str">
-        <v>حاجی آباد</v>
+        <v>ریگان</v>
       </c>
       <c r="C193" t="str">
-        <v>حاجی-آباد</v>
+        <v>ریگان</v>
       </c>
       <c r="D193">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="194">
       <c r="A194">
-        <v>1220009</v>
+        <v>10800018</v>
       </c>
       <c r="B194" t="str">
-        <v>بستک</v>
+        <v>رابر</v>
       </c>
       <c r="C194" t="str">
-        <v>بستک</v>
+        <v>رابر</v>
       </c>
       <c r="D194">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>1230001</v>
+        <v>10800019</v>
       </c>
       <c r="B195" t="str">
-        <v>تهران</v>
+        <v>فهرج</v>
       </c>
       <c r="C195" t="str">
-        <v>تهران</v>
+        <v>فهرج</v>
       </c>
       <c r="D195">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>1230002</v>
+        <v>10800020</v>
       </c>
       <c r="B196" t="str">
-        <v>دماوند</v>
+        <v>انار</v>
       </c>
       <c r="C196" t="str">
-        <v>دماوند</v>
+        <v>انار</v>
       </c>
       <c r="D196">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>1230003</v>
+        <v>10800021</v>
       </c>
       <c r="B197" t="str">
-        <v>ری</v>
+        <v>نرماشیر</v>
       </c>
       <c r="C197" t="str">
-        <v>ری</v>
+        <v>نرماشیر</v>
       </c>
       <c r="D197">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>1230004</v>
+        <v>10800022</v>
       </c>
       <c r="B198" t="str">
-        <v>شمیرانات</v>
+        <v>فاریاب</v>
       </c>
       <c r="C198" t="str">
-        <v>شمیرانات</v>
+        <v>فاریاب</v>
       </c>
       <c r="D198">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>1230006</v>
+        <v>10800023</v>
       </c>
       <c r="B199" t="str">
-        <v>ورامین</v>
+        <v>ارزوییه</v>
       </c>
       <c r="C199" t="str">
-        <v>ورامین</v>
+        <v>ارزوییه</v>
       </c>
       <c r="D199">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>1230009</v>
+        <v>10800024</v>
       </c>
       <c r="B200" t="str">
-        <v>شهریار</v>
+        <v>گنبکی</v>
       </c>
       <c r="C200" t="str">
-        <v>شهریار</v>
+        <v>گنبکی</v>
       </c>
       <c r="D200">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>1240001</v>
+        <v>10800025</v>
       </c>
       <c r="B201" t="str">
-        <v>اردبیل</v>
+        <v>جازموریان</v>
       </c>
       <c r="C201" t="str">
-        <v>اردبیل</v>
+        <v>جازموریان</v>
       </c>
       <c r="D201">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="202">
       <c r="A202">
-        <v>1240002</v>
+        <v>10900004</v>
       </c>
       <c r="B202" t="str">
-        <v>بیله سوار</v>
+        <v>تایباد</v>
       </c>
       <c r="C202" t="str">
-        <v>بیله-سوار</v>
+        <v>تایباد</v>
       </c>
       <c r="D202">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>1240003</v>
+        <v>10900005</v>
       </c>
       <c r="B203" t="str">
-        <v>خلخال</v>
+        <v>تربت حیدریه</v>
       </c>
       <c r="C203" t="str">
-        <v>خلخال</v>
+        <v>تربت-حیدریه</v>
       </c>
       <c r="D203">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>1240004</v>
+        <v>10900006</v>
       </c>
       <c r="B204" t="str">
-        <v>مشگین شهر</v>
+        <v>تربت جام</v>
       </c>
       <c r="C204" t="str">
-        <v>مشگین-شهر</v>
+        <v>تربت-جام</v>
       </c>
       <c r="D204">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>1240005</v>
+        <v>10900007</v>
       </c>
       <c r="B205" t="str">
-        <v>گرمی</v>
+        <v>درگز</v>
       </c>
       <c r="C205" t="str">
-        <v>گرمی</v>
+        <v>درگز</v>
       </c>
       <c r="D205">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>1240006</v>
+        <v>10900008</v>
       </c>
       <c r="B206" t="str">
-        <v>پارس آباد</v>
+        <v>سبزوار</v>
       </c>
       <c r="C206" t="str">
-        <v>پارس-آباد</v>
+        <v>سبزوار</v>
       </c>
       <c r="D206">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>1240007</v>
+        <v>10900013</v>
       </c>
       <c r="B207" t="str">
-        <v>کوثر</v>
+        <v>قوچان</v>
       </c>
       <c r="C207" t="str">
-        <v>کوثر</v>
+        <v>قوچان</v>
       </c>
       <c r="D207">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>1240008</v>
+        <v>10900014</v>
       </c>
       <c r="B208" t="str">
-        <v>نمین</v>
+        <v>کاشمر</v>
       </c>
       <c r="C208" t="str">
-        <v>نمین</v>
+        <v>کاشمر</v>
       </c>
       <c r="D208">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>1240009</v>
+        <v>10900015</v>
       </c>
       <c r="B209" t="str">
-        <v>نیر</v>
+        <v>گناباد</v>
       </c>
       <c r="C209" t="str">
-        <v>نیر</v>
+        <v>گناباد</v>
       </c>
       <c r="D209">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>1250001</v>
+        <v>10900016</v>
       </c>
       <c r="B210" t="str">
-        <v>قم</v>
+        <v>مشهد</v>
       </c>
       <c r="C210" t="str">
-        <v>قم</v>
+        <v>مشهد</v>
       </c>
       <c r="D210">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>1250002</v>
+        <v>10900017</v>
       </c>
       <c r="B211" t="str">
-        <v>جعفرآباد</v>
+        <v>نیشابور</v>
       </c>
       <c r="C211" t="str">
-        <v>جعفرآباد</v>
+        <v>نیشابور</v>
       </c>
       <c r="D211">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>1250003</v>
+        <v>10900018</v>
       </c>
       <c r="B212" t="str">
-        <v>کهک</v>
+        <v>چناران</v>
       </c>
       <c r="C212" t="str">
-        <v>کهک</v>
+        <v>چناران</v>
       </c>
       <c r="D212">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>1260001</v>
+        <v>10900019</v>
       </c>
       <c r="B213" t="str">
-        <v>بویین زهرا</v>
+        <v>خواف</v>
       </c>
       <c r="C213" t="str">
-        <v>بویین-زهرا</v>
+        <v>خواف</v>
       </c>
       <c r="D213">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>1260002</v>
+        <v>10900020</v>
       </c>
       <c r="B214" t="str">
-        <v>تاکستان</v>
+        <v>سرخس</v>
       </c>
       <c r="C214" t="str">
-        <v>تاکستان</v>
+        <v>سرخس</v>
       </c>
       <c r="D214">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>1260003</v>
+        <v>10900022</v>
       </c>
       <c r="B215" t="str">
-        <v>قزوین</v>
+        <v>فریمان</v>
       </c>
       <c r="C215" t="str">
-        <v>قزوین</v>
+        <v>فریمان</v>
       </c>
       <c r="D215">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>1260004</v>
+        <v>10900023</v>
       </c>
       <c r="B216" t="str">
-        <v>آبیک</v>
+        <v>بردسکن</v>
       </c>
       <c r="C216" t="str">
-        <v>آبیک</v>
+        <v>بردسکن</v>
       </c>
       <c r="D216">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>1260005</v>
+        <v>10900027</v>
       </c>
       <c r="B217" t="str">
-        <v>البرز</v>
+        <v>رشتخوار</v>
       </c>
       <c r="C217" t="str">
-        <v>البرز</v>
+        <v>رشتخوار</v>
       </c>
       <c r="D217">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>1260006</v>
+        <v>10900028</v>
       </c>
       <c r="B218" t="str">
-        <v>آوج</v>
+        <v>کلات</v>
       </c>
       <c r="C218" t="str">
-        <v>آوج</v>
+        <v>کلات</v>
       </c>
       <c r="D218">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>1270001</v>
+        <v>10900029</v>
       </c>
       <c r="B219" t="str">
-        <v>بندرگز</v>
+        <v>خلیل آباد</v>
       </c>
       <c r="C219" t="str">
-        <v>بندرگز</v>
+        <v>خلیل-آباد</v>
       </c>
       <c r="D219">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>1270002</v>
+        <v>10900030</v>
       </c>
       <c r="B220" t="str">
-        <v>ترکمن</v>
+        <v>مه ولات</v>
       </c>
       <c r="C220" t="str">
-        <v>ترکمن</v>
+        <v>مه-ولات</v>
       </c>
       <c r="D220">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="221">
       <c r="A221">
-        <v>1270003</v>
+        <v>10900031</v>
       </c>
       <c r="B221" t="str">
-        <v>علی آباد کتول</v>
+        <v>بجستان</v>
       </c>
       <c r="C221" t="str">
-        <v>علی-آباد-کتول</v>
+        <v>بجستان</v>
       </c>
       <c r="D221">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="222">
       <c r="A222">
-        <v>1270004</v>
+        <v>10900032</v>
       </c>
       <c r="B222" t="str">
-        <v>کردکوی</v>
+        <v>طرقبه شاندیز</v>
       </c>
       <c r="C222" t="str">
-        <v>کردکوی</v>
+        <v>طرقبه-شاندیز</v>
       </c>
       <c r="D222">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>1270005</v>
+        <v>10900033</v>
       </c>
       <c r="B223" t="str">
-        <v>گرگان</v>
+        <v>فیروزه</v>
       </c>
       <c r="C223" t="str">
-        <v>گرگان</v>
+        <v>فیروزه</v>
       </c>
       <c r="D223">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>1270006</v>
+        <v>10900034</v>
       </c>
       <c r="B224" t="str">
-        <v>گنبدکاووس</v>
+        <v>جغتای</v>
       </c>
       <c r="C224" t="str">
-        <v>گنبدکاووس</v>
+        <v>جغتای</v>
       </c>
       <c r="D224">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="225">
       <c r="A225">
-        <v>1270007</v>
+        <v>10900035</v>
       </c>
       <c r="B225" t="str">
-        <v>مینودشت</v>
+        <v>زاوه</v>
       </c>
       <c r="C225" t="str">
-        <v>مینودشت</v>
+        <v>زاوه</v>
       </c>
       <c r="D225">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>1270008</v>
+        <v>10900036</v>
       </c>
       <c r="B226" t="str">
-        <v>آق قلا</v>
+        <v>جوین</v>
       </c>
       <c r="C226" t="str">
-        <v>آق-قلا</v>
+        <v>جوین</v>
       </c>
       <c r="D226">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>1270009</v>
+        <v>10900037</v>
       </c>
       <c r="B227" t="str">
-        <v>کلاله</v>
+        <v>باخرز</v>
       </c>
       <c r="C227" t="str">
-        <v>کلاله</v>
+        <v>باخرز</v>
       </c>
       <c r="D227">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>1280001</v>
+        <v>10900038</v>
       </c>
       <c r="B228" t="str">
-        <v>اسفراین</v>
+        <v>خوشاب</v>
       </c>
       <c r="C228" t="str">
-        <v>اسفراین</v>
+        <v>خوشاب</v>
       </c>
       <c r="D228">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>1280002</v>
+        <v>10900039</v>
       </c>
       <c r="B229" t="str">
-        <v>بجنورد</v>
+        <v>داورزن</v>
       </c>
       <c r="C229" t="str">
-        <v>بجنورد</v>
+        <v>داورزن</v>
       </c>
       <c r="D229">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>1280003</v>
+        <v>10900040</v>
       </c>
       <c r="B230" t="str">
-        <v>جاجرم</v>
+        <v>صالح آباد</v>
       </c>
       <c r="C230" t="str">
-        <v>جاجرم</v>
+        <v>صالح-آباد</v>
       </c>
       <c r="D230">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>1280004</v>
+        <v>10900041</v>
       </c>
       <c r="B231" t="str">
-        <v>شیروان</v>
+        <v>کوهسرخ</v>
       </c>
       <c r="C231" t="str">
-        <v>شیروان</v>
+        <v>کوهسرخ</v>
       </c>
       <c r="D231">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>1280005</v>
+        <v>10900042</v>
       </c>
       <c r="B232" t="str">
-        <v>فاروج</v>
+        <v>زبرخان</v>
       </c>
       <c r="C232" t="str">
-        <v>فاروج</v>
+        <v>زبرخان</v>
       </c>
       <c r="D232">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>1280006</v>
+        <v>10900043</v>
       </c>
       <c r="B233" t="str">
-        <v>سملقان</v>
+        <v>ششتمد</v>
       </c>
       <c r="C233" t="str">
-        <v>سملقان</v>
+        <v>ششتمد</v>
       </c>
       <c r="D233">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>1280007</v>
+        <v>10900044</v>
       </c>
       <c r="B234" t="str">
-        <v>گرمه</v>
+        <v>گلبهار</v>
       </c>
       <c r="C234" t="str">
-        <v>گرمه</v>
+        <v>گلبهار</v>
       </c>
       <c r="D234">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="235">
       <c r="A235">
-        <v>1280008</v>
+        <v>10900045</v>
       </c>
       <c r="B235" t="str">
-        <v>راز و جرگلان</v>
+        <v>میان جلگه</v>
       </c>
       <c r="C235" t="str">
-        <v>راز-و-جرگلان</v>
+        <v>میان-جلگه</v>
       </c>
       <c r="D235">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>1280009</v>
+        <v>11000001</v>
       </c>
       <c r="B236" t="str">
-        <v>بام و صفی آباد</v>
+        <v>اردستان</v>
       </c>
       <c r="C236" t="str">
-        <v>بام-و-صفی-آباد</v>
+        <v>اردستان</v>
       </c>
       <c r="D236">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>1290001</v>
+        <v>11000002</v>
       </c>
       <c r="B237" t="str">
-        <v>بیرجند</v>
+        <v>اصفهان</v>
       </c>
       <c r="C237" t="str">
-        <v>بیرجند</v>
+        <v>اصفهان</v>
       </c>
       <c r="D237">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>1290002</v>
+        <v>11000003</v>
       </c>
       <c r="B238" t="str">
-        <v>درمیان</v>
+        <v>خمینی شهر</v>
       </c>
       <c r="C238" t="str">
-        <v>درمیان</v>
+        <v>خمینی-شهر</v>
       </c>
       <c r="D238">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>1290003</v>
+        <v>11000004</v>
       </c>
       <c r="B239" t="str">
-        <v>سربیشه</v>
+        <v>خوانسار</v>
       </c>
       <c r="C239" t="str">
-        <v>سربیشه</v>
+        <v>خوانسار</v>
       </c>
       <c r="D239">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>1290004</v>
+        <v>11000005</v>
       </c>
       <c r="B240" t="str">
-        <v>قاینات</v>
+        <v>سمیرم</v>
       </c>
       <c r="C240" t="str">
-        <v>قاینات</v>
+        <v>سمیرم</v>
       </c>
       <c r="D240">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>1290005</v>
+        <v>11000006</v>
       </c>
       <c r="B241" t="str">
-        <v>نهبندان</v>
+        <v>فریدن</v>
       </c>
       <c r="C241" t="str">
-        <v>نهبندان</v>
+        <v>فریدن</v>
       </c>
       <c r="D241">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>1290006</v>
+        <v>11000007</v>
       </c>
       <c r="B242" t="str">
-        <v>سرایان</v>
+        <v>فریدونشهر</v>
       </c>
       <c r="C242" t="str">
-        <v>سرایان</v>
+        <v>فریدونشهر</v>
       </c>
       <c r="D242">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>1290007</v>
+        <v>11000008</v>
       </c>
       <c r="B243" t="str">
-        <v>فردوس</v>
+        <v>فلاورجان</v>
       </c>
       <c r="C243" t="str">
-        <v>فردوس</v>
+        <v>فلاورجان</v>
       </c>
       <c r="D243">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>1290008</v>
+        <v>11000009</v>
       </c>
       <c r="B244" t="str">
-        <v>بشرویه</v>
+        <v>شهرضا</v>
       </c>
       <c r="C244" t="str">
-        <v>بشرویه</v>
+        <v>شهرضا</v>
       </c>
       <c r="D244">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>1290009</v>
+        <v>11000010</v>
       </c>
       <c r="B245" t="str">
-        <v>زیرکوه</v>
+        <v>کاشان</v>
       </c>
       <c r="C245" t="str">
-        <v>زیرکوه</v>
+        <v>کاشان</v>
       </c>
       <c r="D245">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>1300001</v>
+        <v>11000011</v>
       </c>
       <c r="B246" t="str">
-        <v>کرج</v>
+        <v>گلپایگان</v>
       </c>
       <c r="C246" t="str">
-        <v>کرج</v>
+        <v>گلپایگان</v>
       </c>
       <c r="D246">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="247">
       <c r="A247">
-        <v>1300002</v>
+        <v>11000012</v>
       </c>
       <c r="B247" t="str">
-        <v>ساوجبلاغ</v>
+        <v>لنجان</v>
       </c>
       <c r="C247" t="str">
-        <v>ساوجبلاغ</v>
+        <v>لنجان</v>
       </c>
       <c r="D247">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="248">
       <c r="A248">
-        <v>1300003</v>
+        <v>11000013</v>
       </c>
       <c r="B248" t="str">
-        <v>نظرآباد</v>
+        <v>نایین</v>
       </c>
       <c r="C248" t="str">
-        <v>نظرآباد</v>
+        <v>نایین</v>
       </c>
       <c r="D248">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="249">
       <c r="A249">
-        <v>1300004</v>
+        <v>11000014</v>
       </c>
       <c r="B249" t="str">
-        <v>طالقان</v>
+        <v>نجف آباد</v>
       </c>
       <c r="C249" t="str">
-        <v>طالقان</v>
+        <v>نجف-آباد</v>
       </c>
       <c r="D249">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="250">
       <c r="A250">
-        <v>1300005</v>
+        <v>11000015</v>
       </c>
       <c r="B250" t="str">
-        <v>اشتهارد</v>
+        <v>نطنز</v>
       </c>
       <c r="C250" t="str">
-        <v>اشتهارد</v>
+        <v>نطنز</v>
       </c>
       <c r="D250">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="251">
       <c r="A251">
-        <v>1300006</v>
+        <v>11000016</v>
       </c>
       <c r="B251" t="str">
-        <v>فردیس</v>
+        <v>شاهین شهرو میمه</v>
       </c>
       <c r="C251" t="str">
-        <v>فردیس</v>
+        <v>شاهین-شهرو-میمه</v>
       </c>
       <c r="D251">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="252">
       <c r="A252">
-        <v>1300007</v>
+        <v>11000017</v>
       </c>
       <c r="B252" t="str">
-        <v>چهارباغ</v>
+        <v>مبارکه</v>
       </c>
       <c r="C252" t="str">
-        <v>چهارباغ</v>
+        <v>مبارکه</v>
       </c>
       <c r="D252">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="253">
       <c r="A253">
-        <v>10000010</v>
+        <v>11000018</v>
       </c>
       <c r="B253" t="str">
-        <v>زرندیه</v>
+        <v>آران و بیدگل</v>
       </c>
       <c r="C253" t="str">
-        <v>زرندیه</v>
+        <v>آران-و-بیدگل</v>
       </c>
       <c r="D253">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="254">
       <c r="A254">
-        <v>10000011</v>
+        <v>11000019</v>
       </c>
       <c r="B254" t="str">
-        <v>کمیجان</v>
+        <v>تیران وکرون</v>
       </c>
       <c r="C254" t="str">
-        <v>کمیجان</v>
+        <v>تیران-وکرون</v>
       </c>
       <c r="D254">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="255">
       <c r="A255">
-        <v>10000012</v>
+        <v>11000020</v>
       </c>
       <c r="B255" t="str">
-        <v>خنداب</v>
+        <v>چادگان</v>
       </c>
       <c r="C255" t="str">
-        <v>خنداب</v>
+        <v>چادگان</v>
       </c>
       <c r="D255">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="256">
       <c r="A256">
-        <v>10000013</v>
+        <v>11000021</v>
       </c>
       <c r="B256" t="str">
-        <v>فراهان</v>
+        <v>دهاقان</v>
       </c>
       <c r="C256" t="str">
-        <v>فراهان</v>
+        <v>دهاقان</v>
       </c>
       <c r="D256">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="257">
       <c r="A257">
-        <v>10100010</v>
+        <v>11000022</v>
       </c>
       <c r="B257" t="str">
-        <v>لنگرود</v>
+        <v>برخوار</v>
       </c>
       <c r="C257" t="str">
-        <v>لنگرود</v>
+        <v>برخوار</v>
       </c>
       <c r="D257">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="258">
       <c r="A258">
-        <v>10100011</v>
+        <v>11000023</v>
       </c>
       <c r="B258" t="str">
-        <v>لاهیجان</v>
+        <v>خور و بیابانک</v>
       </c>
       <c r="C258" t="str">
-        <v>لاهیجان</v>
+        <v>خور-و-بیابانک</v>
       </c>
       <c r="D258">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="259">
       <c r="A259">
-        <v>10100012</v>
+        <v>11000024</v>
       </c>
       <c r="B259" t="str">
-        <v>شفت</v>
+        <v>بویین و میاندشت</v>
       </c>
       <c r="C259" t="str">
-        <v>شفت</v>
+        <v>بویین-و-میاندشت</v>
       </c>
       <c r="D259">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="260">
       <c r="A260">
-        <v>10100013</v>
+        <v>11000025</v>
       </c>
       <c r="B260" t="str">
-        <v>املش</v>
+        <v>کوهپایه</v>
       </c>
       <c r="C260" t="str">
-        <v>املش</v>
+        <v>کوهپایه</v>
       </c>
       <c r="D260">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="261">
       <c r="A261">
-        <v>10100014</v>
+        <v>11000026</v>
       </c>
       <c r="B261" t="str">
-        <v>رضوانشهر</v>
+        <v>جرقویه</v>
       </c>
       <c r="C261" t="str">
-        <v>رضوانشهر</v>
+        <v>جرقویه</v>
       </c>
       <c r="D261">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="262">
       <c r="A262">
-        <v>10100015</v>
+        <v>11000027</v>
       </c>
       <c r="B262" t="str">
-        <v>سیاهکل</v>
+        <v>ورزنه</v>
       </c>
       <c r="C262" t="str">
-        <v>سیاهکل</v>
+        <v>ورزنه</v>
       </c>
       <c r="D262">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="263">
       <c r="A263">
-        <v>10100016</v>
+        <v>11000028</v>
       </c>
       <c r="B263" t="str">
-        <v>ماسال</v>
+        <v>هرند</v>
       </c>
       <c r="C263" t="str">
-        <v>ماسال</v>
+        <v>هرند</v>
       </c>
       <c r="D263">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="264">
       <c r="A264">
-        <v>10100017</v>
+        <v>11100001</v>
       </c>
       <c r="B264" t="str">
-        <v>خمام</v>
+        <v>ایرانشهر</v>
       </c>
       <c r="C264" t="str">
-        <v>خمام</v>
+        <v>ایرانشهر</v>
       </c>
       <c r="D264">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="265">
       <c r="A265">
-        <v>10200010</v>
+        <v>11100002</v>
       </c>
       <c r="B265" t="str">
-        <v>قایم شهر</v>
+        <v>چاه بهار</v>
       </c>
       <c r="C265" t="str">
-        <v>قایم-شهر</v>
+        <v>چاه-بهار</v>
       </c>
       <c r="D265">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="266">
       <c r="A266">
-        <v>10200014</v>
+        <v>11100003</v>
       </c>
       <c r="B266" t="str">
-        <v>نور</v>
+        <v>خاش</v>
       </c>
       <c r="C266" t="str">
-        <v>نور</v>
+        <v>خاش</v>
       </c>
       <c r="D266">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="267">
       <c r="A267">
-        <v>10200015</v>
+        <v>11100004</v>
       </c>
       <c r="B267" t="str">
-        <v>نوشهر</v>
+        <v>زابل</v>
       </c>
       <c r="C267" t="str">
-        <v>نوشهر</v>
+        <v>زابل</v>
       </c>
       <c r="D267">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="268">
       <c r="A268">
-        <v>10200016</v>
+        <v>11100005</v>
       </c>
       <c r="B268" t="str">
-        <v>بابلسر</v>
+        <v>زاهدان</v>
       </c>
       <c r="C268" t="str">
-        <v>بابلسر</v>
+        <v>زاهدان</v>
       </c>
       <c r="D268">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="269">
       <c r="A269">
-        <v>10200018</v>
+        <v>11100006</v>
       </c>
       <c r="B269" t="str">
-        <v>محمودآباد</v>
+        <v>سراوان</v>
       </c>
       <c r="C269" t="str">
-        <v>محمودآباد</v>
+        <v>سراوان</v>
       </c>
       <c r="D269">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="270">
       <c r="A270">
-        <v>10200019</v>
+        <v>11100007</v>
       </c>
       <c r="B270" t="str">
-        <v>نکا</v>
+        <v>نیک شهر</v>
       </c>
       <c r="C270" t="str">
-        <v>نکا</v>
+        <v>نیک-شهر</v>
       </c>
       <c r="D270">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="271">
       <c r="A271">
-        <v>10200020</v>
+        <v>11100008</v>
       </c>
       <c r="B271" t="str">
-        <v>چالوس</v>
+        <v>راسک</v>
       </c>
       <c r="C271" t="str">
-        <v>چالوس</v>
+        <v>راسک</v>
       </c>
       <c r="D271">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="272">
       <c r="A272">
-        <v>10200021</v>
+        <v>11100009</v>
       </c>
       <c r="B272" t="str">
-        <v>جویبار</v>
+        <v>کنارک</v>
       </c>
       <c r="C272" t="str">
-        <v>جویبار</v>
+        <v>کنارک</v>
       </c>
       <c r="D272">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="273">
       <c r="A273">
-        <v>10200022</v>
+        <v>11100010</v>
       </c>
       <c r="B273" t="str">
-        <v>گلوگاه</v>
+        <v>زهک</v>
       </c>
       <c r="C273" t="str">
-        <v>گلوگاه</v>
+        <v>زهک</v>
       </c>
       <c r="D273">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="274">
       <c r="A274">
-        <v>10200023</v>
+        <v>11100011</v>
       </c>
       <c r="B274" t="str">
-        <v>فریدونکنار</v>
+        <v>هیرمند</v>
       </c>
       <c r="C274" t="str">
-        <v>فریدونکنار</v>
+        <v>هیرمند</v>
       </c>
       <c r="D274">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="275">
       <c r="A275">
-        <v>10200024</v>
+        <v>11100012</v>
       </c>
       <c r="B275" t="str">
-        <v>عباس آباد</v>
+        <v>دلگان</v>
       </c>
       <c r="C275" t="str">
-        <v>عباس-آباد</v>
+        <v>دلگان</v>
       </c>
       <c r="D275">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="276">
       <c r="A276">
-        <v>10200025</v>
+        <v>11100013</v>
       </c>
       <c r="B276" t="str">
-        <v>میاندورود</v>
+        <v>مهرستان</v>
       </c>
       <c r="C276" t="str">
-        <v>میاندورود</v>
+        <v>مهرستان</v>
       </c>
       <c r="D276">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="277">
       <c r="A277">
-        <v>10200026</v>
+        <v>11100014</v>
       </c>
       <c r="B277" t="str">
-        <v>سیمرغ</v>
+        <v>سیب و سوران</v>
       </c>
       <c r="C277" t="str">
-        <v>سیمرغ</v>
+        <v>سیب-و-سوران</v>
       </c>
       <c r="D277">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="278">
       <c r="A278">
-        <v>10200027</v>
+        <v>11100015</v>
       </c>
       <c r="B278" t="str">
-        <v>سوادکوه شمالی</v>
+        <v>نیمروز</v>
       </c>
       <c r="C278" t="str">
-        <v>سوادکوه-شمالی</v>
+        <v>نیمروز</v>
       </c>
       <c r="D278">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="279">
       <c r="A279">
-        <v>10200028</v>
+        <v>11100016</v>
       </c>
       <c r="B279" t="str">
-        <v>کلاردشت</v>
+        <v>هامون</v>
       </c>
       <c r="C279" t="str">
-        <v>کلاردشت</v>
+        <v>هامون</v>
       </c>
       <c r="D279">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="280">
       <c r="A280">
-        <v>10300010</v>
+        <v>11100017</v>
       </c>
       <c r="B280" t="str">
-        <v>میانه</v>
+        <v>میرجاوه</v>
       </c>
       <c r="C280" t="str">
-        <v>میانه</v>
+        <v>میرجاوه</v>
       </c>
       <c r="D280">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="281">
       <c r="A281">
-        <v>10300011</v>
+        <v>11100018</v>
       </c>
       <c r="B281" t="str">
-        <v>هشترود</v>
+        <v>قصرقند</v>
       </c>
       <c r="C281" t="str">
-        <v>هشترود</v>
+        <v>قصرقند</v>
       </c>
       <c r="D281">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="282">
       <c r="A282">
-        <v>10300012</v>
+        <v>11100019</v>
       </c>
       <c r="B282" t="str">
-        <v>بناب</v>
+        <v>فنوج</v>
       </c>
       <c r="C282" t="str">
-        <v>بناب</v>
+        <v>فنوج</v>
       </c>
       <c r="D282">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="283">
       <c r="A283">
-        <v>10300013</v>
+        <v>11100020</v>
       </c>
       <c r="B283" t="str">
-        <v>بستان آباد</v>
+        <v>بمپور</v>
       </c>
       <c r="C283" t="str">
-        <v>بستان-آباد</v>
+        <v>بمپور</v>
       </c>
       <c r="D283">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="284">
       <c r="A284">
-        <v>10300014</v>
+        <v>11100021</v>
       </c>
       <c r="B284" t="str">
-        <v>شبستر</v>
+        <v>تفتان</v>
       </c>
       <c r="C284" t="str">
-        <v>شبستر</v>
+        <v>تفتان</v>
       </c>
       <c r="D284">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="285">
       <c r="A285">
-        <v>10300015</v>
+        <v>11100022</v>
       </c>
       <c r="B285" t="str">
-        <v>کلیبر</v>
+        <v>دشتیاری</v>
       </c>
       <c r="C285" t="str">
-        <v>کلیبر</v>
+        <v>دشتیاری</v>
       </c>
       <c r="D285">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="286">
       <c r="A286">
-        <v>10300016</v>
+        <v>11100023</v>
       </c>
       <c r="B286" t="str">
-        <v>هریس</v>
+        <v>سرباز</v>
       </c>
       <c r="C286" t="str">
-        <v>هریس</v>
+        <v>سرباز</v>
       </c>
       <c r="D286">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="287">
       <c r="A287">
-        <v>10300019</v>
+        <v>11100024</v>
       </c>
       <c r="B287" t="str">
-        <v>جلفا</v>
+        <v>گلشن</v>
       </c>
       <c r="C287" t="str">
-        <v>جلفا</v>
+        <v>گلشن</v>
       </c>
       <c r="D287">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="288">
       <c r="A288">
-        <v>10300020</v>
+        <v>11100025</v>
       </c>
       <c r="B288" t="str">
-        <v>ملکان</v>
+        <v>لاشار</v>
       </c>
       <c r="C288" t="str">
-        <v>ملکان</v>
+        <v>لاشار</v>
       </c>
       <c r="D288">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="289">
       <c r="A289">
-        <v>10300021</v>
+        <v>11100026</v>
       </c>
       <c r="B289" t="str">
-        <v>آذرشهر</v>
+        <v>زرآباد</v>
       </c>
       <c r="C289" t="str">
-        <v>آذرشهر</v>
+        <v>زرآباد</v>
       </c>
       <c r="D289">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="290">
       <c r="A290">
-        <v>10300022</v>
+        <v>11200001</v>
       </c>
       <c r="B290" t="str">
-        <v>اسکو</v>
+        <v>بانه</v>
       </c>
       <c r="C290" t="str">
-        <v>اسکو</v>
+        <v>بانه</v>
       </c>
       <c r="D290">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="291">
       <c r="A291">
-        <v>10300023</v>
+        <v>11200002</v>
       </c>
       <c r="B291" t="str">
-        <v>چاراویماق</v>
+        <v>بیجار</v>
       </c>
       <c r="C291" t="str">
-        <v>چاراویماق</v>
+        <v>بیجار</v>
       </c>
       <c r="D291">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="292">
       <c r="A292">
-        <v>10300024</v>
+        <v>11200003</v>
       </c>
       <c r="B292" t="str">
-        <v>ورزقان</v>
+        <v>سقز</v>
       </c>
       <c r="C292" t="str">
-        <v>ورزقان</v>
+        <v>سقز</v>
       </c>
       <c r="D292">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="293">
       <c r="A293">
-        <v>10300025</v>
+        <v>11200004</v>
       </c>
       <c r="B293" t="str">
-        <v>عجب شیر</v>
+        <v>سنندج</v>
       </c>
       <c r="C293" t="str">
-        <v>عجب-شیر</v>
+        <v>سنندج</v>
       </c>
       <c r="D293">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="294">
       <c r="A294">
-        <v>10300026</v>
+        <v>11200005</v>
       </c>
       <c r="B294" t="str">
-        <v>خداآفرین</v>
+        <v>قروه</v>
       </c>
       <c r="C294" t="str">
-        <v>خداآفرین</v>
+        <v>قروه</v>
       </c>
       <c r="D294">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="295">
       <c r="A295">
-        <v>10300027</v>
+        <v>11200006</v>
       </c>
       <c r="B295" t="str">
-        <v>هوراند</v>
+        <v>مریوان</v>
       </c>
       <c r="C295" t="str">
-        <v>هوراند</v>
+        <v>مریوان</v>
       </c>
       <c r="D295">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="296">
       <c r="A296">
-        <v>10300028</v>
+        <v>11200007</v>
       </c>
       <c r="B296" t="str">
-        <v>لیلان</v>
+        <v>دیواندره</v>
       </c>
       <c r="C296" t="str">
-        <v>لیلان</v>
+        <v>دیواندره</v>
       </c>
       <c r="D296">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="297">
       <c r="A297">
-        <v>10400010</v>
+        <v>11200008</v>
       </c>
       <c r="B297" t="str">
-        <v>بوکان</v>
+        <v>کامیاران</v>
       </c>
       <c r="C297" t="str">
-        <v>بوکان</v>
+        <v>کامیاران</v>
       </c>
       <c r="D297">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="298">
       <c r="A298">
-        <v>10400011</v>
+        <v>11200009</v>
       </c>
       <c r="B298" t="str">
-        <v>شاهین دژ</v>
+        <v>سروآباد</v>
       </c>
       <c r="C298" t="str">
-        <v>شاهین-دژ</v>
+        <v>سروآباد</v>
       </c>
       <c r="D298">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="299">
       <c r="A299">
-        <v>10400012</v>
+        <v>11200010</v>
       </c>
       <c r="B299" t="str">
-        <v>تکاب</v>
+        <v>دهگلان</v>
       </c>
       <c r="C299" t="str">
-        <v>تکاب</v>
+        <v>دهگلان</v>
       </c>
       <c r="D299">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="300">
       <c r="A300">
-        <v>10400013</v>
+        <v>11300001</v>
       </c>
       <c r="B300" t="str">
-        <v>اشنویه</v>
+        <v>تویسرکان</v>
       </c>
       <c r="C300" t="str">
-        <v>اشنویه</v>
+        <v>تویسرکان</v>
       </c>
       <c r="D300">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="301">
       <c r="A301">
-        <v>10400014</v>
+        <v>11300002</v>
       </c>
       <c r="B301" t="str">
-        <v>چالدران</v>
+        <v>ملایر</v>
       </c>
       <c r="C301" t="str">
-        <v>چالدران</v>
+        <v>ملایر</v>
       </c>
       <c r="D301">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="302">
       <c r="A302">
-        <v>10400015</v>
+        <v>11300003</v>
       </c>
       <c r="B302" t="str">
-        <v>پلدشت</v>
+        <v>نهاوند</v>
       </c>
       <c r="C302" t="str">
-        <v>پلدشت</v>
+        <v>نهاوند</v>
       </c>
       <c r="D302">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="303">
       <c r="A303">
-        <v>10400016</v>
+        <v>11300004</v>
       </c>
       <c r="B303" t="str">
-        <v>چایپاره</v>
+        <v>همدان</v>
       </c>
       <c r="C303" t="str">
-        <v>چایپاره</v>
+        <v>همدان</v>
       </c>
       <c r="D303">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="304">
       <c r="A304">
-        <v>10400017</v>
+        <v>11300005</v>
       </c>
       <c r="B304" t="str">
-        <v>شوط</v>
+        <v>کبودرآهنگ</v>
       </c>
       <c r="C304" t="str">
-        <v>شوط</v>
+        <v>کبودرآهنگ</v>
       </c>
       <c r="D304">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="305">
       <c r="A305">
-        <v>10400018</v>
+        <v>11300006</v>
       </c>
       <c r="B305" t="str">
-        <v>چهاربرج</v>
+        <v>اسدآباد</v>
       </c>
       <c r="C305" t="str">
-        <v>چهاربرج</v>
+        <v>اسدآباد</v>
       </c>
       <c r="D305">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="306">
       <c r="A306">
-        <v>10400019</v>
+        <v>11300007</v>
       </c>
       <c r="B306" t="str">
-        <v>باروق</v>
+        <v>بهار</v>
       </c>
       <c r="C306" t="str">
-        <v>باروق</v>
+        <v>بهار</v>
       </c>
       <c r="D306">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="307">
       <c r="A307">
-        <v>10400020</v>
+        <v>11300008</v>
       </c>
       <c r="B307" t="str">
-        <v>میرآباد</v>
+        <v>رزن</v>
       </c>
       <c r="C307" t="str">
-        <v>میرآباد</v>
+        <v>رزن</v>
       </c>
       <c r="D307">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="308">
       <c r="A308">
-        <v>10500010</v>
+        <v>11300009</v>
       </c>
       <c r="B308" t="str">
-        <v>صحنه</v>
+        <v>فامنین</v>
       </c>
       <c r="C308" t="str">
-        <v>صحنه</v>
+        <v>فامنین</v>
       </c>
       <c r="D308">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="309">
       <c r="A309">
-        <v>10500011</v>
+        <v>11300010</v>
       </c>
       <c r="B309" t="str">
-        <v>هرسین</v>
+        <v>درگزین</v>
       </c>
       <c r="C309" t="str">
-        <v>هرسین</v>
+        <v>درگزین</v>
       </c>
       <c r="D309">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="310">
       <c r="A310">
-        <v>10500012</v>
+        <v>11400001</v>
       </c>
       <c r="B310" t="str">
-        <v>ثلاث باباجانی</v>
+        <v>بروجن</v>
       </c>
       <c r="C310" t="str">
-        <v>ثلاث-باباجانی</v>
+        <v>بروجن</v>
       </c>
       <c r="D310">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="311">
       <c r="A311">
-        <v>10500013</v>
+        <v>11400002</v>
       </c>
       <c r="B311" t="str">
-        <v>دالاهو</v>
+        <v>شهرکرد</v>
       </c>
       <c r="C311" t="str">
-        <v>دالاهو</v>
+        <v>شهرکرد</v>
       </c>
       <c r="D311">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="312">
       <c r="A312">
-        <v>10500014</v>
+        <v>11400003</v>
       </c>
       <c r="B312" t="str">
-        <v>روانسر</v>
+        <v>فارسان</v>
       </c>
       <c r="C312" t="str">
-        <v>روانسر</v>
+        <v>فارسان</v>
       </c>
       <c r="D312">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="313">
       <c r="A313">
-        <v>10600010</v>
+        <v>11400004</v>
       </c>
       <c r="B313" t="str">
-        <v>رامهرمز</v>
+        <v>لردگان</v>
       </c>
       <c r="C313" t="str">
-        <v>رامهرمز</v>
+        <v>لردگان</v>
       </c>
       <c r="D313">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="314">
       <c r="A314">
-        <v>10600011</v>
+        <v>11400005</v>
       </c>
       <c r="B314" t="str">
-        <v>شادگان</v>
+        <v>اردل</v>
       </c>
       <c r="C314" t="str">
-        <v>شادگان</v>
+        <v>اردل</v>
       </c>
       <c r="D314">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="315">
       <c r="A315">
-        <v>10600012</v>
+        <v>11400006</v>
       </c>
       <c r="B315" t="str">
-        <v>شوشتر</v>
+        <v>کوهرنگ</v>
       </c>
       <c r="C315" t="str">
-        <v>شوشتر</v>
+        <v>کوهرنگ</v>
       </c>
       <c r="D315">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="316">
       <c r="A316">
-        <v>10600013</v>
+        <v>11400007</v>
       </c>
       <c r="B316" t="str">
-        <v>مسجدسلیمان</v>
+        <v>کیار</v>
       </c>
       <c r="C316" t="str">
-        <v>مسجدسلیمان</v>
+        <v>کیار</v>
       </c>
       <c r="D316">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="317">
       <c r="A317">
-        <v>10600014</v>
+        <v>11400008</v>
       </c>
       <c r="B317" t="str">
-        <v>شوش</v>
+        <v>سامان</v>
       </c>
       <c r="C317" t="str">
-        <v>شوش</v>
+        <v>سامان</v>
       </c>
       <c r="D317">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="318">
       <c r="A318">
-        <v>10600015</v>
+        <v>11400009</v>
       </c>
       <c r="B318" t="str">
-        <v>باغ ملک</v>
+        <v>بن</v>
       </c>
       <c r="C318" t="str">
-        <v>باغ-ملک</v>
+        <v>بن</v>
       </c>
       <c r="D318">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="319">
       <c r="A319">
-        <v>10600016</v>
+        <v>11400010</v>
       </c>
       <c r="B319" t="str">
-        <v>امیدیه</v>
+        <v>خانمیرزا</v>
       </c>
       <c r="C319" t="str">
-        <v>امیدیه</v>
+        <v>خانمیرزا</v>
       </c>
       <c r="D319">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="320">
       <c r="A320">
-        <v>10600017</v>
+        <v>11400011</v>
       </c>
       <c r="B320" t="str">
-        <v>لالی</v>
+        <v>فلارد</v>
       </c>
       <c r="C320" t="str">
-        <v>لالی</v>
+        <v>فلارد</v>
       </c>
       <c r="D320">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="321">
       <c r="A321">
-        <v>10600018</v>
+        <v>11400012</v>
       </c>
       <c r="B321" t="str">
-        <v>هندیجان</v>
+        <v>فرخ شهر</v>
       </c>
       <c r="C321" t="str">
-        <v>هندیجان</v>
+        <v>فرخ-شهر</v>
       </c>
       <c r="D321">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="322">
       <c r="A322">
-        <v>10600019</v>
+        <v>11500001</v>
       </c>
       <c r="B322" t="str">
-        <v>رامشیر</v>
+        <v>الیگودرز</v>
       </c>
       <c r="C322" t="str">
-        <v>رامشیر</v>
+        <v>الیگودرز</v>
       </c>
       <c r="D322">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="323">
       <c r="A323">
-        <v>10600020</v>
+        <v>11500002</v>
       </c>
       <c r="B323" t="str">
-        <v>گتوند</v>
+        <v>بروجرد</v>
       </c>
       <c r="C323" t="str">
-        <v>گتوند</v>
+        <v>بروجرد</v>
       </c>
       <c r="D323">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="324">
       <c r="A324">
-        <v>10600021</v>
+        <v>11500003</v>
       </c>
       <c r="B324" t="str">
-        <v>اندیکا</v>
+        <v>خرم آباد</v>
       </c>
       <c r="C324" t="str">
-        <v>اندیکا</v>
+        <v>خرم-آباد</v>
       </c>
       <c r="D324">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="325">
       <c r="A325">
-        <v>10600022</v>
+        <v>11500004</v>
       </c>
       <c r="B325" t="str">
-        <v>هفتکل</v>
+        <v>دلفان</v>
       </c>
       <c r="C325" t="str">
-        <v>هفتکل</v>
+        <v>دلفان</v>
       </c>
       <c r="D325">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="326">
       <c r="A326">
-        <v>10600023</v>
+        <v>11500005</v>
       </c>
       <c r="B326" t="str">
-        <v>هویزه</v>
+        <v>دورود</v>
       </c>
       <c r="C326" t="str">
-        <v>هویزه</v>
+        <v>دورود</v>
       </c>
       <c r="D326">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="327">
       <c r="A327">
-        <v>10600024</v>
+        <v>11500006</v>
       </c>
       <c r="B327" t="str">
-        <v>باوی</v>
+        <v>کوهدشت</v>
       </c>
       <c r="C327" t="str">
-        <v>باوی</v>
+        <v>کوهدشت</v>
       </c>
       <c r="D327">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="328">
       <c r="A328">
-        <v>10600025</v>
+        <v>11500007</v>
       </c>
       <c r="B328" t="str">
-        <v>حمیدیه</v>
+        <v>ازنا</v>
       </c>
       <c r="C328" t="str">
-        <v>حمیدیه</v>
+        <v>ازنا</v>
       </c>
       <c r="D328">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="329">
       <c r="A329">
-        <v>10600026</v>
+        <v>11500008</v>
       </c>
       <c r="B329" t="str">
-        <v>آغاجاری</v>
+        <v>پلدختر</v>
       </c>
       <c r="C329" t="str">
-        <v>آغاجاری</v>
+        <v>پلدختر</v>
       </c>
       <c r="D329">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="330">
       <c r="A330">
-        <v>10600027</v>
+        <v>11500009</v>
       </c>
       <c r="B330" t="str">
-        <v>کارون</v>
+        <v>سلسله</v>
       </c>
       <c r="C330" t="str">
-        <v>کارون</v>
+        <v>سلسله</v>
       </c>
       <c r="D330">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="331">
       <c r="A331">
-        <v>10600028</v>
+        <v>11500010</v>
       </c>
       <c r="B331" t="str">
-        <v>کرخه</v>
+        <v>چگنی</v>
       </c>
       <c r="C331" t="str">
-        <v>کرخه</v>
+        <v>چگنی</v>
       </c>
       <c r="D331">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="332">
       <c r="A332">
-        <v>10600029</v>
+        <v>11500011</v>
       </c>
       <c r="B332" t="str">
-        <v>دزپارت</v>
+        <v>رومشکان</v>
       </c>
       <c r="C332" t="str">
-        <v>دزپارت</v>
+        <v>رومشکان</v>
       </c>
       <c r="D332">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="333">
       <c r="A333">
-        <v>10600030</v>
+        <v>11500012</v>
       </c>
       <c r="B333" t="str">
-        <v>صیدون</v>
+        <v>معمولان</v>
       </c>
       <c r="C333" t="str">
-        <v>صیدون</v>
+        <v>معمولان</v>
       </c>
       <c r="D333">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="334">
       <c r="A334">
-        <v>10700010</v>
+        <v>11600001</v>
       </c>
       <c r="B334" t="str">
-        <v>کازرون</v>
+        <v>ایلام</v>
       </c>
       <c r="C334" t="str">
-        <v>کازرون</v>
+        <v>ایلام</v>
       </c>
       <c r="D334">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="335">
       <c r="A335">
-        <v>10700011</v>
+        <v>11600002</v>
       </c>
       <c r="B335" t="str">
-        <v>لارستان</v>
+        <v>دره شهر</v>
       </c>
       <c r="C335" t="str">
-        <v>لارستان</v>
+        <v>دره-شهر</v>
       </c>
       <c r="D335">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="336">
       <c r="A336">
-        <v>10700012</v>
+        <v>11600003</v>
       </c>
       <c r="B336" t="str">
-        <v>مرودشت</v>
+        <v>دهلران</v>
       </c>
       <c r="C336" t="str">
-        <v>مرودشت</v>
+        <v>دهلران</v>
       </c>
       <c r="D336">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="337">
       <c r="A337">
-        <v>10700013</v>
+        <v>11600004</v>
       </c>
       <c r="B337" t="str">
-        <v>ممسنی</v>
+        <v>چرداول</v>
       </c>
       <c r="C337" t="str">
-        <v>ممسنی</v>
+        <v>چرداول</v>
       </c>
       <c r="D337">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="338">
       <c r="A338">
-        <v>10700014</v>
+        <v>11600005</v>
       </c>
       <c r="B338" t="str">
-        <v>نی ریز</v>
+        <v>مهران</v>
       </c>
       <c r="C338" t="str">
-        <v>نی-ریز</v>
+        <v>مهران</v>
       </c>
       <c r="D338">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="339">
       <c r="A339">
-        <v>10700015</v>
+        <v>11600006</v>
       </c>
       <c r="B339" t="str">
-        <v>لامرد</v>
+        <v>آبدانان</v>
       </c>
       <c r="C339" t="str">
-        <v>لامرد</v>
+        <v>آبدانان</v>
       </c>
       <c r="D339">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="340">
       <c r="A340">
-        <v>10700016</v>
+        <v>11600007</v>
       </c>
       <c r="B340" t="str">
-        <v>بوانات</v>
+        <v>ایوان</v>
       </c>
       <c r="C340" t="str">
-        <v>بوانات</v>
+        <v>ایوان</v>
       </c>
       <c r="D340">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="341">
       <c r="A341">
-        <v>10700017</v>
+        <v>11600008</v>
       </c>
       <c r="B341" t="str">
-        <v>ارسنجان</v>
+        <v>ملکشاهی</v>
       </c>
       <c r="C341" t="str">
-        <v>ارسنجان</v>
+        <v>ملکشاهی</v>
       </c>
       <c r="D341">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="342">
       <c r="A342">
-        <v>10700018</v>
+        <v>11600009</v>
       </c>
       <c r="B342" t="str">
-        <v>خرم بید</v>
+        <v>سیروان</v>
       </c>
       <c r="C342" t="str">
-        <v>خرم-بید</v>
+        <v>سیروان</v>
       </c>
       <c r="D342">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="343">
       <c r="A343">
-        <v>10700019</v>
+        <v>11600010</v>
       </c>
       <c r="B343" t="str">
-        <v>زرین دشت</v>
+        <v>بدره</v>
       </c>
       <c r="C343" t="str">
-        <v>زرین-دشت</v>
+        <v>بدره</v>
       </c>
       <c r="D343">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="344">
       <c r="A344">
-        <v>10700020</v>
+        <v>11600011</v>
       </c>
       <c r="B344" t="str">
-        <v>قیروکارزین</v>
+        <v>هلیلان</v>
       </c>
       <c r="C344" t="str">
-        <v>قیروکارزین</v>
+        <v>هلیلان</v>
       </c>
       <c r="D344">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="345">
       <c r="A345">
-        <v>10700021</v>
+        <v>11600012</v>
       </c>
       <c r="B345" t="str">
-        <v>مهر</v>
+        <v>چوار</v>
       </c>
       <c r="C345" t="str">
-        <v>مهر</v>
+        <v>چوار</v>
       </c>
       <c r="D345">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="346">
       <c r="A346">
-        <v>10700022</v>
+        <v>11700001</v>
       </c>
       <c r="B346" t="str">
-        <v>فراشبند</v>
+        <v>بویراحمد</v>
       </c>
       <c r="C346" t="str">
-        <v>فراشبند</v>
+        <v>بویراحمد</v>
       </c>
       <c r="D346">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="347">
       <c r="A347">
-        <v>10700023</v>
+        <v>11700002</v>
       </c>
       <c r="B347" t="str">
-        <v>پاسارگاد</v>
+        <v>کهگیلویه</v>
       </c>
       <c r="C347" t="str">
-        <v>پاسارگاد</v>
+        <v>کهگیلویه</v>
       </c>
       <c r="D347">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="348">
       <c r="A348">
-        <v>10700024</v>
+        <v>11700003</v>
       </c>
       <c r="B348" t="str">
-        <v>خنج</v>
+        <v>گچساران</v>
       </c>
       <c r="C348" t="str">
-        <v>خنج</v>
+        <v>گچساران</v>
       </c>
       <c r="D348">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="349">
       <c r="A349">
-        <v>10700025</v>
+        <v>11700004</v>
       </c>
       <c r="B349" t="str">
-        <v>سروستان</v>
+        <v>دنا</v>
       </c>
       <c r="C349" t="str">
-        <v>سروستان</v>
+        <v>دنا</v>
       </c>
       <c r="D349">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="350">
       <c r="A350">
-        <v>10700026</v>
+        <v>11700005</v>
       </c>
       <c r="B350" t="str">
-        <v>رستم</v>
+        <v>بهمیی</v>
       </c>
       <c r="C350" t="str">
-        <v>رستم</v>
+        <v>بهمیی</v>
       </c>
       <c r="D350">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="351">
       <c r="A351">
-        <v>10700027</v>
+        <v>11700006</v>
       </c>
       <c r="B351" t="str">
-        <v>گراش</v>
+        <v>چرام</v>
       </c>
       <c r="C351" t="str">
-        <v>گراش</v>
+        <v>چرام</v>
       </c>
       <c r="D351">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="352">
       <c r="A352">
-        <v>10700028</v>
+        <v>11700007</v>
       </c>
       <c r="B352" t="str">
-        <v>کوار</v>
+        <v>باشت</v>
       </c>
       <c r="C352" t="str">
-        <v>کوار</v>
+        <v>باشت</v>
       </c>
       <c r="D352">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="353">
       <c r="A353">
-        <v>10700029</v>
+        <v>11700008</v>
       </c>
       <c r="B353" t="str">
-        <v>خرامه</v>
+        <v>لنده</v>
       </c>
       <c r="C353" t="str">
-        <v>خرامه</v>
+        <v>لنده</v>
       </c>
       <c r="D353">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="354">
       <c r="A354">
-        <v>10700030</v>
+        <v>11700009</v>
       </c>
       <c r="B354" t="str">
-        <v>زرقان</v>
+        <v>مارگون</v>
       </c>
       <c r="C354" t="str">
-        <v>زرقان</v>
+        <v>مارگون</v>
       </c>
       <c r="D354">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="355">
       <c r="A355">
-        <v>10700031</v>
+        <v>11800001</v>
       </c>
       <c r="B355" t="str">
-        <v>بیضا</v>
+        <v>بوشهر</v>
       </c>
       <c r="C355" t="str">
-        <v>بیضا</v>
+        <v>بوشهر</v>
       </c>
       <c r="D355">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="356">
       <c r="A356">
-        <v>10700032</v>
+        <v>11800002</v>
       </c>
       <c r="B356" t="str">
-        <v>سرچهان</v>
+        <v>تنگستان</v>
       </c>
       <c r="C356" t="str">
-        <v>سرچهان</v>
+        <v>تنگستان</v>
       </c>
       <c r="D356">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="357">
       <c r="A357">
-        <v>10700033</v>
+        <v>11800003</v>
       </c>
       <c r="B357" t="str">
-        <v>کوه چنار</v>
+        <v>دشتستان</v>
       </c>
       <c r="C357" t="str">
-        <v>کوه-چنار</v>
+        <v>دشتستان</v>
       </c>
       <c r="D357">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="358">
       <c r="A358">
-        <v>10700034</v>
+        <v>11800004</v>
       </c>
       <c r="B358" t="str">
-        <v>خفر</v>
+        <v>دشتی</v>
       </c>
       <c r="C358" t="str">
-        <v>خفر</v>
+        <v>دشتی</v>
       </c>
       <c r="D358">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="359">
       <c r="A359">
-        <v>10700035</v>
+        <v>11800005</v>
       </c>
       <c r="B359" t="str">
-        <v>بختگان</v>
+        <v>دیر</v>
       </c>
       <c r="C359" t="str">
-        <v>بختگان</v>
+        <v>دیر</v>
       </c>
       <c r="D359">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="360">
       <c r="A360">
-        <v>10700036</v>
+        <v>11800006</v>
       </c>
       <c r="B360" t="str">
-        <v>اوز</v>
+        <v>کنگان</v>
       </c>
       <c r="C360" t="str">
-        <v>اوز</v>
+        <v>کنگان</v>
       </c>
       <c r="D360">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="361">
       <c r="A361">
-        <v>10700037</v>
+        <v>11800007</v>
       </c>
       <c r="B361" t="str">
-        <v>جویم</v>
+        <v>گناوه</v>
       </c>
       <c r="C361" t="str">
-        <v>جویم</v>
+        <v>گناوه</v>
       </c>
       <c r="D361">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="362">
       <c r="A362">
-        <v>10800010</v>
+        <v>11800008</v>
       </c>
       <c r="B362" t="str">
-        <v>بردسیر</v>
+        <v>دیلم</v>
       </c>
       <c r="C362" t="str">
-        <v>بردسیر</v>
+        <v>دیلم</v>
       </c>
       <c r="D362">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="363">
       <c r="A363">
-        <v>10800011</v>
+        <v>11800009</v>
       </c>
       <c r="B363" t="str">
-        <v>راور</v>
+        <v>جم</v>
       </c>
       <c r="C363" t="str">
-        <v>راور</v>
+        <v>جم</v>
       </c>
       <c r="D363">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="364">
       <c r="A364">
-        <v>10800012</v>
+        <v>11800010</v>
       </c>
       <c r="B364" t="str">
-        <v>عنبرآباد</v>
+        <v>عسلویه</v>
       </c>
       <c r="C364" t="str">
-        <v>عنبرآباد</v>
+        <v>عسلویه</v>
       </c>
       <c r="D364">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="365">
       <c r="A365">
-        <v>10800013</v>
+        <v>11900001</v>
       </c>
       <c r="B365" t="str">
-        <v>منوجان</v>
+        <v>ابهر</v>
       </c>
       <c r="C365" t="str">
-        <v>منوجان</v>
+        <v>ابهر</v>
       </c>
       <c r="D365">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="366">
       <c r="A366">
-        <v>10800014</v>
+        <v>11900003</v>
       </c>
       <c r="B366" t="str">
-        <v>کوهبنان</v>
+        <v>خدابنده</v>
       </c>
       <c r="C366" t="str">
-        <v>کوهبنان</v>
+        <v>خدابنده</v>
       </c>
       <c r="D366">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="367">
       <c r="A367">
-        <v>10800015</v>
+        <v>11900004</v>
       </c>
       <c r="B367" t="str">
-        <v>رودبارجنوب</v>
+        <v>زنجان</v>
       </c>
       <c r="C367" t="str">
-        <v>رودبارجنوب</v>
+        <v>زنجان</v>
       </c>
       <c r="D367">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="368">
       <c r="A368">
-        <v>10800016</v>
+        <v>11900006</v>
       </c>
       <c r="B368" t="str">
-        <v>قلعه گنج</v>
+        <v>ایجرود</v>
       </c>
       <c r="C368" t="str">
-        <v>قلعه-گنج</v>
+        <v>ایجرود</v>
       </c>
       <c r="D368">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="369">
       <c r="A369">
-        <v>10800017</v>
+        <v>11900007</v>
       </c>
       <c r="B369" t="str">
-        <v>ریگان</v>
+        <v>خرمدره</v>
       </c>
       <c r="C369" t="str">
-        <v>ریگان</v>
+        <v>خرمدره</v>
       </c>
       <c r="D369">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="370">
       <c r="A370">
-        <v>10800018</v>
+        <v>11900008</v>
       </c>
       <c r="B370" t="str">
-        <v>رابر</v>
+        <v>طارم</v>
       </c>
       <c r="C370" t="str">
-        <v>رابر</v>
+        <v>طارم</v>
       </c>
       <c r="D370">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="371">
       <c r="A371">
-        <v>10800019</v>
+        <v>11900009</v>
       </c>
       <c r="B371" t="str">
-        <v>فهرج</v>
+        <v>ماهنشان</v>
       </c>
       <c r="C371" t="str">
-        <v>فهرج</v>
+        <v>ماهنشان</v>
       </c>
       <c r="D371">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="372">
       <c r="A372">
-        <v>10800020</v>
+        <v>11900010</v>
       </c>
       <c r="B372" t="str">
-        <v>انار</v>
+        <v>سلطانیه</v>
       </c>
       <c r="C372" t="str">
-        <v>انار</v>
+        <v>سلطانیه</v>
       </c>
       <c r="D372">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="373">
       <c r="A373">
-        <v>10800021</v>
+        <v>12000001</v>
       </c>
       <c r="B373" t="str">
-        <v>نرماشیر</v>
+        <v>دامغان</v>
       </c>
       <c r="C373" t="str">
-        <v>نرماشیر</v>
+        <v>دامغان</v>
       </c>
       <c r="D373">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="374">
       <c r="A374">
-        <v>10800022</v>
+        <v>12000002</v>
       </c>
       <c r="B374" t="str">
-        <v>فاریاب</v>
+        <v>سمنان</v>
       </c>
       <c r="C374" t="str">
-        <v>فاریاب</v>
+        <v>سمنان</v>
       </c>
       <c r="D374">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="375">
       <c r="A375">
-        <v>10800023</v>
+        <v>12000003</v>
       </c>
       <c r="B375" t="str">
-        <v>ارزوییه</v>
+        <v>شاهرود</v>
       </c>
       <c r="C375" t="str">
-        <v>ارزوییه</v>
+        <v>شاهرود</v>
       </c>
       <c r="D375">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="376">
       <c r="A376">
-        <v>10800024</v>
+        <v>12000004</v>
       </c>
       <c r="B376" t="str">
-        <v>گنبکی</v>
+        <v>گرمسار</v>
       </c>
       <c r="C376" t="str">
-        <v>گنبکی</v>
+        <v>گرمسار</v>
       </c>
       <c r="D376">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="377">
       <c r="A377">
-        <v>10800025</v>
+        <v>12000005</v>
       </c>
       <c r="B377" t="str">
-        <v>جازموریان</v>
+        <v>مهدی شهر</v>
       </c>
       <c r="C377" t="str">
-        <v>جازموریان</v>
+        <v>مهدی-شهر</v>
       </c>
       <c r="D377">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="378">
       <c r="A378">
-        <v>10900013</v>
+        <v>12000006</v>
       </c>
       <c r="B378" t="str">
-        <v>قوچان</v>
+        <v>آرادان</v>
       </c>
       <c r="C378" t="str">
-        <v>قوچان</v>
+        <v>آرادان</v>
       </c>
       <c r="D378">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="379">
       <c r="A379">
-        <v>10900014</v>
+        <v>12000007</v>
       </c>
       <c r="B379" t="str">
-        <v>کاشمر</v>
+        <v>میامی</v>
       </c>
       <c r="C379" t="str">
-        <v>کاشمر</v>
+        <v>میامی</v>
       </c>
       <c r="D379">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="380">
       <c r="A380">
-        <v>10900015</v>
+        <v>12000008</v>
       </c>
       <c r="B380" t="str">
-        <v>گناباد</v>
+        <v>سرخه</v>
       </c>
       <c r="C380" t="str">
-        <v>گناباد</v>
+        <v>سرخه</v>
       </c>
       <c r="D380">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="381">
       <c r="A381">
-        <v>10900016</v>
+        <v>12100001</v>
       </c>
       <c r="B381" t="str">
-        <v>مشهد</v>
+        <v>اردکان</v>
       </c>
       <c r="C381" t="str">
-        <v>مشهد</v>
+        <v>اردکان</v>
       </c>
       <c r="D381">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="382">
       <c r="A382">
-        <v>10900017</v>
+        <v>12100002</v>
       </c>
       <c r="B382" t="str">
-        <v>نیشابور</v>
+        <v>بافق</v>
       </c>
       <c r="C382" t="str">
-        <v>نیشابور</v>
+        <v>بافق</v>
       </c>
       <c r="D382">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="383">
       <c r="A383">
-        <v>10900018</v>
+        <v>12100003</v>
       </c>
       <c r="B383" t="str">
-        <v>چناران</v>
+        <v>تفت</v>
       </c>
       <c r="C383" t="str">
-        <v>چناران</v>
+        <v>تفت</v>
       </c>
       <c r="D383">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="384">
       <c r="A384">
-        <v>10900019</v>
+        <v>12100004</v>
       </c>
       <c r="B384" t="str">
-        <v>خواف</v>
+        <v>مهریز</v>
       </c>
       <c r="C384" t="str">
-        <v>خواف</v>
+        <v>مهریز</v>
       </c>
       <c r="D384">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="385">
       <c r="A385">
-        <v>10900020</v>
+        <v>12100005</v>
       </c>
       <c r="B385" t="str">
-        <v>سرخس</v>
+        <v>یزد</v>
       </c>
       <c r="C385" t="str">
-        <v>سرخس</v>
+        <v>یزد</v>
       </c>
       <c r="D385">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="386">
       <c r="A386">
-        <v>10900022</v>
+        <v>12100006</v>
       </c>
       <c r="B386" t="str">
-        <v>فریمان</v>
+        <v>میبد</v>
       </c>
       <c r="C386" t="str">
-        <v>فریمان</v>
+        <v>میبد</v>
       </c>
       <c r="D386">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="387">
       <c r="A387">
-        <v>10900023</v>
+        <v>12100007</v>
       </c>
       <c r="B387" t="str">
-        <v>بردسکن</v>
+        <v>ابرکوه</v>
       </c>
       <c r="C387" t="str">
-        <v>بردسکن</v>
+        <v>ابرکوه</v>
       </c>
       <c r="D387">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="388">
       <c r="A388">
-        <v>10900027</v>
+        <v>12100008</v>
       </c>
       <c r="B388" t="str">
-        <v>رشتخوار</v>
+        <v>اشکذر</v>
       </c>
       <c r="C388" t="str">
-        <v>رشتخوار</v>
+        <v>اشکذر</v>
       </c>
       <c r="D388">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="389">
       <c r="A389">
-        <v>10900028</v>
+        <v>12100009</v>
       </c>
       <c r="B389" t="str">
-        <v>کلات</v>
+        <v>خاتم</v>
       </c>
       <c r="C389" t="str">
-        <v>کلات</v>
+        <v>خاتم</v>
       </c>
       <c r="D389">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="390">
       <c r="A390">
-        <v>10900029</v>
+        <v>12100011</v>
       </c>
       <c r="B390" t="str">
-        <v>خلیل آباد</v>
+        <v>بهاباد</v>
       </c>
       <c r="C390" t="str">
-        <v>خلیل-آباد</v>
+        <v>بهاباد</v>
       </c>
       <c r="D390">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="391">
       <c r="A391">
-        <v>10900030</v>
+        <v>12100012</v>
       </c>
       <c r="B391" t="str">
-        <v>مه ولات</v>
+        <v>مروست</v>
       </c>
       <c r="C391" t="str">
-        <v>مه-ولات</v>
+        <v>مروست</v>
       </c>
       <c r="D391">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="392">
       <c r="A392">
-        <v>10900031</v>
+        <v>12100013</v>
       </c>
       <c r="B392" t="str">
-        <v>بجستان</v>
+        <v>زارچ</v>
       </c>
       <c r="C392" t="str">
-        <v>بجستان</v>
+        <v>زارچ</v>
       </c>
       <c r="D392">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="393">
       <c r="A393">
-        <v>10900032</v>
+        <v>12200001</v>
       </c>
       <c r="B393" t="str">
-        <v>طرقبه شاندیز</v>
+        <v>ابوموسی</v>
       </c>
       <c r="C393" t="str">
-        <v>طرقبه-شاندیز</v>
+        <v>ابوموسی</v>
       </c>
       <c r="D393">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="394">
       <c r="A394">
-        <v>10900033</v>
+        <v>12200002</v>
       </c>
       <c r="B394" t="str">
-        <v>فیروزه</v>
+        <v>بندر عباس</v>
       </c>
       <c r="C394" t="str">
-        <v>فیروزه</v>
+        <v>بندر-عباس</v>
       </c>
       <c r="D394">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="395">
       <c r="A395">
-        <v>10900034</v>
+        <v>12200003</v>
       </c>
       <c r="B395" t="str">
-        <v>جغتای</v>
+        <v>بندر لنگه</v>
       </c>
       <c r="C395" t="str">
-        <v>جغتای</v>
+        <v>بندر-لنگه</v>
       </c>
       <c r="D395">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="396">
       <c r="A396">
-        <v>10900035</v>
+        <v>12200004</v>
       </c>
       <c r="B396" t="str">
-        <v>زاوه</v>
+        <v>قشم</v>
       </c>
       <c r="C396" t="str">
-        <v>زاوه</v>
+        <v>قشم</v>
       </c>
       <c r="D396">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="397">
       <c r="A397">
-        <v>10900036</v>
+        <v>12200005</v>
       </c>
       <c r="B397" t="str">
-        <v>جوین</v>
+        <v>میناب</v>
       </c>
       <c r="C397" t="str">
-        <v>جوین</v>
+        <v>میناب</v>
       </c>
       <c r="D397">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="398">
       <c r="A398">
-        <v>10900037</v>
+        <v>12200006</v>
       </c>
       <c r="B398" t="str">
-        <v>باخرز</v>
+        <v>جاسک</v>
       </c>
       <c r="C398" t="str">
-        <v>باخرز</v>
+        <v>جاسک</v>
       </c>
       <c r="D398">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="399">
       <c r="A399">
-        <v>10900038</v>
+        <v>12200007</v>
       </c>
       <c r="B399" t="str">
-        <v>خوشاب</v>
+        <v>رودان</v>
       </c>
       <c r="C399" t="str">
-        <v>خوشاب</v>
+        <v>رودان</v>
       </c>
       <c r="D399">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="400">
       <c r="A400">
-        <v>10900039</v>
+        <v>12200008</v>
       </c>
       <c r="B400" t="str">
-        <v>داورزن</v>
+        <v>حاجی آباد</v>
       </c>
       <c r="C400" t="str">
-        <v>داورزن</v>
+        <v>حاجی-آباد</v>
       </c>
       <c r="D400">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="401">
       <c r="A401">
-        <v>10900040</v>
+        <v>12200009</v>
       </c>
       <c r="B401" t="str">
-        <v>صالح آباد</v>
+        <v>بستک</v>
       </c>
       <c r="C401" t="str">
-        <v>صالح-آباد</v>
+        <v>بستک</v>
       </c>
       <c r="D401">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="402">
       <c r="A402">
-        <v>10900041</v>
+        <v>12200010</v>
       </c>
       <c r="B402" t="str">
-        <v>کوهسرخ</v>
+        <v>خمیر</v>
       </c>
       <c r="C402" t="str">
-        <v>کوهسرخ</v>
+        <v>خمیر</v>
       </c>
       <c r="D402">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="403">
       <c r="A403">
-        <v>10900042</v>
+        <v>12200011</v>
       </c>
       <c r="B403" t="str">
-        <v>زبرخان</v>
+        <v>پارسیان</v>
       </c>
       <c r="C403" t="str">
-        <v>زبرخان</v>
+        <v>پارسیان</v>
       </c>
       <c r="D403">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="404">
       <c r="A404">
-        <v>10900043</v>
+        <v>12200012</v>
       </c>
       <c r="B404" t="str">
-        <v>ششتمد</v>
+        <v>سیریک</v>
       </c>
       <c r="C404" t="str">
-        <v>ششتمد</v>
+        <v>سیریک</v>
       </c>
       <c r="D404">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="405">
       <c r="A405">
-        <v>10900044</v>
+        <v>12200013</v>
       </c>
       <c r="B405" t="str">
-        <v>گلبهار</v>
+        <v>بشاگرد</v>
       </c>
       <c r="C405" t="str">
-        <v>گلبهار</v>
+        <v>بشاگرد</v>
       </c>
       <c r="D405">
-        <v>109</v>
+        <v>122</v>
       </c>
     </row>
     <row r="406">
       <c r="A406">
-        <v>10900045</v>
+        <v>12300001</v>
       </c>
       <c r="B406" t="str">
-        <v>میان جلگه</v>
+        <v>تهران</v>
       </c>
       <c r="C406" t="str">
-        <v>میان-جلگه</v>
+        <v>تهران</v>
       </c>
       <c r="D406">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="407">
       <c r="A407">
-        <v>11000010</v>
+        <v>12300002</v>
       </c>
       <c r="B407" t="str">
-        <v>کاشان</v>
+        <v>دماوند</v>
       </c>
       <c r="C407" t="str">
-        <v>کاشان</v>
+        <v>دماوند</v>
       </c>
       <c r="D407">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="408">
       <c r="A408">
-        <v>11000011</v>
+        <v>12300003</v>
       </c>
       <c r="B408" t="str">
-        <v>گلپایگان</v>
+        <v>ری</v>
       </c>
       <c r="C408" t="str">
-        <v>گلپایگان</v>
+        <v>ری</v>
       </c>
       <c r="D408">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="409">
       <c r="A409">
-        <v>11000012</v>
+        <v>12300004</v>
       </c>
       <c r="B409" t="str">
-        <v>لنجان</v>
+        <v>شمیرانات</v>
       </c>
       <c r="C409" t="str">
-        <v>لنجان</v>
+        <v>شمیرانات</v>
       </c>
       <c r="D409">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="410">
       <c r="A410">
-        <v>11000013</v>
+        <v>12300006</v>
       </c>
       <c r="B410" t="str">
-        <v>نایین</v>
+        <v>ورامین</v>
       </c>
       <c r="C410" t="str">
-        <v>نایین</v>
+        <v>ورامین</v>
       </c>
       <c r="D410">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="411">
       <c r="A411">
-        <v>11000014</v>
+        <v>12300009</v>
       </c>
       <c r="B411" t="str">
-        <v>نجف آباد</v>
+        <v>شهریار</v>
       </c>
       <c r="C411" t="str">
-        <v>نجف-آباد</v>
+        <v>شهریار</v>
       </c>
       <c r="D411">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="412">
       <c r="A412">
-        <v>11000015</v>
+        <v>12300010</v>
       </c>
       <c r="B412" t="str">
-        <v>نطنز</v>
+        <v>اسلامشهر</v>
       </c>
       <c r="C412" t="str">
-        <v>نطنز</v>
+        <v>اسلامشهر</v>
       </c>
       <c r="D412">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="413">
       <c r="A413">
-        <v>11000016</v>
+        <v>12300012</v>
       </c>
       <c r="B413" t="str">
-        <v>شاهین شهرو میمه</v>
+        <v>رباط‌کریم</v>
       </c>
       <c r="C413" t="str">
-        <v>شاهین-شهرو-میمه</v>
+        <v>رباطکریم</v>
       </c>
       <c r="D413">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="414">
       <c r="A414">
-        <v>11000017</v>
+        <v>12300013</v>
       </c>
       <c r="B414" t="str">
-        <v>مبارکه</v>
+        <v>پاکدشت</v>
       </c>
       <c r="C414" t="str">
-        <v>مبارکه</v>
+        <v>پاکدشت</v>
       </c>
       <c r="D414">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="415">
       <c r="A415">
-        <v>11000018</v>
+        <v>12300014</v>
       </c>
       <c r="B415" t="str">
-        <v>آران و بیدگل</v>
+        <v>فیروزکوه</v>
       </c>
       <c r="C415" t="str">
-        <v>آران-و-بیدگل</v>
+        <v>فیروزکوه</v>
       </c>
       <c r="D415">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="416">
       <c r="A416">
-        <v>11000019</v>
+        <v>12300016</v>
       </c>
       <c r="B416" t="str">
-        <v>تیران وکرون</v>
+        <v>قدس</v>
       </c>
       <c r="C416" t="str">
-        <v>تیران-وکرون</v>
+        <v>قدس</v>
       </c>
       <c r="D416">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="417">
       <c r="A417">
-        <v>11000020</v>
+        <v>12300017</v>
       </c>
       <c r="B417" t="str">
-        <v>چادگان</v>
+        <v>ملارد</v>
       </c>
       <c r="C417" t="str">
-        <v>چادگان</v>
+        <v>ملارد</v>
       </c>
       <c r="D417">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="418">
       <c r="A418">
-        <v>11000021</v>
+        <v>12300018</v>
       </c>
       <c r="B418" t="str">
-        <v>دهاقان</v>
+        <v>پیشوا</v>
       </c>
       <c r="C418" t="str">
-        <v>دهاقان</v>
+        <v>پیشوا</v>
       </c>
       <c r="D418">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="419">
       <c r="A419">
-        <v>11000022</v>
+        <v>12300019</v>
       </c>
       <c r="B419" t="str">
-        <v>برخوار</v>
+        <v>بهارستان</v>
       </c>
       <c r="C419" t="str">
-        <v>برخوار</v>
+        <v>بهارستان</v>
       </c>
       <c r="D419">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="420">
       <c r="A420">
-        <v>11000023</v>
+        <v>12300020</v>
       </c>
       <c r="B420" t="str">
-        <v>خور و بیابانک</v>
+        <v>پردیس</v>
       </c>
       <c r="C420" t="str">
-        <v>خور-و-بیابانک</v>
+        <v>پردیس</v>
       </c>
       <c r="D420">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="421">
       <c r="A421">
-        <v>11000024</v>
+        <v>12300021</v>
       </c>
       <c r="B421" t="str">
-        <v>بویین و میاندشت</v>
+        <v>قرچک</v>
       </c>
       <c r="C421" t="str">
-        <v>بویین-و-میاندشت</v>
+        <v>قرچک</v>
       </c>
       <c r="D421">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="422">
       <c r="A422">
-        <v>11000025</v>
+        <v>12400001</v>
       </c>
       <c r="B422" t="str">
-        <v>کوهپایه</v>
+        <v>اردبیل</v>
       </c>
       <c r="C422" t="str">
-        <v>کوهپایه</v>
+        <v>اردبیل</v>
       </c>
       <c r="D422">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="423">
       <c r="A423">
-        <v>11000026</v>
+        <v>12400002</v>
       </c>
       <c r="B423" t="str">
-        <v>جرقویه</v>
+        <v>بیله سوار</v>
       </c>
       <c r="C423" t="str">
-        <v>جرقویه</v>
+        <v>بیله-سوار</v>
       </c>
       <c r="D423">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="424">
       <c r="A424">
-        <v>11000027</v>
+        <v>12400003</v>
       </c>
       <c r="B424" t="str">
-        <v>ورزنه</v>
+        <v>خلخال</v>
       </c>
       <c r="C424" t="str">
-        <v>ورزنه</v>
+        <v>خلخال</v>
       </c>
       <c r="D424">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="425">
       <c r="A425">
-        <v>11000028</v>
+        <v>12400004</v>
       </c>
       <c r="B425" t="str">
-        <v>هرند</v>
+        <v>مشگین شهر</v>
       </c>
       <c r="C425" t="str">
-        <v>هرند</v>
+        <v>مشگین-شهر</v>
       </c>
       <c r="D425">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="426">
       <c r="A426">
-        <v>11100010</v>
+        <v>12400005</v>
       </c>
       <c r="B426" t="str">
-        <v>زهک</v>
+        <v>گرمی</v>
       </c>
       <c r="C426" t="str">
-        <v>زهک</v>
+        <v>گرمی</v>
       </c>
       <c r="D426">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="427">
       <c r="A427">
-        <v>11100011</v>
+        <v>12400006</v>
       </c>
       <c r="B427" t="str">
-        <v>هیرمند</v>
+        <v>پارس آباد</v>
       </c>
       <c r="C427" t="str">
-        <v>هیرمند</v>
+        <v>پارس-آباد</v>
       </c>
       <c r="D427">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="428">
       <c r="A428">
-        <v>11100012</v>
+        <v>12400007</v>
       </c>
       <c r="B428" t="str">
-        <v>دلگان</v>
+        <v>کوثر</v>
       </c>
       <c r="C428" t="str">
-        <v>دلگان</v>
+        <v>کوثر</v>
       </c>
       <c r="D428">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="429">
       <c r="A429">
-        <v>11100013</v>
+        <v>12400008</v>
       </c>
       <c r="B429" t="str">
-        <v>مهرستان</v>
+        <v>نمین</v>
       </c>
       <c r="C429" t="str">
-        <v>مهرستان</v>
+        <v>نمین</v>
       </c>
       <c r="D429">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="430">
       <c r="A430">
-        <v>11100014</v>
+        <v>12400009</v>
       </c>
       <c r="B430" t="str">
-        <v>سیب و سوران</v>
+        <v>نیر</v>
       </c>
       <c r="C430" t="str">
-        <v>سیب-و-سوران</v>
+        <v>نیر</v>
       </c>
       <c r="D430">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="431">
       <c r="A431">
-        <v>11100015</v>
+        <v>12400010</v>
       </c>
       <c r="B431" t="str">
-        <v>نیمروز</v>
+        <v>سرعین</v>
       </c>
       <c r="C431" t="str">
-        <v>نیمروز</v>
+        <v>سرعین</v>
       </c>
       <c r="D431">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="432">
       <c r="A432">
-        <v>11100016</v>
+        <v>12400011</v>
       </c>
       <c r="B432" t="str">
-        <v>هامون</v>
+        <v>اصلاندوز</v>
       </c>
       <c r="C432" t="str">
-        <v>هامون</v>
+        <v>اصلاندوز</v>
       </c>
       <c r="D432">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="433">
       <c r="A433">
-        <v>11100017</v>
+        <v>12400012</v>
       </c>
       <c r="B433" t="str">
-        <v>میرجاوه</v>
+        <v>انگوت</v>
       </c>
       <c r="C433" t="str">
-        <v>میرجاوه</v>
+        <v>انگوت</v>
       </c>
       <c r="D433">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="434">
       <c r="A434">
-        <v>11100018</v>
+        <v>12500001</v>
       </c>
       <c r="B434" t="str">
-        <v>قصرقند</v>
+        <v>قم</v>
       </c>
       <c r="C434" t="str">
-        <v>قصرقند</v>
+        <v>قم</v>
       </c>
       <c r="D434">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="435">
       <c r="A435">
-        <v>11100019</v>
+        <v>12500002</v>
       </c>
       <c r="B435" t="str">
-        <v>فنوج</v>
+        <v>جعفرآباد</v>
       </c>
       <c r="C435" t="str">
-        <v>فنوج</v>
+        <v>جعفرآباد</v>
       </c>
       <c r="D435">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="436">
       <c r="A436">
-        <v>11100020</v>
+        <v>12500003</v>
       </c>
       <c r="B436" t="str">
-        <v>بمپور</v>
+        <v>کهک</v>
       </c>
       <c r="C436" t="str">
-        <v>بمپور</v>
+        <v>کهک</v>
       </c>
       <c r="D436">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="437">
       <c r="A437">
-        <v>11100021</v>
+        <v>12600001</v>
       </c>
       <c r="B437" t="str">
-        <v>تفتان</v>
+        <v>بویین زهرا</v>
       </c>
       <c r="C437" t="str">
-        <v>تفتان</v>
+        <v>بویین-زهرا</v>
       </c>
       <c r="D437">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="438">
       <c r="A438">
-        <v>11100022</v>
+        <v>12600002</v>
       </c>
       <c r="B438" t="str">
-        <v>دشتیاری</v>
+        <v>تاکستان</v>
       </c>
       <c r="C438" t="str">
-        <v>دشتیاری</v>
+        <v>تاکستان</v>
       </c>
       <c r="D438">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="439">
       <c r="A439">
-        <v>11100023</v>
+        <v>12600003</v>
       </c>
       <c r="B439" t="str">
-        <v>سرباز</v>
+        <v>قزوین</v>
       </c>
       <c r="C439" t="str">
-        <v>سرباز</v>
+        <v>قزوین</v>
       </c>
       <c r="D439">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="440">
       <c r="A440">
-        <v>11100024</v>
+        <v>12600004</v>
       </c>
       <c r="B440" t="str">
-        <v>گلشن</v>
+        <v>آبیک</v>
       </c>
       <c r="C440" t="str">
-        <v>گلشن</v>
+        <v>آبیک</v>
       </c>
       <c r="D440">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="441">
       <c r="A441">
-        <v>11100025</v>
+        <v>12600005</v>
       </c>
       <c r="B441" t="str">
-        <v>لاشار</v>
+        <v>البرز</v>
       </c>
       <c r="C441" t="str">
-        <v>لاشار</v>
+        <v>البرز</v>
       </c>
       <c r="D441">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="442">
       <c r="A442">
-        <v>11100026</v>
+        <v>12600006</v>
       </c>
       <c r="B442" t="str">
-        <v>زرآباد</v>
+        <v>آوج</v>
       </c>
       <c r="C442" t="str">
-        <v>زرآباد</v>
+        <v>آوج</v>
       </c>
       <c r="D442">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="443">
       <c r="A443">
-        <v>11200010</v>
+        <v>12700001</v>
       </c>
       <c r="B443" t="str">
-        <v>دهگلان</v>
+        <v>بندرگز</v>
       </c>
       <c r="C443" t="str">
-        <v>دهگلان</v>
+        <v>بندرگز</v>
       </c>
       <c r="D443">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="444">
       <c r="A444">
-        <v>11300010</v>
+        <v>12700002</v>
       </c>
       <c r="B444" t="str">
-        <v>درگزین</v>
+        <v>ترکمن</v>
       </c>
       <c r="C444" t="str">
-        <v>درگزین</v>
+        <v>ترکمن</v>
       </c>
       <c r="D444">
-        <v>113</v>
+        <v>127</v>
       </c>
     </row>
     <row r="445">
       <c r="A445">
-        <v>11400010</v>
+        <v>12700003</v>
       </c>
       <c r="B445" t="str">
-        <v>خانمیرزا</v>
+        <v>علی آباد کتول</v>
       </c>
       <c r="C445" t="str">
-        <v>خانمیرزا</v>
+        <v>علی-آباد-کتول</v>
       </c>
       <c r="D445">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="446">
       <c r="A446">
-        <v>11400011</v>
+        <v>12700004</v>
       </c>
       <c r="B446" t="str">
-        <v>فلارد</v>
+        <v>کردکوی</v>
       </c>
       <c r="C446" t="str">
-        <v>فلارد</v>
+        <v>کردکوی</v>
       </c>
       <c r="D446">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="447">
       <c r="A447">
-        <v>11400012</v>
+        <v>12700005</v>
       </c>
       <c r="B447" t="str">
-        <v>فرخ شهر</v>
+        <v>گرگان</v>
       </c>
       <c r="C447" t="str">
-        <v>فرخ-شهر</v>
+        <v>گرگان</v>
       </c>
       <c r="D447">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="448">
       <c r="A448">
-        <v>11500010</v>
+        <v>12700006</v>
       </c>
       <c r="B448" t="str">
-        <v>چگنی</v>
+        <v>گنبدکاووس</v>
       </c>
       <c r="C448" t="str">
-        <v>چگنی</v>
+        <v>گنبدکاووس</v>
       </c>
       <c r="D448">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="449">
       <c r="A449">
-        <v>11500011</v>
+        <v>12700007</v>
       </c>
       <c r="B449" t="str">
-        <v>رومشکان</v>
+        <v>مینودشت</v>
       </c>
       <c r="C449" t="str">
-        <v>رومشکان</v>
+        <v>مینودشت</v>
       </c>
       <c r="D449">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="450">
       <c r="A450">
-        <v>11500012</v>
+        <v>12700008</v>
       </c>
       <c r="B450" t="str">
-        <v>معمولان</v>
+        <v>آق قلا</v>
       </c>
       <c r="C450" t="str">
-        <v>معمولان</v>
+        <v>آق-قلا</v>
       </c>
       <c r="D450">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="451">
       <c r="A451">
-        <v>11600010</v>
+        <v>12700009</v>
       </c>
       <c r="B451" t="str">
-        <v>بدره</v>
+        <v>کلاله</v>
       </c>
       <c r="C451" t="str">
-        <v>بدره</v>
+        <v>کلاله</v>
       </c>
       <c r="D451">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="452">
       <c r="A452">
-        <v>11600011</v>
+        <v>12700010</v>
       </c>
       <c r="B452" t="str">
-        <v>هلیلان</v>
+        <v>آزادشهر</v>
       </c>
       <c r="C452" t="str">
-        <v>هلیلان</v>
+        <v>آزادشهر</v>
       </c>
       <c r="D452">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="453">
       <c r="A453">
-        <v>11600012</v>
+        <v>12700011</v>
       </c>
       <c r="B453" t="str">
-        <v>چوار</v>
+        <v>رامیان</v>
       </c>
       <c r="C453" t="str">
-        <v>چوار</v>
+        <v>رامیان</v>
       </c>
       <c r="D453">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="454">
       <c r="A454">
-        <v>11800010</v>
+        <v>12700012</v>
       </c>
       <c r="B454" t="str">
-        <v>عسلویه</v>
+        <v>مراوه تپه</v>
       </c>
       <c r="C454" t="str">
-        <v>عسلویه</v>
+        <v>مراوه-تپه</v>
       </c>
       <c r="D454">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="455">
       <c r="A455">
-        <v>11900010</v>
+        <v>12700013</v>
       </c>
       <c r="B455" t="str">
-        <v>سلطانیه</v>
+        <v>گمیشان</v>
       </c>
       <c r="C455" t="str">
-        <v>سلطانیه</v>
+        <v>گمیشان</v>
       </c>
       <c r="D455">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="456">
       <c r="A456">
-        <v>12100011</v>
+        <v>12700014</v>
       </c>
       <c r="B456" t="str">
-        <v>بهاباد</v>
+        <v>گالیکش</v>
       </c>
       <c r="C456" t="str">
-        <v>بهاباد</v>
+        <v>گالیکش</v>
       </c>
       <c r="D456">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="457">
       <c r="A457">
-        <v>12100012</v>
+        <v>12800001</v>
       </c>
       <c r="B457" t="str">
-        <v>مروست</v>
+        <v>اسفراین</v>
       </c>
       <c r="C457" t="str">
-        <v>مروست</v>
+        <v>اسفراین</v>
       </c>
       <c r="D457">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="458">
       <c r="A458">
-        <v>12100013</v>
+        <v>12800002</v>
       </c>
       <c r="B458" t="str">
-        <v>زارچ</v>
+        <v>بجنورد</v>
       </c>
       <c r="C458" t="str">
-        <v>زارچ</v>
+        <v>بجنورد</v>
       </c>
       <c r="D458">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="459">
       <c r="A459">
-        <v>12200010</v>
+        <v>12800003</v>
       </c>
       <c r="B459" t="str">
-        <v>خمیر</v>
+        <v>جاجرم</v>
       </c>
       <c r="C459" t="str">
-        <v>خمیر</v>
+        <v>جاجرم</v>
       </c>
       <c r="D459">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="460">
       <c r="A460">
-        <v>12200011</v>
+        <v>12800004</v>
       </c>
       <c r="B460" t="str">
-        <v>پارسیان</v>
+        <v>شیروان</v>
       </c>
       <c r="C460" t="str">
-        <v>پارسیان</v>
+        <v>شیروان</v>
       </c>
       <c r="D460">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="461">
       <c r="A461">
-        <v>12200012</v>
+        <v>12800005</v>
       </c>
       <c r="B461" t="str">
-        <v>سیریک</v>
+        <v>فاروج</v>
       </c>
       <c r="C461" t="str">
-        <v>سیریک</v>
+        <v>فاروج</v>
       </c>
       <c r="D461">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="462">
       <c r="A462">
-        <v>12200013</v>
+        <v>12800006</v>
       </c>
       <c r="B462" t="str">
-        <v>بشاگرد</v>
+        <v>سملقان</v>
       </c>
       <c r="C462" t="str">
-        <v>بشاگرد</v>
+        <v>سملقان</v>
       </c>
       <c r="D462">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="463">
       <c r="A463">
-        <v>12300010</v>
+        <v>12800007</v>
       </c>
       <c r="B463" t="str">
-        <v>اسلامشهر</v>
+        <v>گرمه</v>
       </c>
       <c r="C463" t="str">
-        <v>اسلامشهر</v>
+        <v>گرمه</v>
       </c>
       <c r="D463">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="464">
       <c r="A464">
-        <v>12300012</v>
+        <v>12800008</v>
       </c>
       <c r="B464" t="str">
-        <v>رباط کریم</v>
+        <v>راز و جرگلان</v>
       </c>
       <c r="C464" t="str">
-        <v>رباط-کریم</v>
+        <v>راز-و-جرگلان</v>
       </c>
       <c r="D464">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="465">
       <c r="A465">
-        <v>12300013</v>
+        <v>12800009</v>
       </c>
       <c r="B465" t="str">
-        <v>پاکدشت</v>
+        <v>بام و صفی آباد</v>
       </c>
       <c r="C465" t="str">
-        <v>پاکدشت</v>
+        <v>بام-و-صفی-آباد</v>
       </c>
       <c r="D465">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="466">
       <c r="A466">
-        <v>12300014</v>
+        <v>12800010</v>
       </c>
       <c r="B466" t="str">
-        <v>فیروزکوه</v>
+        <v>مانه</v>
       </c>
       <c r="C466" t="str">
-        <v>فیروزکوه</v>
+        <v>مانه</v>
       </c>
       <c r="D466">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="467">
       <c r="A467">
-        <v>12300016</v>
+        <v>12900001</v>
       </c>
       <c r="B467" t="str">
-        <v>قدس</v>
+        <v>بیرجند</v>
       </c>
       <c r="C467" t="str">
-        <v>قدس</v>
+        <v>بیرجند</v>
       </c>
       <c r="D467">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="468">
       <c r="A468">
-        <v>12300017</v>
+        <v>12900002</v>
       </c>
       <c r="B468" t="str">
-        <v>ملارد</v>
+        <v>درمیان</v>
       </c>
       <c r="C468" t="str">
-        <v>ملارد</v>
+        <v>درمیان</v>
       </c>
       <c r="D468">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="469">
       <c r="A469">
-        <v>12300018</v>
+        <v>12900003</v>
       </c>
       <c r="B469" t="str">
-        <v>پیشوا</v>
+        <v>سربیشه</v>
       </c>
       <c r="C469" t="str">
-        <v>پیشوا</v>
+        <v>سربیشه</v>
       </c>
       <c r="D469">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="470">
       <c r="A470">
-        <v>12300019</v>
+        <v>12900004</v>
       </c>
       <c r="B470" t="str">
-        <v>بهارستان</v>
+        <v>قاینات</v>
       </c>
       <c r="C470" t="str">
-        <v>بهارستان</v>
+        <v>قاینات</v>
       </c>
       <c r="D470">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="471">
       <c r="A471">
-        <v>12300020</v>
+        <v>12900005</v>
       </c>
       <c r="B471" t="str">
-        <v>پردیس</v>
+        <v>نهبندان</v>
       </c>
       <c r="C471" t="str">
-        <v>پردیس</v>
+        <v>نهبندان</v>
       </c>
       <c r="D471">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="472">
       <c r="A472">
-        <v>12300021</v>
+        <v>12900006</v>
       </c>
       <c r="B472" t="str">
-        <v>قرچک</v>
+        <v>سرایان</v>
       </c>
       <c r="C472" t="str">
-        <v>قرچک</v>
+        <v>سرایان</v>
       </c>
       <c r="D472">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="473">
       <c r="A473">
-        <v>12400010</v>
+        <v>12900007</v>
       </c>
       <c r="B473" t="str">
-        <v>سرعین</v>
+        <v>فردوس</v>
       </c>
       <c r="C473" t="str">
-        <v>سرعین</v>
+        <v>فردوس</v>
       </c>
       <c r="D473">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="474">
       <c r="A474">
-        <v>12400011</v>
+        <v>12900008</v>
       </c>
       <c r="B474" t="str">
-        <v>اصلاندوز</v>
+        <v>بشرویه</v>
       </c>
       <c r="C474" t="str">
-        <v>اصلاندوز</v>
+        <v>بشرویه</v>
       </c>
       <c r="D474">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="475">
       <c r="A475">
-        <v>12400012</v>
+        <v>12900009</v>
       </c>
       <c r="B475" t="str">
-        <v>انگوت</v>
+        <v>زیرکوه</v>
       </c>
       <c r="C475" t="str">
-        <v>انگوت</v>
+        <v>زیرکوه</v>
       </c>
       <c r="D475">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="476">
       <c r="A476">
-        <v>12700010</v>
+        <v>12900010</v>
       </c>
       <c r="B476" t="str">
-        <v>آزادشهر</v>
+        <v>خوسف</v>
       </c>
       <c r="C476" t="str">
-        <v>آزادشهر</v>
+        <v>خوسف</v>
       </c>
       <c r="D476">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="477">
       <c r="A477">
-        <v>12700011</v>
+        <v>12900011</v>
       </c>
       <c r="B477" t="str">
-        <v>رامیان</v>
+        <v>طبس</v>
       </c>
       <c r="C477" t="str">
-        <v>رامیان</v>
+        <v>طبس</v>
       </c>
       <c r="D477">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="478">
       <c r="A478">
-        <v>12700012</v>
+        <v>12900012</v>
       </c>
       <c r="B478" t="str">
-        <v>مراوه تپه</v>
+        <v>عشق آباد</v>
       </c>
       <c r="C478" t="str">
-        <v>مراوه-تپه</v>
+        <v>عشق-آباد</v>
       </c>
       <c r="D478">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="479">
       <c r="A479">
-        <v>12700013</v>
+        <v>13000001</v>
       </c>
       <c r="B479" t="str">
-        <v>گمیشان</v>
+        <v>کرج</v>
       </c>
       <c r="C479" t="str">
-        <v>گمیشان</v>
+        <v>کرج</v>
       </c>
       <c r="D479">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="480">
       <c r="A480">
-        <v>12700014</v>
+        <v>13000002</v>
       </c>
       <c r="B480" t="str">
-        <v>گالیکش</v>
+        <v>ساوجبلاغ</v>
       </c>
       <c r="C480" t="str">
-        <v>گالیکش</v>
+        <v>ساوجبلاغ</v>
       </c>
       <c r="D480">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="481">
       <c r="A481">
-        <v>12800010</v>
+        <v>13000003</v>
       </c>
       <c r="B481" t="str">
-        <v>مانه</v>
+        <v>نظرآباد</v>
       </c>
       <c r="C481" t="str">
-        <v>مانه</v>
+        <v>نظرآباد</v>
       </c>
       <c r="D481">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="482">
       <c r="A482">
-        <v>12900010</v>
+        <v>13000004</v>
       </c>
       <c r="B482" t="str">
-        <v>خوسف</v>
+        <v>طالقان</v>
       </c>
       <c r="C482" t="str">
-        <v>خوسف</v>
+        <v>طالقان</v>
       </c>
       <c r="D482">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="483">
       <c r="A483">
-        <v>12900011</v>
+        <v>13000005</v>
       </c>
       <c r="B483" t="str">
-        <v>طبس</v>
+        <v>اشتهارد</v>
       </c>
       <c r="C483" t="str">
-        <v>طبس</v>
+        <v>اشتهارد</v>
       </c>
       <c r="D483">
-        <v>129</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484">
+        <v>13000006</v>
+      </c>
+      <c r="B484" t="str">
+        <v>فردیس</v>
+      </c>
+      <c r="C484" t="str">
+        <v>فردیس</v>
+      </c>
+      <c r="D484">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485">
+        <v>13000007</v>
+      </c>
+      <c r="B485" t="str">
+        <v>چهارباغ</v>
+      </c>
+      <c r="C485" t="str">
+        <v>چهارباغ</v>
+      </c>
+      <c r="D485">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D483"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D485"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dist/xlsx/counties.xlsx
+++ b/dist/xlsx/counties.xlsx
@@ -415,7 +415,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>10000001</v>
+        <v>1000001</v>
       </c>
       <c r="B2" t="str">
         <v>اراک</v>
@@ -429,7 +429,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>10000002</v>
+        <v>1000002</v>
       </c>
       <c r="B3" t="str">
         <v>آشتیان</v>
@@ -443,7 +443,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>10000003</v>
+        <v>1000003</v>
       </c>
       <c r="B4" t="str">
         <v>تفرش</v>
@@ -457,7 +457,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>10000004</v>
+        <v>1000004</v>
       </c>
       <c r="B5" t="str">
         <v>خمین</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>10000005</v>
+        <v>1000005</v>
       </c>
       <c r="B6" t="str">
         <v>دلیجان</v>
@@ -485,7 +485,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>10000006</v>
+        <v>1000006</v>
       </c>
       <c r="B7" t="str">
         <v>ساوه</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>10000007</v>
+        <v>1000007</v>
       </c>
       <c r="B8" t="str">
         <v>شازند</v>
@@ -513,7 +513,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>10000009</v>
+        <v>1000009</v>
       </c>
       <c r="B9" t="str">
         <v>محلات</v>
@@ -527,69 +527,69 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>10000010</v>
+        <v>1010001</v>
       </c>
       <c r="B10" t="str">
-        <v>زرندیه</v>
+        <v>آستارا</v>
       </c>
       <c r="C10" t="str">
-        <v>زرندیه</v>
+        <v>آستارا</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>10000011</v>
+        <v>1010002</v>
       </c>
       <c r="B11" t="str">
-        <v>کمیجان</v>
+        <v>آستانه اشرفیه</v>
       </c>
       <c r="C11" t="str">
-        <v>کمیجان</v>
+        <v>آستانه-اشرفیه</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10000012</v>
+        <v>1010003</v>
       </c>
       <c r="B12" t="str">
-        <v>خنداب</v>
+        <v>بندرانزلی</v>
       </c>
       <c r="C12" t="str">
-        <v>خنداب</v>
+        <v>بندرانزلی</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>10000013</v>
+        <v>1010004</v>
       </c>
       <c r="B13" t="str">
-        <v>فراهان</v>
+        <v>طوالش</v>
       </c>
       <c r="C13" t="str">
-        <v>فراهان</v>
+        <v>طوالش</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>10100001</v>
+        <v>1010005</v>
       </c>
       <c r="B14" t="str">
-        <v>آستارا</v>
+        <v>رشت</v>
       </c>
       <c r="C14" t="str">
-        <v>آستارا</v>
+        <v>رشت</v>
       </c>
       <c r="D14">
         <v>101</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>10100002</v>
+        <v>1010006</v>
       </c>
       <c r="B15" t="str">
-        <v>آستانه اشرفیه</v>
+        <v>رودبار</v>
       </c>
       <c r="C15" t="str">
-        <v>آستانه-اشرفیه</v>
+        <v>رودبار</v>
       </c>
       <c r="D15">
         <v>101</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>10100003</v>
+        <v>1010007</v>
       </c>
       <c r="B16" t="str">
-        <v>بندرانزلی</v>
+        <v>رودسر</v>
       </c>
       <c r="C16" t="str">
-        <v>بندرانزلی</v>
+        <v>رودسر</v>
       </c>
       <c r="D16">
         <v>101</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>10100004</v>
+        <v>1010008</v>
       </c>
       <c r="B17" t="str">
-        <v>طوالش</v>
+        <v>صومعه سرا</v>
       </c>
       <c r="C17" t="str">
-        <v>طوالش</v>
+        <v>صومعه-سرا</v>
       </c>
       <c r="D17">
         <v>101</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>10100005</v>
+        <v>1010009</v>
       </c>
       <c r="B18" t="str">
-        <v>رشت</v>
+        <v>فومن</v>
       </c>
       <c r="C18" t="str">
-        <v>رشت</v>
+        <v>فومن</v>
       </c>
       <c r="D18">
         <v>101</v>
@@ -653,6540 +653,6540 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>10100006</v>
+        <v>1020001</v>
       </c>
       <c r="B19" t="str">
-        <v>رودبار</v>
+        <v>آمل</v>
       </c>
       <c r="C19" t="str">
-        <v>رودبار</v>
+        <v>آمل</v>
       </c>
       <c r="D19">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>10100007</v>
+        <v>1020002</v>
       </c>
       <c r="B20" t="str">
-        <v>رودسر</v>
+        <v>بابل</v>
       </c>
       <c r="C20" t="str">
-        <v>رودسر</v>
+        <v>بابل</v>
       </c>
       <c r="D20">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>10100008</v>
+        <v>1020004</v>
       </c>
       <c r="B21" t="str">
-        <v>صومعه سرا</v>
+        <v>بهشهر</v>
       </c>
       <c r="C21" t="str">
-        <v>صومعه-سرا</v>
+        <v>بهشهر</v>
       </c>
       <c r="D21">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>10100009</v>
+        <v>1020005</v>
       </c>
       <c r="B22" t="str">
-        <v>فومن</v>
+        <v>تنکابن</v>
       </c>
       <c r="C22" t="str">
-        <v>فومن</v>
+        <v>تنکابن</v>
       </c>
       <c r="D22">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>10100010</v>
+        <v>1020006</v>
       </c>
       <c r="B23" t="str">
-        <v>لنگرود</v>
+        <v>رامسر</v>
       </c>
       <c r="C23" t="str">
-        <v>لنگرود</v>
+        <v>رامسر</v>
       </c>
       <c r="D23">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>10100011</v>
+        <v>1020007</v>
       </c>
       <c r="B24" t="str">
-        <v>لاهیجان</v>
+        <v>ساری</v>
       </c>
       <c r="C24" t="str">
-        <v>لاهیجان</v>
+        <v>ساری</v>
       </c>
       <c r="D24">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>10100012</v>
+        <v>1020008</v>
       </c>
       <c r="B25" t="str">
-        <v>شفت</v>
+        <v>سوادکوه</v>
       </c>
       <c r="C25" t="str">
-        <v>شفت</v>
+        <v>سوادکوه</v>
       </c>
       <c r="D25">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>10100013</v>
+        <v>1030002</v>
       </c>
       <c r="B26" t="str">
-        <v>املش</v>
+        <v>اهر</v>
       </c>
       <c r="C26" t="str">
-        <v>املش</v>
+        <v>اهر</v>
       </c>
       <c r="D26">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>10100014</v>
+        <v>1030003</v>
       </c>
       <c r="B27" t="str">
-        <v>رضوانشهر</v>
+        <v>تبریز</v>
       </c>
       <c r="C27" t="str">
-        <v>رضوانشهر</v>
+        <v>تبریز</v>
       </c>
       <c r="D27">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>10100015</v>
+        <v>1030005</v>
       </c>
       <c r="B28" t="str">
-        <v>سیاهکل</v>
+        <v>سراب</v>
       </c>
       <c r="C28" t="str">
-        <v>سیاهکل</v>
+        <v>سراب</v>
       </c>
       <c r="D28">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>10100016</v>
+        <v>1030006</v>
       </c>
       <c r="B29" t="str">
-        <v>ماسال</v>
+        <v>مراغه</v>
       </c>
       <c r="C29" t="str">
-        <v>ماسال</v>
+        <v>مراغه</v>
       </c>
       <c r="D29">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>10100017</v>
+        <v>1030007</v>
       </c>
       <c r="B30" t="str">
-        <v>خمام</v>
+        <v>مرند</v>
       </c>
       <c r="C30" t="str">
-        <v>خمام</v>
+        <v>مرند</v>
       </c>
       <c r="D30">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>10200001</v>
+        <v>1040001</v>
       </c>
       <c r="B31" t="str">
-        <v>آمل</v>
+        <v>ارومیه</v>
       </c>
       <c r="C31" t="str">
-        <v>آمل</v>
+        <v>ارومیه</v>
       </c>
       <c r="D31">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>10200002</v>
+        <v>1040002</v>
       </c>
       <c r="B32" t="str">
-        <v>بابل</v>
+        <v>پیرانشهر</v>
       </c>
       <c r="C32" t="str">
-        <v>بابل</v>
+        <v>پیرانشهر</v>
       </c>
       <c r="D32">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>10200004</v>
+        <v>1040003</v>
       </c>
       <c r="B33" t="str">
-        <v>بهشهر</v>
+        <v>خوی</v>
       </c>
       <c r="C33" t="str">
-        <v>بهشهر</v>
+        <v>خوی</v>
       </c>
       <c r="D33">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>10200005</v>
+        <v>1040004</v>
       </c>
       <c r="B34" t="str">
-        <v>تنکابن</v>
+        <v>سردشت</v>
       </c>
       <c r="C34" t="str">
-        <v>تنکابن</v>
+        <v>سردشت</v>
       </c>
       <c r="D34">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>10200006</v>
+        <v>1040005</v>
       </c>
       <c r="B35" t="str">
-        <v>رامسر</v>
+        <v>سلماس</v>
       </c>
       <c r="C35" t="str">
-        <v>رامسر</v>
+        <v>سلماس</v>
       </c>
       <c r="D35">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>10200007</v>
+        <v>1040006</v>
       </c>
       <c r="B36" t="str">
-        <v>ساری</v>
+        <v>ماکو</v>
       </c>
       <c r="C36" t="str">
-        <v>ساری</v>
+        <v>ماکو</v>
       </c>
       <c r="D36">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>10200008</v>
+        <v>1040007</v>
       </c>
       <c r="B37" t="str">
-        <v>سوادکوه</v>
+        <v>مهاباد</v>
       </c>
       <c r="C37" t="str">
-        <v>سوادکوه</v>
+        <v>مهاباد</v>
       </c>
       <c r="D37">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>10200010</v>
+        <v>1040008</v>
       </c>
       <c r="B38" t="str">
-        <v>قایم شهر</v>
+        <v>میاندوآب</v>
       </c>
       <c r="C38" t="str">
-        <v>قایم-شهر</v>
+        <v>میاندوآب</v>
       </c>
       <c r="D38">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>10200014</v>
+        <v>1040009</v>
       </c>
       <c r="B39" t="str">
-        <v>نور</v>
+        <v>نقده</v>
       </c>
       <c r="C39" t="str">
-        <v>نور</v>
+        <v>نقده</v>
       </c>
       <c r="D39">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>10200015</v>
+        <v>1050001</v>
       </c>
       <c r="B40" t="str">
-        <v>نوشهر</v>
+        <v>اسلام آبادغرب</v>
       </c>
       <c r="C40" t="str">
-        <v>نوشهر</v>
+        <v>اسلام-آبادغرب</v>
       </c>
       <c r="D40">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>10200016</v>
+        <v>1050002</v>
       </c>
       <c r="B41" t="str">
-        <v>بابلسر</v>
+        <v>کرمانشاه</v>
       </c>
       <c r="C41" t="str">
-        <v>بابلسر</v>
+        <v>کرمانشاه</v>
       </c>
       <c r="D41">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>10200018</v>
+        <v>1050003</v>
       </c>
       <c r="B42" t="str">
-        <v>محمودآباد</v>
+        <v>پاوه</v>
       </c>
       <c r="C42" t="str">
-        <v>محمودآباد</v>
+        <v>پاوه</v>
       </c>
       <c r="D42">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>10200019</v>
+        <v>1050004</v>
       </c>
       <c r="B43" t="str">
-        <v>نکا</v>
+        <v>سرپل ذهاب</v>
       </c>
       <c r="C43" t="str">
-        <v>نکا</v>
+        <v>سرپل-ذهاب</v>
       </c>
       <c r="D43">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>10200020</v>
+        <v>1050005</v>
       </c>
       <c r="B44" t="str">
-        <v>چالوس</v>
+        <v>سنقر</v>
       </c>
       <c r="C44" t="str">
-        <v>چالوس</v>
+        <v>سنقر</v>
       </c>
       <c r="D44">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>10200021</v>
+        <v>1050006</v>
       </c>
       <c r="B45" t="str">
-        <v>جویبار</v>
+        <v>قصرشیرین</v>
       </c>
       <c r="C45" t="str">
-        <v>جویبار</v>
+        <v>قصرشیرین</v>
       </c>
       <c r="D45">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>10200022</v>
+        <v>1050007</v>
       </c>
       <c r="B46" t="str">
-        <v>گلوگاه</v>
+        <v>کنگاور</v>
       </c>
       <c r="C46" t="str">
-        <v>گلوگاه</v>
+        <v>کنگاور</v>
       </c>
       <c r="D46">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>10200023</v>
+        <v>1050008</v>
       </c>
       <c r="B47" t="str">
-        <v>فریدونکنار</v>
+        <v>گیلانغرب</v>
       </c>
       <c r="C47" t="str">
-        <v>فریدونکنار</v>
+        <v>گیلانغرب</v>
       </c>
       <c r="D47">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>10200024</v>
+        <v>1050009</v>
       </c>
       <c r="B48" t="str">
-        <v>عباس آباد</v>
+        <v>جوانرود</v>
       </c>
       <c r="C48" t="str">
-        <v>عباس-آباد</v>
+        <v>جوانرود</v>
       </c>
       <c r="D48">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>10200025</v>
+        <v>1060001</v>
       </c>
       <c r="B49" t="str">
-        <v>میاندورود</v>
+        <v>آبادان</v>
       </c>
       <c r="C49" t="str">
-        <v>میاندورود</v>
+        <v>آبادان</v>
       </c>
       <c r="D49">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>10200026</v>
+        <v>1060002</v>
       </c>
       <c r="B50" t="str">
-        <v>سیمرغ</v>
+        <v>اندیمشک</v>
       </c>
       <c r="C50" t="str">
-        <v>سیمرغ</v>
+        <v>اندیمشک</v>
       </c>
       <c r="D50">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>10200027</v>
+        <v>1060003</v>
       </c>
       <c r="B51" t="str">
-        <v>سوادکوه شمالی</v>
+        <v>اهواز</v>
       </c>
       <c r="C51" t="str">
-        <v>سوادکوه-شمالی</v>
+        <v>اهواز</v>
       </c>
       <c r="D51">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>10200028</v>
+        <v>1060004</v>
       </c>
       <c r="B52" t="str">
-        <v>کلاردشت</v>
+        <v>ایذه</v>
       </c>
       <c r="C52" t="str">
-        <v>کلاردشت</v>
+        <v>ایذه</v>
       </c>
       <c r="D52">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>10300002</v>
+        <v>1060005</v>
       </c>
       <c r="B53" t="str">
-        <v>اهر</v>
+        <v>بندر ماهشهر</v>
       </c>
       <c r="C53" t="str">
-        <v>اهر</v>
+        <v>بندرماهشهر</v>
       </c>
       <c r="D53">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>10300003</v>
+        <v>1060006</v>
       </c>
       <c r="B54" t="str">
-        <v>تبریز</v>
+        <v>بهبهان</v>
       </c>
       <c r="C54" t="str">
-        <v>تبریز</v>
+        <v>بهبهان</v>
       </c>
       <c r="D54">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>10300005</v>
+        <v>1060007</v>
       </c>
       <c r="B55" t="str">
-        <v>سراب</v>
+        <v>خرمشهر</v>
       </c>
       <c r="C55" t="str">
-        <v>سراب</v>
+        <v>خرمشهر</v>
       </c>
       <c r="D55">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>10300006</v>
+        <v>1060008</v>
       </c>
       <c r="B56" t="str">
-        <v>مراغه</v>
+        <v>دزفول</v>
       </c>
       <c r="C56" t="str">
-        <v>مراغه</v>
+        <v>دزفول</v>
       </c>
       <c r="D56">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>10300007</v>
+        <v>1060009</v>
       </c>
       <c r="B57" t="str">
-        <v>مرند</v>
+        <v>دشت آزادگان</v>
       </c>
       <c r="C57" t="str">
-        <v>مرند</v>
+        <v>دشت-آزادگان</v>
       </c>
       <c r="D57">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>10300010</v>
+        <v>1070001</v>
       </c>
       <c r="B58" t="str">
-        <v>میانه</v>
+        <v>آباده</v>
       </c>
       <c r="C58" t="str">
-        <v>میانه</v>
+        <v>آباده</v>
       </c>
       <c r="D58">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>10300011</v>
+        <v>1070002</v>
       </c>
       <c r="B59" t="str">
-        <v>هشترود</v>
+        <v>استهبان</v>
       </c>
       <c r="C59" t="str">
-        <v>هشترود</v>
+        <v>استهبان</v>
       </c>
       <c r="D59">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>10300012</v>
+        <v>1070003</v>
       </c>
       <c r="B60" t="str">
-        <v>بناب</v>
+        <v>اقلید</v>
       </c>
       <c r="C60" t="str">
-        <v>بناب</v>
+        <v>اقلید</v>
       </c>
       <c r="D60">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>10300013</v>
+        <v>1070004</v>
       </c>
       <c r="B61" t="str">
-        <v>بستان آباد</v>
+        <v>جهرم</v>
       </c>
       <c r="C61" t="str">
-        <v>بستان-آباد</v>
+        <v>جهرم</v>
       </c>
       <c r="D61">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>10300014</v>
+        <v>1070005</v>
       </c>
       <c r="B62" t="str">
-        <v>شبستر</v>
+        <v>داراب</v>
       </c>
       <c r="C62" t="str">
-        <v>شبستر</v>
+        <v>داراب</v>
       </c>
       <c r="D62">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>10300015</v>
+        <v>1070006</v>
       </c>
       <c r="B63" t="str">
-        <v>کلیبر</v>
+        <v>سپیدان</v>
       </c>
       <c r="C63" t="str">
-        <v>کلیبر</v>
+        <v>سپیدان</v>
       </c>
       <c r="D63">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>10300016</v>
+        <v>1070007</v>
       </c>
       <c r="B64" t="str">
-        <v>هریس</v>
+        <v>شیراز</v>
       </c>
       <c r="C64" t="str">
-        <v>هریس</v>
+        <v>شیراز</v>
       </c>
       <c r="D64">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>10300019</v>
+        <v>1070008</v>
       </c>
       <c r="B65" t="str">
-        <v>جلفا</v>
+        <v>فسا</v>
       </c>
       <c r="C65" t="str">
-        <v>جلفا</v>
+        <v>فسا</v>
       </c>
       <c r="D65">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>10300020</v>
+        <v>1070009</v>
       </c>
       <c r="B66" t="str">
-        <v>ملکان</v>
+        <v>فیروزآباد</v>
       </c>
       <c r="C66" t="str">
-        <v>ملکان</v>
+        <v>فیروزآباد</v>
       </c>
       <c r="D66">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>10300021</v>
+        <v>1080001</v>
       </c>
       <c r="B67" t="str">
-        <v>آذرشهر</v>
+        <v>بافت</v>
       </c>
       <c r="C67" t="str">
-        <v>آذرشهر</v>
+        <v>بافت</v>
       </c>
       <c r="D67">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>10300022</v>
+        <v>1080002</v>
       </c>
       <c r="B68" t="str">
-        <v>اسکو</v>
+        <v>بم</v>
       </c>
       <c r="C68" t="str">
-        <v>اسکو</v>
+        <v>بم</v>
       </c>
       <c r="D68">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>10300023</v>
+        <v>1080003</v>
       </c>
       <c r="B69" t="str">
-        <v>چاراویماق</v>
+        <v>جیرفت</v>
       </c>
       <c r="C69" t="str">
-        <v>چاراویماق</v>
+        <v>جیرفت</v>
       </c>
       <c r="D69">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>10300024</v>
+        <v>1080004</v>
       </c>
       <c r="B70" t="str">
-        <v>ورزقان</v>
+        <v>رفسنجان</v>
       </c>
       <c r="C70" t="str">
-        <v>ورزقان</v>
+        <v>رفسنجان</v>
       </c>
       <c r="D70">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>10300025</v>
+        <v>1080005</v>
       </c>
       <c r="B71" t="str">
-        <v>عجب شیر</v>
+        <v>زرند</v>
       </c>
       <c r="C71" t="str">
-        <v>عجب-شیر</v>
+        <v>زرند</v>
       </c>
       <c r="D71">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>10300026</v>
+        <v>1080006</v>
       </c>
       <c r="B72" t="str">
-        <v>خدا آفرین</v>
+        <v>سیرجان</v>
       </c>
       <c r="C72" t="str">
-        <v>خدا-آفرین</v>
+        <v>سیرجان</v>
       </c>
       <c r="D72">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>10300027</v>
+        <v>1080007</v>
       </c>
       <c r="B73" t="str">
-        <v>هوراند</v>
+        <v>شهربابک</v>
       </c>
       <c r="C73" t="str">
-        <v>هوراند</v>
+        <v>شهربابک</v>
       </c>
       <c r="D73">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>10300028</v>
+        <v>1080008</v>
       </c>
       <c r="B74" t="str">
-        <v>لیلان</v>
+        <v>کرمان</v>
       </c>
       <c r="C74" t="str">
-        <v>لیلان</v>
+        <v>کرمان</v>
       </c>
       <c r="D74">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>10300029</v>
+        <v>1080009</v>
       </c>
       <c r="B75" t="str">
-        <v>ترکمانچای</v>
+        <v>کهنوج</v>
       </c>
       <c r="C75" t="str">
-        <v>ترکمانچای</v>
+        <v>کهنوج</v>
       </c>
       <c r="D75">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>10400001</v>
+        <v>1090004</v>
       </c>
       <c r="B76" t="str">
-        <v>ارومیه</v>
+        <v>تایباد</v>
       </c>
       <c r="C76" t="str">
-        <v>ارومیه</v>
+        <v>تایباد</v>
       </c>
       <c r="D76">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>10400002</v>
+        <v>1090005</v>
       </c>
       <c r="B77" t="str">
-        <v>پیرانشهر</v>
+        <v>تربت حیدریه</v>
       </c>
       <c r="C77" t="str">
-        <v>پیرانشهر</v>
+        <v>تربت-حیدریه</v>
       </c>
       <c r="D77">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>10400003</v>
+        <v>1090006</v>
       </c>
       <c r="B78" t="str">
-        <v>خوی</v>
+        <v>تربت جام</v>
       </c>
       <c r="C78" t="str">
-        <v>خوی</v>
+        <v>تربت-جام</v>
       </c>
       <c r="D78">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>10400004</v>
+        <v>1090007</v>
       </c>
       <c r="B79" t="str">
-        <v>سردشت</v>
+        <v>درگز</v>
       </c>
       <c r="C79" t="str">
-        <v>سردشت</v>
+        <v>درگز</v>
       </c>
       <c r="D79">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>10400005</v>
+        <v>1090008</v>
       </c>
       <c r="B80" t="str">
-        <v>سلماس</v>
+        <v>سبزوار</v>
       </c>
       <c r="C80" t="str">
-        <v>سلماس</v>
+        <v>سبزوار</v>
       </c>
       <c r="D80">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>10400006</v>
+        <v>1100001</v>
       </c>
       <c r="B81" t="str">
-        <v>ماکو</v>
+        <v>اردستان</v>
       </c>
       <c r="C81" t="str">
-        <v>ماکو</v>
+        <v>اردستان</v>
       </c>
       <c r="D81">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>10400007</v>
+        <v>1100002</v>
       </c>
       <c r="B82" t="str">
-        <v>مهاباد</v>
+        <v>اصفهان</v>
       </c>
       <c r="C82" t="str">
-        <v>مهاباد</v>
+        <v>اصفهان</v>
       </c>
       <c r="D82">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>10400008</v>
+        <v>1100003</v>
       </c>
       <c r="B83" t="str">
-        <v>میاندوآب</v>
+        <v>خمینی شهر</v>
       </c>
       <c r="C83" t="str">
-        <v>میاندوآب</v>
+        <v>خمینی-شهر</v>
       </c>
       <c r="D83">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>10400009</v>
+        <v>1100004</v>
       </c>
       <c r="B84" t="str">
-        <v>نقده</v>
+        <v>خوانسار</v>
       </c>
       <c r="C84" t="str">
-        <v>نقده</v>
+        <v>خوانسار</v>
       </c>
       <c r="D84">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>10400010</v>
+        <v>1100005</v>
       </c>
       <c r="B85" t="str">
-        <v>بوکان</v>
+        <v>سمیرم</v>
       </c>
       <c r="C85" t="str">
-        <v>بوکان</v>
+        <v>سمیرم</v>
       </c>
       <c r="D85">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>10400011</v>
+        <v>1100006</v>
       </c>
       <c r="B86" t="str">
-        <v>شاهین دژ</v>
+        <v>فریدن</v>
       </c>
       <c r="C86" t="str">
-        <v>شاهین-دژ</v>
+        <v>فریدن</v>
       </c>
       <c r="D86">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>10400012</v>
+        <v>1100007</v>
       </c>
       <c r="B87" t="str">
-        <v>تکاب</v>
+        <v>فریدونشهر</v>
       </c>
       <c r="C87" t="str">
-        <v>تکاب</v>
+        <v>فریدونشهر</v>
       </c>
       <c r="D87">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>10400013</v>
+        <v>1100008</v>
       </c>
       <c r="B88" t="str">
-        <v>اشنویه</v>
+        <v>فلاورجان</v>
       </c>
       <c r="C88" t="str">
-        <v>اشنویه</v>
+        <v>فلاورجان</v>
       </c>
       <c r="D88">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>10400014</v>
+        <v>1100009</v>
       </c>
       <c r="B89" t="str">
-        <v>چالدران</v>
+        <v>شهرضا</v>
       </c>
       <c r="C89" t="str">
-        <v>چالدران</v>
+        <v>شهرضا</v>
       </c>
       <c r="D89">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>10400015</v>
+        <v>1110001</v>
       </c>
       <c r="B90" t="str">
-        <v>پلدشت</v>
+        <v>ایرانشهر</v>
       </c>
       <c r="C90" t="str">
-        <v>پلدشت</v>
+        <v>ایرانشهر</v>
       </c>
       <c r="D90">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>10400016</v>
+        <v>1110002</v>
       </c>
       <c r="B91" t="str">
-        <v>چایپاره</v>
+        <v>چاه بهار</v>
       </c>
       <c r="C91" t="str">
-        <v>چایپاره</v>
+        <v>چاه-بهار</v>
       </c>
       <c r="D91">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>10400017</v>
+        <v>1110003</v>
       </c>
       <c r="B92" t="str">
-        <v>شوط</v>
+        <v>خاش</v>
       </c>
       <c r="C92" t="str">
-        <v>شوط</v>
+        <v>خاش</v>
       </c>
       <c r="D92">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>10400018</v>
+        <v>1110004</v>
       </c>
       <c r="B93" t="str">
-        <v>چهاربرج</v>
+        <v>زابل</v>
       </c>
       <c r="C93" t="str">
-        <v>چهاربرج</v>
+        <v>زابل</v>
       </c>
       <c r="D93">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>10400019</v>
+        <v>1110005</v>
       </c>
       <c r="B94" t="str">
-        <v>باروق</v>
+        <v>زاهدان</v>
       </c>
       <c r="C94" t="str">
-        <v>باروق</v>
+        <v>زاهدان</v>
       </c>
       <c r="D94">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>10400020</v>
+        <v>1110006</v>
       </c>
       <c r="B95" t="str">
-        <v>میرآباد</v>
+        <v>سراوان</v>
       </c>
       <c r="C95" t="str">
-        <v>میرآباد</v>
+        <v>سراوان</v>
       </c>
       <c r="D95">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>10500001</v>
+        <v>1110007</v>
       </c>
       <c r="B96" t="str">
-        <v>اسلام آبادغرب</v>
+        <v>نیک شهر</v>
       </c>
       <c r="C96" t="str">
-        <v>اسلام-آبادغرب</v>
+        <v>نیک-شهر</v>
       </c>
       <c r="D96">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>10500002</v>
+        <v>1110008</v>
       </c>
       <c r="B97" t="str">
-        <v>کرمانشاه</v>
+        <v>راسک</v>
       </c>
       <c r="C97" t="str">
-        <v>کرمانشاه</v>
+        <v>راسک</v>
       </c>
       <c r="D97">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>10500003</v>
+        <v>1110009</v>
       </c>
       <c r="B98" t="str">
-        <v>پاوه</v>
+        <v>کنارک</v>
       </c>
       <c r="C98" t="str">
-        <v>پاوه</v>
+        <v>کنارک</v>
       </c>
       <c r="D98">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>10500004</v>
+        <v>1120001</v>
       </c>
       <c r="B99" t="str">
-        <v>سرپل ذهاب</v>
+        <v>بانه</v>
       </c>
       <c r="C99" t="str">
-        <v>سرپل-ذهاب</v>
+        <v>بانه</v>
       </c>
       <c r="D99">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>10500005</v>
+        <v>1120002</v>
       </c>
       <c r="B100" t="str">
-        <v>سنقر</v>
+        <v>بیجار</v>
       </c>
       <c r="C100" t="str">
-        <v>سنقر</v>
+        <v>بیجار</v>
       </c>
       <c r="D100">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>10500006</v>
+        <v>1120003</v>
       </c>
       <c r="B101" t="str">
-        <v>قصرشیرین</v>
+        <v>سقز</v>
       </c>
       <c r="C101" t="str">
-        <v>قصرشیرین</v>
+        <v>سقز</v>
       </c>
       <c r="D101">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>10500007</v>
+        <v>1120004</v>
       </c>
       <c r="B102" t="str">
-        <v>کنگاور</v>
+        <v>سنندج</v>
       </c>
       <c r="C102" t="str">
-        <v>کنگاور</v>
+        <v>سنندج</v>
       </c>
       <c r="D102">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>10500008</v>
+        <v>1120005</v>
       </c>
       <c r="B103" t="str">
-        <v>گیلانغرب</v>
+        <v>قروه</v>
       </c>
       <c r="C103" t="str">
-        <v>گیلانغرب</v>
+        <v>قروه</v>
       </c>
       <c r="D103">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>10500009</v>
+        <v>1120006</v>
       </c>
       <c r="B104" t="str">
-        <v>جوانرود</v>
+        <v>مریوان</v>
       </c>
       <c r="C104" t="str">
-        <v>جوانرود</v>
+        <v>مریوان</v>
       </c>
       <c r="D104">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>10500010</v>
+        <v>1120007</v>
       </c>
       <c r="B105" t="str">
-        <v>صحنه</v>
+        <v>دیواندره</v>
       </c>
       <c r="C105" t="str">
-        <v>صحنه</v>
+        <v>دیواندره</v>
       </c>
       <c r="D105">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>10500011</v>
+        <v>1120008</v>
       </c>
       <c r="B106" t="str">
-        <v>هرسین</v>
+        <v>کامیاران</v>
       </c>
       <c r="C106" t="str">
-        <v>هرسین</v>
+        <v>کامیاران</v>
       </c>
       <c r="D106">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>10500012</v>
+        <v>1120009</v>
       </c>
       <c r="B107" t="str">
-        <v>ثلاث باباجانی</v>
+        <v>سروآباد</v>
       </c>
       <c r="C107" t="str">
-        <v>ثلاث-باباجانی</v>
+        <v>سروآباد</v>
       </c>
       <c r="D107">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>10500013</v>
+        <v>1130001</v>
       </c>
       <c r="B108" t="str">
-        <v>دالاهو</v>
+        <v>تویسرکان</v>
       </c>
       <c r="C108" t="str">
-        <v>دالاهو</v>
+        <v>تویسرکان</v>
       </c>
       <c r="D108">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>10500014</v>
+        <v>1130002</v>
       </c>
       <c r="B109" t="str">
-        <v>روانسر</v>
+        <v>ملایر</v>
       </c>
       <c r="C109" t="str">
-        <v>روانسر</v>
+        <v>ملایر</v>
       </c>
       <c r="D109">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>10600001</v>
+        <v>1130003</v>
       </c>
       <c r="B110" t="str">
-        <v>آبادان</v>
+        <v>نهاوند</v>
       </c>
       <c r="C110" t="str">
-        <v>آبادان</v>
+        <v>نهاوند</v>
       </c>
       <c r="D110">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>10600002</v>
+        <v>1130004</v>
       </c>
       <c r="B111" t="str">
-        <v>اندیمشک</v>
+        <v>همدان</v>
       </c>
       <c r="C111" t="str">
-        <v>اندیمشک</v>
+        <v>همدان</v>
       </c>
       <c r="D111">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <v>10600003</v>
+        <v>1130005</v>
       </c>
       <c r="B112" t="str">
-        <v>اهواز</v>
+        <v>کبودرآهنگ</v>
       </c>
       <c r="C112" t="str">
-        <v>اهواز</v>
+        <v>کبودرآهنگ</v>
       </c>
       <c r="D112">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>10600004</v>
+        <v>1130006</v>
       </c>
       <c r="B113" t="str">
-        <v>ایذه</v>
+        <v>اسدآباد</v>
       </c>
       <c r="C113" t="str">
-        <v>ایذه</v>
+        <v>اسدآباد</v>
       </c>
       <c r="D113">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>10600005</v>
+        <v>1130007</v>
       </c>
       <c r="B114" t="str">
-        <v>بندر ماهشهر</v>
+        <v>بهار</v>
       </c>
       <c r="C114" t="str">
-        <v>بندر-ماهشهر</v>
+        <v>بهار</v>
       </c>
       <c r="D114">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>10600006</v>
+        <v>1130008</v>
       </c>
       <c r="B115" t="str">
-        <v>بهبهان</v>
+        <v>رزن</v>
       </c>
       <c r="C115" t="str">
-        <v>بهبهان</v>
+        <v>رزن</v>
       </c>
       <c r="D115">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>10600007</v>
+        <v>1130009</v>
       </c>
       <c r="B116" t="str">
-        <v>خرمشهر</v>
+        <v>فامنین</v>
       </c>
       <c r="C116" t="str">
-        <v>خرمشهر</v>
+        <v>فامنین</v>
       </c>
       <c r="D116">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>10600008</v>
+        <v>1140001</v>
       </c>
       <c r="B117" t="str">
-        <v>دزفول</v>
+        <v>بروجن</v>
       </c>
       <c r="C117" t="str">
-        <v>دزفول</v>
+        <v>بروجن</v>
       </c>
       <c r="D117">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>10600009</v>
+        <v>1140002</v>
       </c>
       <c r="B118" t="str">
-        <v>دشت آزادگان</v>
+        <v>شهرکرد</v>
       </c>
       <c r="C118" t="str">
-        <v>دشت-آزادگان</v>
+        <v>شهرکرد</v>
       </c>
       <c r="D118">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>10600010</v>
+        <v>1140003</v>
       </c>
       <c r="B119" t="str">
-        <v>رامهرمز</v>
+        <v>فارسان</v>
       </c>
       <c r="C119" t="str">
-        <v>رامهرمز</v>
+        <v>فارسان</v>
       </c>
       <c r="D119">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>10600011</v>
+        <v>1140004</v>
       </c>
       <c r="B120" t="str">
-        <v>شادگان</v>
+        <v>لردگان</v>
       </c>
       <c r="C120" t="str">
-        <v>شادگان</v>
+        <v>لردگان</v>
       </c>
       <c r="D120">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>10600012</v>
+        <v>1140005</v>
       </c>
       <c r="B121" t="str">
-        <v>شوشتر</v>
+        <v>اردل</v>
       </c>
       <c r="C121" t="str">
-        <v>شوشتر</v>
+        <v>اردل</v>
       </c>
       <c r="D121">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>10600013</v>
+        <v>1140006</v>
       </c>
       <c r="B122" t="str">
-        <v>مسجدسلیمان</v>
+        <v>کوهرنگ</v>
       </c>
       <c r="C122" t="str">
-        <v>مسجدسلیمان</v>
+        <v>کوهرنگ</v>
       </c>
       <c r="D122">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>10600014</v>
+        <v>1140007</v>
       </c>
       <c r="B123" t="str">
-        <v>شوش</v>
+        <v>کیار</v>
       </c>
       <c r="C123" t="str">
-        <v>شوش</v>
+        <v>کیار</v>
       </c>
       <c r="D123">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="124">
       <c r="A124">
-        <v>10600015</v>
+        <v>1140008</v>
       </c>
       <c r="B124" t="str">
-        <v>باغ ملک</v>
+        <v>سامان</v>
       </c>
       <c r="C124" t="str">
-        <v>باغ-ملک</v>
+        <v>سامان</v>
       </c>
       <c r="D124">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>10600016</v>
+        <v>1140009</v>
       </c>
       <c r="B125" t="str">
-        <v>امیدیه</v>
+        <v>بن</v>
       </c>
       <c r="C125" t="str">
-        <v>امیدیه</v>
+        <v>بن</v>
       </c>
       <c r="D125">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="126">
       <c r="A126">
-        <v>10600017</v>
+        <v>1150001</v>
       </c>
       <c r="B126" t="str">
-        <v>لالی</v>
+        <v>الیگودرز</v>
       </c>
       <c r="C126" t="str">
-        <v>لالی</v>
+        <v>الیگودرز</v>
       </c>
       <c r="D126">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="127">
       <c r="A127">
-        <v>10600018</v>
+        <v>1150002</v>
       </c>
       <c r="B127" t="str">
-        <v>هندیجان</v>
+        <v>بروجرد</v>
       </c>
       <c r="C127" t="str">
-        <v>هندیجان</v>
+        <v>بروجرد</v>
       </c>
       <c r="D127">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
-        <v>10600019</v>
+        <v>1150003</v>
       </c>
       <c r="B128" t="str">
-        <v>رامشیر</v>
+        <v>خرم آباد</v>
       </c>
       <c r="C128" t="str">
-        <v>رامشیر</v>
+        <v>خرم-آباد</v>
       </c>
       <c r="D128">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>10600020</v>
+        <v>1150004</v>
       </c>
       <c r="B129" t="str">
-        <v>گتوند</v>
+        <v>دلفان</v>
       </c>
       <c r="C129" t="str">
-        <v>گتوند</v>
+        <v>دلفان</v>
       </c>
       <c r="D129">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>10600021</v>
+        <v>1150005</v>
       </c>
       <c r="B130" t="str">
-        <v>اندیکا</v>
+        <v>دورود</v>
       </c>
       <c r="C130" t="str">
-        <v>اندیکا</v>
+        <v>دورود</v>
       </c>
       <c r="D130">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>10600022</v>
+        <v>1150006</v>
       </c>
       <c r="B131" t="str">
-        <v>هفتکل</v>
+        <v>کوهدشت</v>
       </c>
       <c r="C131" t="str">
-        <v>هفتکل</v>
+        <v>کوهدشت</v>
       </c>
       <c r="D131">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>10600023</v>
+        <v>1150007</v>
       </c>
       <c r="B132" t="str">
-        <v>هویزه</v>
+        <v>ازنا</v>
       </c>
       <c r="C132" t="str">
-        <v>هویزه</v>
+        <v>ازنا</v>
       </c>
       <c r="D132">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>10600024</v>
+        <v>1150008</v>
       </c>
       <c r="B133" t="str">
-        <v>باوی</v>
+        <v>پلدختر</v>
       </c>
       <c r="C133" t="str">
-        <v>باوی</v>
+        <v>پلدختر</v>
       </c>
       <c r="D133">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>10600025</v>
+        <v>1150009</v>
       </c>
       <c r="B134" t="str">
-        <v>حمیدیه</v>
+        <v>سلسله</v>
       </c>
       <c r="C134" t="str">
-        <v>حمیدیه</v>
+        <v>سلسله</v>
       </c>
       <c r="D134">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>10600026</v>
+        <v>1160001</v>
       </c>
       <c r="B135" t="str">
-        <v>آغاجاری</v>
+        <v>ایلام</v>
       </c>
       <c r="C135" t="str">
-        <v>آغاجاری</v>
+        <v>ایلام</v>
       </c>
       <c r="D135">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>10600027</v>
+        <v>1160002</v>
       </c>
       <c r="B136" t="str">
-        <v>کارون</v>
+        <v>دره شهر</v>
       </c>
       <c r="C136" t="str">
-        <v>کارون</v>
+        <v>دره-شهر</v>
       </c>
       <c r="D136">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>10600028</v>
+        <v>1160003</v>
       </c>
       <c r="B137" t="str">
-        <v>کرخه</v>
+        <v>دهلران</v>
       </c>
       <c r="C137" t="str">
-        <v>کرخه</v>
+        <v>دهلران</v>
       </c>
       <c r="D137">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>10600029</v>
+        <v>1160004</v>
       </c>
       <c r="B138" t="str">
-        <v>دزپارت</v>
+        <v>چرداول</v>
       </c>
       <c r="C138" t="str">
-        <v>دزپارت</v>
+        <v>چرداول</v>
       </c>
       <c r="D138">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>10600030</v>
+        <v>1160005</v>
       </c>
       <c r="B139" t="str">
-        <v>صیدون</v>
+        <v>مهران</v>
       </c>
       <c r="C139" t="str">
-        <v>صیدون</v>
+        <v>مهران</v>
       </c>
       <c r="D139">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>10700001</v>
+        <v>1160006</v>
       </c>
       <c r="B140" t="str">
-        <v>آباده</v>
+        <v>آبدانان</v>
       </c>
       <c r="C140" t="str">
-        <v>آباده</v>
+        <v>آبدانان</v>
       </c>
       <c r="D140">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="141">
       <c r="A141">
-        <v>10700002</v>
+        <v>1160007</v>
       </c>
       <c r="B141" t="str">
-        <v>استهبان</v>
+        <v>ایوان</v>
       </c>
       <c r="C141" t="str">
-        <v>استهبان</v>
+        <v>ایوان</v>
       </c>
       <c r="D141">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>10700003</v>
+        <v>1160008</v>
       </c>
       <c r="B142" t="str">
-        <v>اقلید</v>
+        <v>ملکشاهی</v>
       </c>
       <c r="C142" t="str">
-        <v>اقلید</v>
+        <v>ملکشاهی</v>
       </c>
       <c r="D142">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>10700004</v>
+        <v>1160009</v>
       </c>
       <c r="B143" t="str">
-        <v>جهرم</v>
+        <v>سیروان</v>
       </c>
       <c r="C143" t="str">
-        <v>جهرم</v>
+        <v>سیروان</v>
       </c>
       <c r="D143">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>10700005</v>
+        <v>1170001</v>
       </c>
       <c r="B144" t="str">
-        <v>داراب</v>
+        <v>بویراحمد</v>
       </c>
       <c r="C144" t="str">
-        <v>داراب</v>
+        <v>بویراحمد</v>
       </c>
       <c r="D144">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="145">
       <c r="A145">
-        <v>10700006</v>
+        <v>1170002</v>
       </c>
       <c r="B145" t="str">
-        <v>سپیدان</v>
+        <v>کهگیلویه</v>
       </c>
       <c r="C145" t="str">
-        <v>سپیدان</v>
+        <v>کهگیلویه</v>
       </c>
       <c r="D145">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="146">
       <c r="A146">
-        <v>10700007</v>
+        <v>1170003</v>
       </c>
       <c r="B146" t="str">
-        <v>شیراز</v>
+        <v>گچساران</v>
       </c>
       <c r="C146" t="str">
-        <v>شیراز</v>
+        <v>گچساران</v>
       </c>
       <c r="D146">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>10700008</v>
+        <v>1170004</v>
       </c>
       <c r="B147" t="str">
-        <v>فسا</v>
+        <v>دنا</v>
       </c>
       <c r="C147" t="str">
-        <v>فسا</v>
+        <v>دنا</v>
       </c>
       <c r="D147">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>10700009</v>
+        <v>1170005</v>
       </c>
       <c r="B148" t="str">
-        <v>فیروزآباد</v>
+        <v>بهمیی</v>
       </c>
       <c r="C148" t="str">
-        <v>فیروزآباد</v>
+        <v>بهمیی</v>
       </c>
       <c r="D148">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="149">
       <c r="A149">
-        <v>10700010</v>
+        <v>1170006</v>
       </c>
       <c r="B149" t="str">
-        <v>کازرون</v>
+        <v>چرام</v>
       </c>
       <c r="C149" t="str">
-        <v>کازرون</v>
+        <v>چرام</v>
       </c>
       <c r="D149">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>10700011</v>
+        <v>1170007</v>
       </c>
       <c r="B150" t="str">
-        <v>لارستان</v>
+        <v>باشت</v>
       </c>
       <c r="C150" t="str">
-        <v>لارستان</v>
+        <v>باشت</v>
       </c>
       <c r="D150">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>10700012</v>
+        <v>1170008</v>
       </c>
       <c r="B151" t="str">
-        <v>مرودشت</v>
+        <v>لنده</v>
       </c>
       <c r="C151" t="str">
-        <v>مرودشت</v>
+        <v>لنده</v>
       </c>
       <c r="D151">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>10700013</v>
+        <v>1170009</v>
       </c>
       <c r="B152" t="str">
-        <v>ممسنی</v>
+        <v>مارگون</v>
       </c>
       <c r="C152" t="str">
-        <v>ممسنی</v>
+        <v>مارگون</v>
       </c>
       <c r="D152">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>10700014</v>
+        <v>1180001</v>
       </c>
       <c r="B153" t="str">
-        <v>نی ریز</v>
+        <v>بوشهر</v>
       </c>
       <c r="C153" t="str">
-        <v>نی-ریز</v>
+        <v>بوشهر</v>
       </c>
       <c r="D153">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="154">
       <c r="A154">
-        <v>10700015</v>
+        <v>1180002</v>
       </c>
       <c r="B154" t="str">
-        <v>لامرد</v>
+        <v>تنگستان</v>
       </c>
       <c r="C154" t="str">
-        <v>لامرد</v>
+        <v>تنگستان</v>
       </c>
       <c r="D154">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>10700016</v>
+        <v>1180003</v>
       </c>
       <c r="B155" t="str">
-        <v>بوانات</v>
+        <v>دشتستان</v>
       </c>
       <c r="C155" t="str">
-        <v>بوانات</v>
+        <v>دشتستان</v>
       </c>
       <c r="D155">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="156">
       <c r="A156">
-        <v>10700017</v>
+        <v>1180004</v>
       </c>
       <c r="B156" t="str">
-        <v>ارسنجان</v>
+        <v>دشتی</v>
       </c>
       <c r="C156" t="str">
-        <v>ارسنجان</v>
+        <v>دشتی</v>
       </c>
       <c r="D156">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="157">
       <c r="A157">
-        <v>10700018</v>
+        <v>1180005</v>
       </c>
       <c r="B157" t="str">
-        <v>خرم بید</v>
+        <v>دیر</v>
       </c>
       <c r="C157" t="str">
-        <v>خرم-بید</v>
+        <v>دیر</v>
       </c>
       <c r="D157">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="158">
       <c r="A158">
-        <v>10700019</v>
+        <v>1180006</v>
       </c>
       <c r="B158" t="str">
-        <v>زرین دشت</v>
+        <v>کنگان</v>
       </c>
       <c r="C158" t="str">
-        <v>زرین-دشت</v>
+        <v>کنگان</v>
       </c>
       <c r="D158">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="159">
       <c r="A159">
-        <v>10700020</v>
+        <v>1180007</v>
       </c>
       <c r="B159" t="str">
-        <v>قیرو کارزین</v>
+        <v>گناوه</v>
       </c>
       <c r="C159" t="str">
-        <v>قیرو-کارزین</v>
+        <v>گناوه</v>
       </c>
       <c r="D159">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="160">
       <c r="A160">
-        <v>10700021</v>
+        <v>1180008</v>
       </c>
       <c r="B160" t="str">
-        <v>مهر</v>
+        <v>دیلم</v>
       </c>
       <c r="C160" t="str">
-        <v>مهر</v>
+        <v>دیلم</v>
       </c>
       <c r="D160">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>10700022</v>
+        <v>1180009</v>
       </c>
       <c r="B161" t="str">
-        <v>فراشبند</v>
+        <v>جم</v>
       </c>
       <c r="C161" t="str">
-        <v>فراشبند</v>
+        <v>جم</v>
       </c>
       <c r="D161">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="162">
       <c r="A162">
-        <v>10700023</v>
+        <v>1190001</v>
       </c>
       <c r="B162" t="str">
-        <v>پاسارگاد</v>
+        <v>ابهر</v>
       </c>
       <c r="C162" t="str">
-        <v>پاسارگاد</v>
+        <v>ابهر</v>
       </c>
       <c r="D162">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>10700024</v>
+        <v>1190003</v>
       </c>
       <c r="B163" t="str">
-        <v>خنج</v>
+        <v>خدابنده</v>
       </c>
       <c r="C163" t="str">
-        <v>خنج</v>
+        <v>خدابنده</v>
       </c>
       <c r="D163">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>10700025</v>
+        <v>1190004</v>
       </c>
       <c r="B164" t="str">
-        <v>سروستان</v>
+        <v>زنجان</v>
       </c>
       <c r="C164" t="str">
-        <v>سروستان</v>
+        <v>زنجان</v>
       </c>
       <c r="D164">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="165">
       <c r="A165">
-        <v>10700026</v>
+        <v>1190006</v>
       </c>
       <c r="B165" t="str">
-        <v>رستم</v>
+        <v>ایجرود</v>
       </c>
       <c r="C165" t="str">
-        <v>رستم</v>
+        <v>ایجرود</v>
       </c>
       <c r="D165">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>10700027</v>
+        <v>1190007</v>
       </c>
       <c r="B166" t="str">
-        <v>گراش</v>
+        <v>خرمدره</v>
       </c>
       <c r="C166" t="str">
-        <v>گراش</v>
+        <v>خرمدره</v>
       </c>
       <c r="D166">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="167">
       <c r="A167">
-        <v>10700028</v>
+        <v>1190008</v>
       </c>
       <c r="B167" t="str">
-        <v>کوار</v>
+        <v>طارم</v>
       </c>
       <c r="C167" t="str">
-        <v>کوار</v>
+        <v>طارم</v>
       </c>
       <c r="D167">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="168">
       <c r="A168">
-        <v>10700029</v>
+        <v>1190009</v>
       </c>
       <c r="B168" t="str">
-        <v>خرامه</v>
+        <v>ماهنشان</v>
       </c>
       <c r="C168" t="str">
-        <v>خرامه</v>
+        <v>ماهنشان</v>
       </c>
       <c r="D168">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="169">
       <c r="A169">
-        <v>10700030</v>
+        <v>1200001</v>
       </c>
       <c r="B169" t="str">
-        <v>زرقان</v>
+        <v>دامغان</v>
       </c>
       <c r="C169" t="str">
-        <v>زرقان</v>
+        <v>دامغان</v>
       </c>
       <c r="D169">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="170">
       <c r="A170">
-        <v>10700031</v>
+        <v>1200002</v>
       </c>
       <c r="B170" t="str">
-        <v>بیضاء</v>
+        <v>سمنان</v>
       </c>
       <c r="C170" t="str">
-        <v>بیضاء</v>
+        <v>سمنان</v>
       </c>
       <c r="D170">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="171">
       <c r="A171">
-        <v>10700032</v>
+        <v>1200003</v>
       </c>
       <c r="B171" t="str">
-        <v>سرچهان</v>
+        <v>شاهرود</v>
       </c>
       <c r="C171" t="str">
-        <v>سرچهان</v>
+        <v>شاهرود</v>
       </c>
       <c r="D171">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172">
       <c r="A172">
-        <v>10700033</v>
+        <v>1200004</v>
       </c>
       <c r="B172" t="str">
-        <v>کوه چنار</v>
+        <v>گرمسار</v>
       </c>
       <c r="C172" t="str">
-        <v>کوه-چنار</v>
+        <v>گرمسار</v>
       </c>
       <c r="D172">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>10700034</v>
+        <v>1200005</v>
       </c>
       <c r="B173" t="str">
-        <v>خفر</v>
+        <v>مهدی شهر</v>
       </c>
       <c r="C173" t="str">
-        <v>خفر</v>
+        <v>مهدی-شهر</v>
       </c>
       <c r="D173">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="174">
       <c r="A174">
-        <v>10700035</v>
+        <v>1200006</v>
       </c>
       <c r="B174" t="str">
-        <v>بختگان</v>
+        <v>آرادان</v>
       </c>
       <c r="C174" t="str">
-        <v>بختگان</v>
+        <v>آرادان</v>
       </c>
       <c r="D174">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="175">
       <c r="A175">
-        <v>10700036</v>
+        <v>1200007</v>
       </c>
       <c r="B175" t="str">
-        <v>اوز</v>
+        <v>میامی</v>
       </c>
       <c r="C175" t="str">
-        <v>اوز</v>
+        <v>میامی</v>
       </c>
       <c r="D175">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="176">
       <c r="A176">
-        <v>10700037</v>
+        <v>1200008</v>
       </c>
       <c r="B176" t="str">
-        <v>جویم</v>
+        <v>سرخه</v>
       </c>
       <c r="C176" t="str">
-        <v>جویم</v>
+        <v>سرخه</v>
       </c>
       <c r="D176">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="177">
       <c r="A177">
-        <v>10800001</v>
+        <v>1210001</v>
       </c>
       <c r="B177" t="str">
-        <v>بافت</v>
+        <v>اردکان</v>
       </c>
       <c r="C177" t="str">
-        <v>بافت</v>
+        <v>اردکان</v>
       </c>
       <c r="D177">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>10800002</v>
+        <v>1210002</v>
       </c>
       <c r="B178" t="str">
-        <v>بم</v>
+        <v>بافق</v>
       </c>
       <c r="C178" t="str">
-        <v>بم</v>
+        <v>بافق</v>
       </c>
       <c r="D178">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>10800003</v>
+        <v>1210003</v>
       </c>
       <c r="B179" t="str">
-        <v>جیرفت</v>
+        <v>تفت</v>
       </c>
       <c r="C179" t="str">
-        <v>جیرفت</v>
+        <v>تفت</v>
       </c>
       <c r="D179">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>10800004</v>
+        <v>1210004</v>
       </c>
       <c r="B180" t="str">
-        <v>رفسنجان</v>
+        <v>مهریز</v>
       </c>
       <c r="C180" t="str">
-        <v>رفسنجان</v>
+        <v>مهریز</v>
       </c>
       <c r="D180">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="181">
       <c r="A181">
-        <v>10800005</v>
+        <v>1210005</v>
       </c>
       <c r="B181" t="str">
-        <v>زرند</v>
+        <v>یزد</v>
       </c>
       <c r="C181" t="str">
-        <v>زرند</v>
+        <v>یزد</v>
       </c>
       <c r="D181">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="182">
       <c r="A182">
-        <v>10800006</v>
+        <v>1210006</v>
       </c>
       <c r="B182" t="str">
-        <v>سیرجان</v>
+        <v>میبد</v>
       </c>
       <c r="C182" t="str">
-        <v>سیرجان</v>
+        <v>میبد</v>
       </c>
       <c r="D182">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="183">
       <c r="A183">
-        <v>10800007</v>
+        <v>1210007</v>
       </c>
       <c r="B183" t="str">
-        <v>شهربابک</v>
+        <v>ابرکوه</v>
       </c>
       <c r="C183" t="str">
-        <v>شهربابک</v>
+        <v>ابرکوه</v>
       </c>
       <c r="D183">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="184">
       <c r="A184">
-        <v>10800008</v>
+        <v>1210008</v>
       </c>
       <c r="B184" t="str">
-        <v>کرمان</v>
+        <v>اشکذر</v>
       </c>
       <c r="C184" t="str">
-        <v>کرمان</v>
+        <v>اشکذر</v>
       </c>
       <c r="D184">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="185">
       <c r="A185">
-        <v>10800009</v>
+        <v>1210009</v>
       </c>
       <c r="B185" t="str">
-        <v>کهنوج</v>
+        <v>خاتم</v>
       </c>
       <c r="C185" t="str">
-        <v>کهنوج</v>
+        <v>خاتم</v>
       </c>
       <c r="D185">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="186">
       <c r="A186">
-        <v>10800010</v>
+        <v>1220001</v>
       </c>
       <c r="B186" t="str">
-        <v>بردسیر</v>
+        <v>ابوموسی</v>
       </c>
       <c r="C186" t="str">
-        <v>بردسیر</v>
+        <v>ابوموسی</v>
       </c>
       <c r="D186">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="187">
       <c r="A187">
-        <v>10800011</v>
+        <v>1220002</v>
       </c>
       <c r="B187" t="str">
-        <v>راور</v>
+        <v>بندر عباس</v>
       </c>
       <c r="C187" t="str">
-        <v>راور</v>
+        <v>بندر-عباس</v>
       </c>
       <c r="D187">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>10800012</v>
+        <v>1220003</v>
       </c>
       <c r="B188" t="str">
-        <v>عنبرآباد</v>
+        <v>بندر لنگه</v>
       </c>
       <c r="C188" t="str">
-        <v>عنبرآباد</v>
+        <v>بندر-لنگه</v>
       </c>
       <c r="D188">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>10800013</v>
+        <v>1220004</v>
       </c>
       <c r="B189" t="str">
-        <v>منوجان</v>
+        <v>قشم</v>
       </c>
       <c r="C189" t="str">
-        <v>منوجان</v>
+        <v>قشم</v>
       </c>
       <c r="D189">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="190">
       <c r="A190">
-        <v>10800014</v>
+        <v>1220005</v>
       </c>
       <c r="B190" t="str">
-        <v>کوهبنان</v>
+        <v>میناب</v>
       </c>
       <c r="C190" t="str">
-        <v>کوهبنان</v>
+        <v>میناب</v>
       </c>
       <c r="D190">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>10800015</v>
+        <v>1220006</v>
       </c>
       <c r="B191" t="str">
-        <v>رودبارجنوب</v>
+        <v>جاسک</v>
       </c>
       <c r="C191" t="str">
-        <v>رودبارجنوب</v>
+        <v>جاسک</v>
       </c>
       <c r="D191">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>10800016</v>
+        <v>1220007</v>
       </c>
       <c r="B192" t="str">
-        <v>قلعه گنج</v>
+        <v>رودان</v>
       </c>
       <c r="C192" t="str">
-        <v>قلعه-گنج</v>
+        <v>رودان</v>
       </c>
       <c r="D192">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>10800017</v>
+        <v>1220008</v>
       </c>
       <c r="B193" t="str">
-        <v>ریگان</v>
+        <v>حاجی آباد</v>
       </c>
       <c r="C193" t="str">
-        <v>ریگان</v>
+        <v>حاجی-آباد</v>
       </c>
       <c r="D193">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="194">
       <c r="A194">
-        <v>10800018</v>
+        <v>1220009</v>
       </c>
       <c r="B194" t="str">
-        <v>رابر</v>
+        <v>بستک</v>
       </c>
       <c r="C194" t="str">
-        <v>رابر</v>
+        <v>بستک</v>
       </c>
       <c r="D194">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>10800019</v>
+        <v>1230001</v>
       </c>
       <c r="B195" t="str">
-        <v>فهرج</v>
+        <v>تهران</v>
       </c>
       <c r="C195" t="str">
-        <v>فهرج</v>
+        <v>تهران</v>
       </c>
       <c r="D195">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>10800020</v>
+        <v>1230002</v>
       </c>
       <c r="B196" t="str">
-        <v>انار</v>
+        <v>دماوند</v>
       </c>
       <c r="C196" t="str">
-        <v>انار</v>
+        <v>دماوند</v>
       </c>
       <c r="D196">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>10800021</v>
+        <v>1230003</v>
       </c>
       <c r="B197" t="str">
-        <v>نرماشیر</v>
+        <v>ری</v>
       </c>
       <c r="C197" t="str">
-        <v>نرماشیر</v>
+        <v>ری</v>
       </c>
       <c r="D197">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>10800022</v>
+        <v>1230004</v>
       </c>
       <c r="B198" t="str">
-        <v>فاریاب</v>
+        <v>شمیرانات</v>
       </c>
       <c r="C198" t="str">
-        <v>فاریاب</v>
+        <v>شمیرانات</v>
       </c>
       <c r="D198">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>10800023</v>
+        <v>1230006</v>
       </c>
       <c r="B199" t="str">
-        <v>ارزوییه</v>
+        <v>ورامین</v>
       </c>
       <c r="C199" t="str">
-        <v>ارزوییه</v>
+        <v>ورامین</v>
       </c>
       <c r="D199">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>10800024</v>
+        <v>1230009</v>
       </c>
       <c r="B200" t="str">
-        <v>گنبکی</v>
+        <v>شهریار</v>
       </c>
       <c r="C200" t="str">
-        <v>گنبکی</v>
+        <v>شهریار</v>
       </c>
       <c r="D200">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>10800025</v>
+        <v>1240001</v>
       </c>
       <c r="B201" t="str">
-        <v>جازموریان</v>
+        <v>اردبیل</v>
       </c>
       <c r="C201" t="str">
-        <v>جازموریان</v>
+        <v>اردبیل</v>
       </c>
       <c r="D201">
-        <v>108</v>
+        <v>124</v>
       </c>
     </row>
     <row r="202">
       <c r="A202">
-        <v>10900004</v>
+        <v>1240002</v>
       </c>
       <c r="B202" t="str">
-        <v>تایباد</v>
+        <v>بیله سوار</v>
       </c>
       <c r="C202" t="str">
-        <v>تایباد</v>
+        <v>بیله-سوار</v>
       </c>
       <c r="D202">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>10900005</v>
+        <v>1240003</v>
       </c>
       <c r="B203" t="str">
-        <v>تربت حیدریه</v>
+        <v>خلخال</v>
       </c>
       <c r="C203" t="str">
-        <v>تربت-حیدریه</v>
+        <v>خلخال</v>
       </c>
       <c r="D203">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>10900006</v>
+        <v>1240004</v>
       </c>
       <c r="B204" t="str">
-        <v>تربت جام</v>
+        <v>مشگین شهر</v>
       </c>
       <c r="C204" t="str">
-        <v>تربت-جام</v>
+        <v>مشگین-شهر</v>
       </c>
       <c r="D204">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>10900007</v>
+        <v>1240005</v>
       </c>
       <c r="B205" t="str">
-        <v>درگز</v>
+        <v>گرمی</v>
       </c>
       <c r="C205" t="str">
-        <v>درگز</v>
+        <v>گرمی</v>
       </c>
       <c r="D205">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>10900008</v>
+        <v>1240006</v>
       </c>
       <c r="B206" t="str">
-        <v>سبزوار</v>
+        <v>پارس آباد</v>
       </c>
       <c r="C206" t="str">
-        <v>سبزوار</v>
+        <v>پارس-آباد</v>
       </c>
       <c r="D206">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>10900013</v>
+        <v>1240007</v>
       </c>
       <c r="B207" t="str">
-        <v>قوچان</v>
+        <v>کوثر</v>
       </c>
       <c r="C207" t="str">
-        <v>قوچان</v>
+        <v>کوثر</v>
       </c>
       <c r="D207">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>10900014</v>
+        <v>1240008</v>
       </c>
       <c r="B208" t="str">
-        <v>کاشمر</v>
+        <v>نمین</v>
       </c>
       <c r="C208" t="str">
-        <v>کاشمر</v>
+        <v>نمین</v>
       </c>
       <c r="D208">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>10900015</v>
+        <v>1240009</v>
       </c>
       <c r="B209" t="str">
-        <v>گناباد</v>
+        <v>نیر</v>
       </c>
       <c r="C209" t="str">
-        <v>گناباد</v>
+        <v>نیر</v>
       </c>
       <c r="D209">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>10900016</v>
+        <v>1250001</v>
       </c>
       <c r="B210" t="str">
-        <v>مشهد</v>
+        <v>قم</v>
       </c>
       <c r="C210" t="str">
-        <v>مشهد</v>
+        <v>قم</v>
       </c>
       <c r="D210">
-        <v>109</v>
+        <v>125</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>10900017</v>
+        <v>1250002</v>
       </c>
       <c r="B211" t="str">
-        <v>نیشابور</v>
+        <v>جعفرآباد</v>
       </c>
       <c r="C211" t="str">
-        <v>نیشابور</v>
+        <v>جعفرآباد</v>
       </c>
       <c r="D211">
-        <v>109</v>
+        <v>125</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>10900018</v>
+        <v>1250003</v>
       </c>
       <c r="B212" t="str">
-        <v>چناران</v>
+        <v>کهک</v>
       </c>
       <c r="C212" t="str">
-        <v>چناران</v>
+        <v>کهک</v>
       </c>
       <c r="D212">
-        <v>109</v>
+        <v>125</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>10900019</v>
+        <v>1260001</v>
       </c>
       <c r="B213" t="str">
-        <v>خواف</v>
+        <v>بویین زهرا</v>
       </c>
       <c r="C213" t="str">
-        <v>خواف</v>
+        <v>بویین-زهرا</v>
       </c>
       <c r="D213">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>10900020</v>
+        <v>1260002</v>
       </c>
       <c r="B214" t="str">
-        <v>سرخس</v>
+        <v>تاکستان</v>
       </c>
       <c r="C214" t="str">
-        <v>سرخس</v>
+        <v>تاکستان</v>
       </c>
       <c r="D214">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>10900022</v>
+        <v>1260003</v>
       </c>
       <c r="B215" t="str">
-        <v>فریمان</v>
+        <v>قزوین</v>
       </c>
       <c r="C215" t="str">
-        <v>فریمان</v>
+        <v>قزوین</v>
       </c>
       <c r="D215">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>10900023</v>
+        <v>1260004</v>
       </c>
       <c r="B216" t="str">
-        <v>بردسکن</v>
+        <v>آبیک</v>
       </c>
       <c r="C216" t="str">
-        <v>بردسکن</v>
+        <v>آبیک</v>
       </c>
       <c r="D216">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>10900027</v>
+        <v>1260005</v>
       </c>
       <c r="B217" t="str">
-        <v>رشتخوار</v>
+        <v>البرز</v>
       </c>
       <c r="C217" t="str">
-        <v>رشتخوار</v>
+        <v>البرز</v>
       </c>
       <c r="D217">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>10900028</v>
+        <v>1260006</v>
       </c>
       <c r="B218" t="str">
-        <v>کلات</v>
+        <v>آوج</v>
       </c>
       <c r="C218" t="str">
-        <v>کلات</v>
+        <v>آوج</v>
       </c>
       <c r="D218">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>10900029</v>
+        <v>1270001</v>
       </c>
       <c r="B219" t="str">
-        <v>خلیل آباد</v>
+        <v>بندرگز</v>
       </c>
       <c r="C219" t="str">
-        <v>خلیل-آباد</v>
+        <v>بندرگز</v>
       </c>
       <c r="D219">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>10900030</v>
+        <v>1270002</v>
       </c>
       <c r="B220" t="str">
-        <v>مه ولات</v>
+        <v>ترکمن</v>
       </c>
       <c r="C220" t="str">
-        <v>مه-ولات</v>
+        <v>ترکمن</v>
       </c>
       <c r="D220">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="221">
       <c r="A221">
-        <v>10900031</v>
+        <v>1270003</v>
       </c>
       <c r="B221" t="str">
-        <v>بجستان</v>
+        <v>علی آباد کتول</v>
       </c>
       <c r="C221" t="str">
-        <v>بجستان</v>
+        <v>علی-آباد-کتول</v>
       </c>
       <c r="D221">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="222">
       <c r="A222">
-        <v>10900032</v>
+        <v>1270004</v>
       </c>
       <c r="B222" t="str">
-        <v>طرقبه شاندیز</v>
+        <v>کردکوی</v>
       </c>
       <c r="C222" t="str">
-        <v>طرقبه-شاندیز</v>
+        <v>کردکوی</v>
       </c>
       <c r="D222">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>10900033</v>
+        <v>1270005</v>
       </c>
       <c r="B223" t="str">
-        <v>فیروزه</v>
+        <v>گرگان</v>
       </c>
       <c r="C223" t="str">
-        <v>فیروزه</v>
+        <v>گرگان</v>
       </c>
       <c r="D223">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>10900034</v>
+        <v>1270006</v>
       </c>
       <c r="B224" t="str">
-        <v>جغتای</v>
+        <v>گنبدکاووس</v>
       </c>
       <c r="C224" t="str">
-        <v>جغتای</v>
+        <v>گنبدکاووس</v>
       </c>
       <c r="D224">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="225">
       <c r="A225">
-        <v>10900035</v>
+        <v>1270007</v>
       </c>
       <c r="B225" t="str">
-        <v>زاوه</v>
+        <v>مینودشت</v>
       </c>
       <c r="C225" t="str">
-        <v>زاوه</v>
+        <v>مینودشت</v>
       </c>
       <c r="D225">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>10900036</v>
+        <v>1270008</v>
       </c>
       <c r="B226" t="str">
-        <v>جوین</v>
+        <v>آق قلا</v>
       </c>
       <c r="C226" t="str">
-        <v>جوین</v>
+        <v>آق-قلا</v>
       </c>
       <c r="D226">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>10900037</v>
+        <v>1270009</v>
       </c>
       <c r="B227" t="str">
-        <v>باخرز</v>
+        <v>کلاله</v>
       </c>
       <c r="C227" t="str">
-        <v>باخرز</v>
+        <v>کلاله</v>
       </c>
       <c r="D227">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>10900038</v>
+        <v>1280001</v>
       </c>
       <c r="B228" t="str">
-        <v>خوشاب</v>
+        <v>اسفراین</v>
       </c>
       <c r="C228" t="str">
-        <v>خوشاب</v>
+        <v>اسفراین</v>
       </c>
       <c r="D228">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>10900039</v>
+        <v>1280002</v>
       </c>
       <c r="B229" t="str">
-        <v>داورزن</v>
+        <v>بجنورد</v>
       </c>
       <c r="C229" t="str">
-        <v>داورزن</v>
+        <v>بجنورد</v>
       </c>
       <c r="D229">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>10900040</v>
+        <v>1280003</v>
       </c>
       <c r="B230" t="str">
-        <v>صالح آباد</v>
+        <v>جاجرم</v>
       </c>
       <c r="C230" t="str">
-        <v>صالح-آباد</v>
+        <v>جاجرم</v>
       </c>
       <c r="D230">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>10900041</v>
+        <v>1280004</v>
       </c>
       <c r="B231" t="str">
-        <v>کوهسرخ</v>
+        <v>شیروان</v>
       </c>
       <c r="C231" t="str">
-        <v>کوهسرخ</v>
+        <v>شیروان</v>
       </c>
       <c r="D231">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>10900042</v>
+        <v>1280005</v>
       </c>
       <c r="B232" t="str">
-        <v>زبرخان</v>
+        <v>فاروج</v>
       </c>
       <c r="C232" t="str">
-        <v>زبرخان</v>
+        <v>فاروج</v>
       </c>
       <c r="D232">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>10900043</v>
+        <v>1280006</v>
       </c>
       <c r="B233" t="str">
-        <v>ششتمد</v>
+        <v>سملقان</v>
       </c>
       <c r="C233" t="str">
-        <v>ششتمد</v>
+        <v>سملقان</v>
       </c>
       <c r="D233">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>10900044</v>
+        <v>1280007</v>
       </c>
       <c r="B234" t="str">
-        <v>گلبهار</v>
+        <v>گرمه</v>
       </c>
       <c r="C234" t="str">
-        <v>گلبهار</v>
+        <v>گرمه</v>
       </c>
       <c r="D234">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="235">
       <c r="A235">
-        <v>10900045</v>
+        <v>1280008</v>
       </c>
       <c r="B235" t="str">
-        <v>میان جلگه</v>
+        <v>راز و جرگلان</v>
       </c>
       <c r="C235" t="str">
-        <v>میان-جلگه</v>
+        <v>راز-و-جرگلان</v>
       </c>
       <c r="D235">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>11000001</v>
+        <v>1280009</v>
       </c>
       <c r="B236" t="str">
-        <v>اردستان</v>
+        <v>بام و صفی آباد</v>
       </c>
       <c r="C236" t="str">
-        <v>اردستان</v>
+        <v>بام-و-صفی-آباد</v>
       </c>
       <c r="D236">
-        <v>110</v>
+        <v>128</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>11000002</v>
+        <v>1290001</v>
       </c>
       <c r="B237" t="str">
-        <v>اصفهان</v>
+        <v>بیرجند</v>
       </c>
       <c r="C237" t="str">
-        <v>اصفهان</v>
+        <v>بیرجند</v>
       </c>
       <c r="D237">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>11000003</v>
+        <v>1290002</v>
       </c>
       <c r="B238" t="str">
-        <v>خمینی شهر</v>
+        <v>درمیان</v>
       </c>
       <c r="C238" t="str">
-        <v>خمینی-شهر</v>
+        <v>درمیان</v>
       </c>
       <c r="D238">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>11000004</v>
+        <v>1290003</v>
       </c>
       <c r="B239" t="str">
-        <v>خوانسار</v>
+        <v>سربیشه</v>
       </c>
       <c r="C239" t="str">
-        <v>خوانسار</v>
+        <v>سربیشه</v>
       </c>
       <c r="D239">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>11000005</v>
+        <v>1290004</v>
       </c>
       <c r="B240" t="str">
-        <v>سمیرم</v>
+        <v>قاینات</v>
       </c>
       <c r="C240" t="str">
-        <v>سمیرم</v>
+        <v>قاینات</v>
       </c>
       <c r="D240">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>11000006</v>
+        <v>1290005</v>
       </c>
       <c r="B241" t="str">
-        <v>فریدن</v>
+        <v>نهبندان</v>
       </c>
       <c r="C241" t="str">
-        <v>فریدن</v>
+        <v>نهبندان</v>
       </c>
       <c r="D241">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>11000007</v>
+        <v>1290006</v>
       </c>
       <c r="B242" t="str">
-        <v>فریدونشهر</v>
+        <v>سرایان</v>
       </c>
       <c r="C242" t="str">
-        <v>فریدونشهر</v>
+        <v>سرایان</v>
       </c>
       <c r="D242">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>11000008</v>
+        <v>1290007</v>
       </c>
       <c r="B243" t="str">
-        <v>فلاورجان</v>
+        <v>فردوس</v>
       </c>
       <c r="C243" t="str">
-        <v>فلاورجان</v>
+        <v>فردوس</v>
       </c>
       <c r="D243">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>11000009</v>
+        <v>1290008</v>
       </c>
       <c r="B244" t="str">
-        <v>شهرضا</v>
+        <v>بشرویه</v>
       </c>
       <c r="C244" t="str">
-        <v>شهرضا</v>
+        <v>بشرویه</v>
       </c>
       <c r="D244">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>11000010</v>
+        <v>1290009</v>
       </c>
       <c r="B245" t="str">
-        <v>کاشان</v>
+        <v>زیرکوه</v>
       </c>
       <c r="C245" t="str">
-        <v>کاشان</v>
+        <v>زیرکوه</v>
       </c>
       <c r="D245">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>11000011</v>
+        <v>1300001</v>
       </c>
       <c r="B246" t="str">
-        <v>گلپایگان</v>
+        <v>کرج</v>
       </c>
       <c r="C246" t="str">
-        <v>گلپایگان</v>
+        <v>کرج</v>
       </c>
       <c r="D246">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="247">
       <c r="A247">
-        <v>11000012</v>
+        <v>1300002</v>
       </c>
       <c r="B247" t="str">
-        <v>لنجان</v>
+        <v>ساوجبلاغ</v>
       </c>
       <c r="C247" t="str">
-        <v>لنجان</v>
+        <v>ساوجبلاغ</v>
       </c>
       <c r="D247">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="248">
       <c r="A248">
-        <v>11000013</v>
+        <v>1300003</v>
       </c>
       <c r="B248" t="str">
-        <v>نایین</v>
+        <v>نظرآباد</v>
       </c>
       <c r="C248" t="str">
-        <v>نایین</v>
+        <v>نظرآباد</v>
       </c>
       <c r="D248">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="249">
       <c r="A249">
-        <v>11000014</v>
+        <v>1300004</v>
       </c>
       <c r="B249" t="str">
-        <v>نجف آباد</v>
+        <v>طالقان</v>
       </c>
       <c r="C249" t="str">
-        <v>نجف-آباد</v>
+        <v>طالقان</v>
       </c>
       <c r="D249">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="250">
       <c r="A250">
-        <v>11000015</v>
+        <v>1300005</v>
       </c>
       <c r="B250" t="str">
-        <v>نطنز</v>
+        <v>اشتهارد</v>
       </c>
       <c r="C250" t="str">
-        <v>نطنز</v>
+        <v>اشتهارد</v>
       </c>
       <c r="D250">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="251">
       <c r="A251">
-        <v>11000016</v>
+        <v>1300006</v>
       </c>
       <c r="B251" t="str">
-        <v>شاهین شهرو میمه</v>
+        <v>فردیس</v>
       </c>
       <c r="C251" t="str">
-        <v>شاهین-شهرو-میمه</v>
+        <v>فردیس</v>
       </c>
       <c r="D251">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="252">
       <c r="A252">
-        <v>11000017</v>
+        <v>1300007</v>
       </c>
       <c r="B252" t="str">
-        <v>مبارکه</v>
+        <v>چهارباغ</v>
       </c>
       <c r="C252" t="str">
-        <v>مبارکه</v>
+        <v>چهارباغ</v>
       </c>
       <c r="D252">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="253">
       <c r="A253">
-        <v>11000018</v>
+        <v>10000010</v>
       </c>
       <c r="B253" t="str">
-        <v>آران و بیدگل</v>
+        <v>زرندیه</v>
       </c>
       <c r="C253" t="str">
-        <v>آران-و-بیدگل</v>
+        <v>زرندیه</v>
       </c>
       <c r="D253">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="254">
       <c r="A254">
-        <v>11000019</v>
+        <v>10000011</v>
       </c>
       <c r="B254" t="str">
-        <v>تیران وکرون</v>
+        <v>کمیجان</v>
       </c>
       <c r="C254" t="str">
-        <v>تیران-وکرون</v>
+        <v>کمیجان</v>
       </c>
       <c r="D254">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="255">
       <c r="A255">
-        <v>11000020</v>
+        <v>10000012</v>
       </c>
       <c r="B255" t="str">
-        <v>چادگان</v>
+        <v>خنداب</v>
       </c>
       <c r="C255" t="str">
-        <v>چادگان</v>
+        <v>خنداب</v>
       </c>
       <c r="D255">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="256">
       <c r="A256">
-        <v>11000021</v>
+        <v>10000013</v>
       </c>
       <c r="B256" t="str">
-        <v>دهاقان</v>
+        <v>فراهان</v>
       </c>
       <c r="C256" t="str">
-        <v>دهاقان</v>
+        <v>فراهان</v>
       </c>
       <c r="D256">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="257">
       <c r="A257">
-        <v>11000022</v>
+        <v>10100010</v>
       </c>
       <c r="B257" t="str">
-        <v>برخوار</v>
+        <v>لنگرود</v>
       </c>
       <c r="C257" t="str">
-        <v>برخوار</v>
+        <v>لنگرود</v>
       </c>
       <c r="D257">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="258">
       <c r="A258">
-        <v>11000023</v>
+        <v>10100011</v>
       </c>
       <c r="B258" t="str">
-        <v>خور و بیابانک</v>
+        <v>لاهیجان</v>
       </c>
       <c r="C258" t="str">
-        <v>خور-و-بیابانک</v>
+        <v>لاهیجان</v>
       </c>
       <c r="D258">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="259">
       <c r="A259">
-        <v>11000024</v>
+        <v>10100012</v>
       </c>
       <c r="B259" t="str">
-        <v>بویین و میاندشت</v>
+        <v>شفت</v>
       </c>
       <c r="C259" t="str">
-        <v>بویین-و-میاندشت</v>
+        <v>شفت</v>
       </c>
       <c r="D259">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="260">
       <c r="A260">
-        <v>11000025</v>
+        <v>10100013</v>
       </c>
       <c r="B260" t="str">
-        <v>کوهپایه</v>
+        <v>املش</v>
       </c>
       <c r="C260" t="str">
-        <v>کوهپایه</v>
+        <v>املش</v>
       </c>
       <c r="D260">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="261">
       <c r="A261">
-        <v>11000026</v>
+        <v>10100014</v>
       </c>
       <c r="B261" t="str">
-        <v>جرقویه</v>
+        <v>رضوانشهر</v>
       </c>
       <c r="C261" t="str">
-        <v>جرقویه</v>
+        <v>رضوانشهر</v>
       </c>
       <c r="D261">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="262">
       <c r="A262">
-        <v>11000027</v>
+        <v>10100015</v>
       </c>
       <c r="B262" t="str">
-        <v>ورزنه</v>
+        <v>سیاهکل</v>
       </c>
       <c r="C262" t="str">
-        <v>ورزنه</v>
+        <v>سیاهکل</v>
       </c>
       <c r="D262">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="263">
       <c r="A263">
-        <v>11000028</v>
+        <v>10100016</v>
       </c>
       <c r="B263" t="str">
-        <v>هرند</v>
+        <v>ماسال</v>
       </c>
       <c r="C263" t="str">
-        <v>هرند</v>
+        <v>ماسال</v>
       </c>
       <c r="D263">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="264">
       <c r="A264">
-        <v>11100001</v>
+        <v>10100017</v>
       </c>
       <c r="B264" t="str">
-        <v>ایرانشهر</v>
+        <v>خمام</v>
       </c>
       <c r="C264" t="str">
-        <v>ایرانشهر</v>
+        <v>خمام</v>
       </c>
       <c r="D264">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
     <row r="265">
       <c r="A265">
-        <v>11100002</v>
+        <v>10200010</v>
       </c>
       <c r="B265" t="str">
-        <v>چاه بهار</v>
+        <v>قایم شهر</v>
       </c>
       <c r="C265" t="str">
-        <v>چاه-بهار</v>
+        <v>قایم-شهر</v>
       </c>
       <c r="D265">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="266">
       <c r="A266">
-        <v>11100003</v>
+        <v>10200014</v>
       </c>
       <c r="B266" t="str">
-        <v>خاش</v>
+        <v>نور</v>
       </c>
       <c r="C266" t="str">
-        <v>خاش</v>
+        <v>نور</v>
       </c>
       <c r="D266">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="267">
       <c r="A267">
-        <v>11100004</v>
+        <v>10200015</v>
       </c>
       <c r="B267" t="str">
-        <v>زابل</v>
+        <v>نوشهر</v>
       </c>
       <c r="C267" t="str">
-        <v>زابل</v>
+        <v>نوشهر</v>
       </c>
       <c r="D267">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="268">
       <c r="A268">
-        <v>11100005</v>
+        <v>10200016</v>
       </c>
       <c r="B268" t="str">
-        <v>زاهدان</v>
+        <v>بابلسر</v>
       </c>
       <c r="C268" t="str">
-        <v>زاهدان</v>
+        <v>بابلسر</v>
       </c>
       <c r="D268">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="269">
       <c r="A269">
-        <v>11100006</v>
+        <v>10200018</v>
       </c>
       <c r="B269" t="str">
-        <v>سراوان</v>
+        <v>محمودآباد</v>
       </c>
       <c r="C269" t="str">
-        <v>سراوان</v>
+        <v>محمودآباد</v>
       </c>
       <c r="D269">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="270">
       <c r="A270">
-        <v>11100007</v>
+        <v>10200019</v>
       </c>
       <c r="B270" t="str">
-        <v>نیک شهر</v>
+        <v>نکا</v>
       </c>
       <c r="C270" t="str">
-        <v>نیک-شهر</v>
+        <v>نکا</v>
       </c>
       <c r="D270">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="271">
       <c r="A271">
-        <v>11100008</v>
+        <v>10200020</v>
       </c>
       <c r="B271" t="str">
-        <v>راسک</v>
+        <v>چالوس</v>
       </c>
       <c r="C271" t="str">
-        <v>راسک</v>
+        <v>چالوس</v>
       </c>
       <c r="D271">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="272">
       <c r="A272">
-        <v>11100009</v>
+        <v>10200021</v>
       </c>
       <c r="B272" t="str">
-        <v>کنارک</v>
+        <v>جویبار</v>
       </c>
       <c r="C272" t="str">
-        <v>کنارک</v>
+        <v>جویبار</v>
       </c>
       <c r="D272">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="273">
       <c r="A273">
-        <v>11100010</v>
+        <v>10200022</v>
       </c>
       <c r="B273" t="str">
-        <v>زهک</v>
+        <v>گلوگاه</v>
       </c>
       <c r="C273" t="str">
-        <v>زهک</v>
+        <v>گلوگاه</v>
       </c>
       <c r="D273">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="274">
       <c r="A274">
-        <v>11100011</v>
+        <v>10200023</v>
       </c>
       <c r="B274" t="str">
-        <v>هیرمند</v>
+        <v>فریدونکنار</v>
       </c>
       <c r="C274" t="str">
-        <v>هیرمند</v>
+        <v>فریدونکنار</v>
       </c>
       <c r="D274">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="275">
       <c r="A275">
-        <v>11100012</v>
+        <v>10200024</v>
       </c>
       <c r="B275" t="str">
-        <v>دلگان</v>
+        <v>عباس آباد</v>
       </c>
       <c r="C275" t="str">
-        <v>دلگان</v>
+        <v>عباس-آباد</v>
       </c>
       <c r="D275">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="276">
       <c r="A276">
-        <v>11100013</v>
+        <v>10200025</v>
       </c>
       <c r="B276" t="str">
-        <v>مهرستان</v>
+        <v>میاندورود</v>
       </c>
       <c r="C276" t="str">
-        <v>مهرستان</v>
+        <v>میاندورود</v>
       </c>
       <c r="D276">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="277">
       <c r="A277">
-        <v>11100014</v>
+        <v>10200026</v>
       </c>
       <c r="B277" t="str">
-        <v>سیب و سوران</v>
+        <v>سیمرغ</v>
       </c>
       <c r="C277" t="str">
-        <v>سیب-و-سوران</v>
+        <v>سیمرغ</v>
       </c>
       <c r="D277">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="278">
       <c r="A278">
-        <v>11100015</v>
+        <v>10200027</v>
       </c>
       <c r="B278" t="str">
-        <v>نیمروز</v>
+        <v>سوادکوه شمالی</v>
       </c>
       <c r="C278" t="str">
-        <v>نیمروز</v>
+        <v>سوادکوه-شمالی</v>
       </c>
       <c r="D278">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="279">
       <c r="A279">
-        <v>11100016</v>
+        <v>10200028</v>
       </c>
       <c r="B279" t="str">
-        <v>هامون</v>
+        <v>کلاردشت</v>
       </c>
       <c r="C279" t="str">
-        <v>هامون</v>
+        <v>کلاردشت</v>
       </c>
       <c r="D279">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="280">
       <c r="A280">
-        <v>11100017</v>
+        <v>10300010</v>
       </c>
       <c r="B280" t="str">
-        <v>میرجاوه</v>
+        <v>میانه</v>
       </c>
       <c r="C280" t="str">
-        <v>میرجاوه</v>
+        <v>میانه</v>
       </c>
       <c r="D280">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="281">
       <c r="A281">
-        <v>11100018</v>
+        <v>10300011</v>
       </c>
       <c r="B281" t="str">
-        <v>قصرقند</v>
+        <v>هشترود</v>
       </c>
       <c r="C281" t="str">
-        <v>قصرقند</v>
+        <v>هشترود</v>
       </c>
       <c r="D281">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="282">
       <c r="A282">
-        <v>11100019</v>
+        <v>10300012</v>
       </c>
       <c r="B282" t="str">
-        <v>فنوج</v>
+        <v>بناب</v>
       </c>
       <c r="C282" t="str">
-        <v>فنوج</v>
+        <v>بناب</v>
       </c>
       <c r="D282">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="283">
       <c r="A283">
-        <v>11100020</v>
+        <v>10300013</v>
       </c>
       <c r="B283" t="str">
-        <v>بمپور</v>
+        <v>بستان آباد</v>
       </c>
       <c r="C283" t="str">
-        <v>بمپور</v>
+        <v>بستان-آباد</v>
       </c>
       <c r="D283">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="284">
       <c r="A284">
-        <v>11100021</v>
+        <v>10300014</v>
       </c>
       <c r="B284" t="str">
-        <v>تفتان</v>
+        <v>شبستر</v>
       </c>
       <c r="C284" t="str">
-        <v>تفتان</v>
+        <v>شبستر</v>
       </c>
       <c r="D284">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="285">
       <c r="A285">
-        <v>11100022</v>
+        <v>10300015</v>
       </c>
       <c r="B285" t="str">
-        <v>دشتیاری</v>
+        <v>کلیبر</v>
       </c>
       <c r="C285" t="str">
-        <v>دشتیاری</v>
+        <v>کلیبر</v>
       </c>
       <c r="D285">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="286">
       <c r="A286">
-        <v>11100023</v>
+        <v>10300016</v>
       </c>
       <c r="B286" t="str">
-        <v>سرباز</v>
+        <v>هریس</v>
       </c>
       <c r="C286" t="str">
-        <v>سرباز</v>
+        <v>هریس</v>
       </c>
       <c r="D286">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="287">
       <c r="A287">
-        <v>11100024</v>
+        <v>10300019</v>
       </c>
       <c r="B287" t="str">
-        <v>گلشن</v>
+        <v>جلفا</v>
       </c>
       <c r="C287" t="str">
-        <v>گلشن</v>
+        <v>جلفا</v>
       </c>
       <c r="D287">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="288">
       <c r="A288">
-        <v>11100025</v>
+        <v>10300020</v>
       </c>
       <c r="B288" t="str">
-        <v>لاشار</v>
+        <v>ملکان</v>
       </c>
       <c r="C288" t="str">
-        <v>لاشار</v>
+        <v>ملکان</v>
       </c>
       <c r="D288">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="289">
       <c r="A289">
-        <v>11100026</v>
+        <v>10300021</v>
       </c>
       <c r="B289" t="str">
-        <v>زرآباد</v>
+        <v>آذرشهر</v>
       </c>
       <c r="C289" t="str">
-        <v>زرآباد</v>
+        <v>آذرشهر</v>
       </c>
       <c r="D289">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="290">
       <c r="A290">
-        <v>11200001</v>
+        <v>10300022</v>
       </c>
       <c r="B290" t="str">
-        <v>بانه</v>
+        <v>اسکو</v>
       </c>
       <c r="C290" t="str">
-        <v>بانه</v>
+        <v>اسکو</v>
       </c>
       <c r="D290">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="291">
       <c r="A291">
-        <v>11200002</v>
+        <v>10300023</v>
       </c>
       <c r="B291" t="str">
-        <v>بیجار</v>
+        <v>چاراویماق</v>
       </c>
       <c r="C291" t="str">
-        <v>بیجار</v>
+        <v>چاراویماق</v>
       </c>
       <c r="D291">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="292">
       <c r="A292">
-        <v>11200003</v>
+        <v>10300024</v>
       </c>
       <c r="B292" t="str">
-        <v>سقز</v>
+        <v>ورزقان</v>
       </c>
       <c r="C292" t="str">
-        <v>سقز</v>
+        <v>ورزقان</v>
       </c>
       <c r="D292">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="293">
       <c r="A293">
-        <v>11200004</v>
+        <v>10300025</v>
       </c>
       <c r="B293" t="str">
-        <v>سنندج</v>
+        <v>عجب شیر</v>
       </c>
       <c r="C293" t="str">
-        <v>سنندج</v>
+        <v>عجب-شیر</v>
       </c>
       <c r="D293">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="294">
       <c r="A294">
-        <v>11200005</v>
+        <v>10300026</v>
       </c>
       <c r="B294" t="str">
-        <v>قروه</v>
+        <v>خدا آفرین</v>
       </c>
       <c r="C294" t="str">
-        <v>قروه</v>
+        <v>خداآفرین</v>
       </c>
       <c r="D294">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="295">
       <c r="A295">
-        <v>11200006</v>
+        <v>10300027</v>
       </c>
       <c r="B295" t="str">
-        <v>مریوان</v>
+        <v>هوراند</v>
       </c>
       <c r="C295" t="str">
-        <v>مریوان</v>
+        <v>هوراند</v>
       </c>
       <c r="D295">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="296">
       <c r="A296">
-        <v>11200007</v>
+        <v>10300028</v>
       </c>
       <c r="B296" t="str">
-        <v>دیواندره</v>
+        <v>لیلان</v>
       </c>
       <c r="C296" t="str">
-        <v>دیواندره</v>
+        <v>لیلان</v>
       </c>
       <c r="D296">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="297">
       <c r="A297">
-        <v>11200008</v>
+        <v>10300029</v>
       </c>
       <c r="B297" t="str">
-        <v>کامیاران</v>
+        <v>ترکمانچای</v>
       </c>
       <c r="C297" t="str">
-        <v>کامیاران</v>
+        <v>ترکمانچای</v>
       </c>
       <c r="D297">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="298">
       <c r="A298">
-        <v>11200009</v>
+        <v>10400010</v>
       </c>
       <c r="B298" t="str">
-        <v>سروآباد</v>
+        <v>بوکان</v>
       </c>
       <c r="C298" t="str">
-        <v>سروآباد</v>
+        <v>بوکان</v>
       </c>
       <c r="D298">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="299">
       <c r="A299">
-        <v>11200010</v>
+        <v>10400011</v>
       </c>
       <c r="B299" t="str">
-        <v>دهگلان</v>
+        <v>شاهین دژ</v>
       </c>
       <c r="C299" t="str">
-        <v>دهگلان</v>
+        <v>شاهین-دژ</v>
       </c>
       <c r="D299">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="300">
       <c r="A300">
-        <v>11300001</v>
+        <v>10400012</v>
       </c>
       <c r="B300" t="str">
-        <v>تویسرکان</v>
+        <v>تکاب</v>
       </c>
       <c r="C300" t="str">
-        <v>تویسرکان</v>
+        <v>تکاب</v>
       </c>
       <c r="D300">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="301">
       <c r="A301">
-        <v>11300002</v>
+        <v>10400013</v>
       </c>
       <c r="B301" t="str">
-        <v>ملایر</v>
+        <v>اشنویه</v>
       </c>
       <c r="C301" t="str">
-        <v>ملایر</v>
+        <v>اشنویه</v>
       </c>
       <c r="D301">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="302">
       <c r="A302">
-        <v>11300003</v>
+        <v>10400014</v>
       </c>
       <c r="B302" t="str">
-        <v>نهاوند</v>
+        <v>چالدران</v>
       </c>
       <c r="C302" t="str">
-        <v>نهاوند</v>
+        <v>چالدران</v>
       </c>
       <c r="D302">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="303">
       <c r="A303">
-        <v>11300004</v>
+        <v>10400015</v>
       </c>
       <c r="B303" t="str">
-        <v>همدان</v>
+        <v>پلدشت</v>
       </c>
       <c r="C303" t="str">
-        <v>همدان</v>
+        <v>پلدشت</v>
       </c>
       <c r="D303">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="304">
       <c r="A304">
-        <v>11300005</v>
+        <v>10400016</v>
       </c>
       <c r="B304" t="str">
-        <v>کبودرآهنگ</v>
+        <v>چایپاره</v>
       </c>
       <c r="C304" t="str">
-        <v>کبودرآهنگ</v>
+        <v>چایپاره</v>
       </c>
       <c r="D304">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="305">
       <c r="A305">
-        <v>11300006</v>
+        <v>10400017</v>
       </c>
       <c r="B305" t="str">
-        <v>اسدآباد</v>
+        <v>شوط</v>
       </c>
       <c r="C305" t="str">
-        <v>اسدآباد</v>
+        <v>شوط</v>
       </c>
       <c r="D305">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="306">
       <c r="A306">
-        <v>11300007</v>
+        <v>10400018</v>
       </c>
       <c r="B306" t="str">
-        <v>بهار</v>
+        <v>چهاربرج</v>
       </c>
       <c r="C306" t="str">
-        <v>بهار</v>
+        <v>چهاربرج</v>
       </c>
       <c r="D306">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="307">
       <c r="A307">
-        <v>11300008</v>
+        <v>10400019</v>
       </c>
       <c r="B307" t="str">
-        <v>رزن</v>
+        <v>باروق</v>
       </c>
       <c r="C307" t="str">
-        <v>رزن</v>
+        <v>باروق</v>
       </c>
       <c r="D307">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="308">
       <c r="A308">
-        <v>11300009</v>
+        <v>10400020</v>
       </c>
       <c r="B308" t="str">
-        <v>فامنین</v>
+        <v>میرآباد</v>
       </c>
       <c r="C308" t="str">
-        <v>فامنین</v>
+        <v>میرآباد</v>
       </c>
       <c r="D308">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="309">
       <c r="A309">
-        <v>11300010</v>
+        <v>10500010</v>
       </c>
       <c r="B309" t="str">
-        <v>درگزین</v>
+        <v>صحنه</v>
       </c>
       <c r="C309" t="str">
-        <v>درگزین</v>
+        <v>صحنه</v>
       </c>
       <c r="D309">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="310">
       <c r="A310">
-        <v>11400001</v>
+        <v>10500011</v>
       </c>
       <c r="B310" t="str">
-        <v>بروجن</v>
+        <v>هرسین</v>
       </c>
       <c r="C310" t="str">
-        <v>بروجن</v>
+        <v>هرسین</v>
       </c>
       <c r="D310">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="311">
       <c r="A311">
-        <v>11400002</v>
+        <v>10500012</v>
       </c>
       <c r="B311" t="str">
-        <v>شهرکرد</v>
+        <v>ثلاث باباجانی</v>
       </c>
       <c r="C311" t="str">
-        <v>شهرکرد</v>
+        <v>ثلاث-باباجانی</v>
       </c>
       <c r="D311">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="312">
       <c r="A312">
-        <v>11400003</v>
+        <v>10500013</v>
       </c>
       <c r="B312" t="str">
-        <v>فارسان</v>
+        <v>دالاهو</v>
       </c>
       <c r="C312" t="str">
-        <v>فارسان</v>
+        <v>دالاهو</v>
       </c>
       <c r="D312">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="313">
       <c r="A313">
-        <v>11400004</v>
+        <v>10500014</v>
       </c>
       <c r="B313" t="str">
-        <v>لردگان</v>
+        <v>روانسر</v>
       </c>
       <c r="C313" t="str">
-        <v>لردگان</v>
+        <v>روانسر</v>
       </c>
       <c r="D313">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="314">
       <c r="A314">
-        <v>11400005</v>
+        <v>10600010</v>
       </c>
       <c r="B314" t="str">
-        <v>اردل</v>
+        <v>رامهرمز</v>
       </c>
       <c r="C314" t="str">
-        <v>اردل</v>
+        <v>رامهرمز</v>
       </c>
       <c r="D314">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="315">
       <c r="A315">
-        <v>11400006</v>
+        <v>10600011</v>
       </c>
       <c r="B315" t="str">
-        <v>کوهرنگ</v>
+        <v>شادگان</v>
       </c>
       <c r="C315" t="str">
-        <v>کوهرنگ</v>
+        <v>شادگان</v>
       </c>
       <c r="D315">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="316">
       <c r="A316">
-        <v>11400007</v>
+        <v>10600012</v>
       </c>
       <c r="B316" t="str">
-        <v>کیار</v>
+        <v>شوشتر</v>
       </c>
       <c r="C316" t="str">
-        <v>کیار</v>
+        <v>شوشتر</v>
       </c>
       <c r="D316">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="317">
       <c r="A317">
-        <v>11400008</v>
+        <v>10600013</v>
       </c>
       <c r="B317" t="str">
-        <v>سامان</v>
+        <v>مسجدسلیمان</v>
       </c>
       <c r="C317" t="str">
-        <v>سامان</v>
+        <v>مسجدسلیمان</v>
       </c>
       <c r="D317">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="318">
       <c r="A318">
-        <v>11400009</v>
+        <v>10600014</v>
       </c>
       <c r="B318" t="str">
-        <v>بن</v>
+        <v>شوش</v>
       </c>
       <c r="C318" t="str">
-        <v>بن</v>
+        <v>شوش</v>
       </c>
       <c r="D318">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="319">
       <c r="A319">
-        <v>11400010</v>
+        <v>10600015</v>
       </c>
       <c r="B319" t="str">
-        <v>خانمیرزا</v>
+        <v>باغ ملک</v>
       </c>
       <c r="C319" t="str">
-        <v>خانمیرزا</v>
+        <v>باغ-ملک</v>
       </c>
       <c r="D319">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="320">
       <c r="A320">
-        <v>11400011</v>
+        <v>10600016</v>
       </c>
       <c r="B320" t="str">
-        <v>فلارد</v>
+        <v>امیدیه</v>
       </c>
       <c r="C320" t="str">
-        <v>فلارد</v>
+        <v>امیدیه</v>
       </c>
       <c r="D320">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="321">
       <c r="A321">
-        <v>11400012</v>
+        <v>10600017</v>
       </c>
       <c r="B321" t="str">
-        <v>فرخ شهر</v>
+        <v>لالی</v>
       </c>
       <c r="C321" t="str">
-        <v>فرخ-شهر</v>
+        <v>لالی</v>
       </c>
       <c r="D321">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="322">
       <c r="A322">
-        <v>11500001</v>
+        <v>10600018</v>
       </c>
       <c r="B322" t="str">
-        <v>الیگودرز</v>
+        <v>هندیجان</v>
       </c>
       <c r="C322" t="str">
-        <v>الیگودرز</v>
+        <v>هندیجان</v>
       </c>
       <c r="D322">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="323">
       <c r="A323">
-        <v>11500002</v>
+        <v>10600019</v>
       </c>
       <c r="B323" t="str">
-        <v>بروجرد</v>
+        <v>رامشیر</v>
       </c>
       <c r="C323" t="str">
-        <v>بروجرد</v>
+        <v>رامشیر</v>
       </c>
       <c r="D323">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="324">
       <c r="A324">
-        <v>11500003</v>
+        <v>10600020</v>
       </c>
       <c r="B324" t="str">
-        <v>خرم آباد</v>
+        <v>گتوند</v>
       </c>
       <c r="C324" t="str">
-        <v>خرم-آباد</v>
+        <v>گتوند</v>
       </c>
       <c r="D324">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="325">
       <c r="A325">
-        <v>11500004</v>
+        <v>10600021</v>
       </c>
       <c r="B325" t="str">
-        <v>دلفان</v>
+        <v>اندیکا</v>
       </c>
       <c r="C325" t="str">
-        <v>دلفان</v>
+        <v>اندیکا</v>
       </c>
       <c r="D325">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="326">
       <c r="A326">
-        <v>11500005</v>
+        <v>10600022</v>
       </c>
       <c r="B326" t="str">
-        <v>دورود</v>
+        <v>هفتکل</v>
       </c>
       <c r="C326" t="str">
-        <v>دورود</v>
+        <v>هفتکل</v>
       </c>
       <c r="D326">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="327">
       <c r="A327">
-        <v>11500006</v>
+        <v>10600023</v>
       </c>
       <c r="B327" t="str">
-        <v>کوهدشت</v>
+        <v>هویزه</v>
       </c>
       <c r="C327" t="str">
-        <v>کوهدشت</v>
+        <v>هویزه</v>
       </c>
       <c r="D327">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="328">
       <c r="A328">
-        <v>11500007</v>
+        <v>10600024</v>
       </c>
       <c r="B328" t="str">
-        <v>ازنا</v>
+        <v>باوی</v>
       </c>
       <c r="C328" t="str">
-        <v>ازنا</v>
+        <v>باوی</v>
       </c>
       <c r="D328">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="329">
       <c r="A329">
-        <v>11500008</v>
+        <v>10600025</v>
       </c>
       <c r="B329" t="str">
-        <v>پلدختر</v>
+        <v>حمیدیه</v>
       </c>
       <c r="C329" t="str">
-        <v>پلدختر</v>
+        <v>حمیدیه</v>
       </c>
       <c r="D329">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="330">
       <c r="A330">
-        <v>11500009</v>
+        <v>10600026</v>
       </c>
       <c r="B330" t="str">
-        <v>سلسله</v>
+        <v>آغاجاری</v>
       </c>
       <c r="C330" t="str">
-        <v>سلسله</v>
+        <v>آغاجاری</v>
       </c>
       <c r="D330">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="331">
       <c r="A331">
-        <v>11500010</v>
+        <v>10600027</v>
       </c>
       <c r="B331" t="str">
-        <v>چگنی</v>
+        <v>کارون</v>
       </c>
       <c r="C331" t="str">
-        <v>چگنی</v>
+        <v>کارون</v>
       </c>
       <c r="D331">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="332">
       <c r="A332">
-        <v>11500011</v>
+        <v>10600028</v>
       </c>
       <c r="B332" t="str">
-        <v>رومشکان</v>
+        <v>کرخه</v>
       </c>
       <c r="C332" t="str">
-        <v>رومشکان</v>
+        <v>کرخه</v>
       </c>
       <c r="D332">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="333">
       <c r="A333">
-        <v>11500012</v>
+        <v>10600029</v>
       </c>
       <c r="B333" t="str">
-        <v>معمولان</v>
+        <v>دزپارت</v>
       </c>
       <c r="C333" t="str">
-        <v>معمولان</v>
+        <v>دزپارت</v>
       </c>
       <c r="D333">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="334">
       <c r="A334">
-        <v>11600001</v>
+        <v>10600030</v>
       </c>
       <c r="B334" t="str">
-        <v>ایلام</v>
+        <v>صیدون</v>
       </c>
       <c r="C334" t="str">
-        <v>ایلام</v>
+        <v>صیدون</v>
       </c>
       <c r="D334">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="335">
       <c r="A335">
-        <v>11600002</v>
+        <v>10700010</v>
       </c>
       <c r="B335" t="str">
-        <v>دره شهر</v>
+        <v>کازرون</v>
       </c>
       <c r="C335" t="str">
-        <v>دره-شهر</v>
+        <v>کازرون</v>
       </c>
       <c r="D335">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="336">
       <c r="A336">
-        <v>11600003</v>
+        <v>10700011</v>
       </c>
       <c r="B336" t="str">
-        <v>دهلران</v>
+        <v>لارستان</v>
       </c>
       <c r="C336" t="str">
-        <v>دهلران</v>
+        <v>لارستان</v>
       </c>
       <c r="D336">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="337">
       <c r="A337">
-        <v>11600004</v>
+        <v>10700012</v>
       </c>
       <c r="B337" t="str">
-        <v>چرداول</v>
+        <v>مرودشت</v>
       </c>
       <c r="C337" t="str">
-        <v>چرداول</v>
+        <v>مرودشت</v>
       </c>
       <c r="D337">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="338">
       <c r="A338">
-        <v>11600005</v>
+        <v>10700013</v>
       </c>
       <c r="B338" t="str">
-        <v>مهران</v>
+        <v>ممسنی</v>
       </c>
       <c r="C338" t="str">
-        <v>مهران</v>
+        <v>ممسنی</v>
       </c>
       <c r="D338">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="339">
       <c r="A339">
-        <v>11600006</v>
+        <v>10700014</v>
       </c>
       <c r="B339" t="str">
-        <v>آبدانان</v>
+        <v>نی ریز</v>
       </c>
       <c r="C339" t="str">
-        <v>آبدانان</v>
+        <v>نی-ریز</v>
       </c>
       <c r="D339">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="340">
       <c r="A340">
-        <v>11600007</v>
+        <v>10700015</v>
       </c>
       <c r="B340" t="str">
-        <v>ایوان</v>
+        <v>لامرد</v>
       </c>
       <c r="C340" t="str">
-        <v>ایوان</v>
+        <v>لامرد</v>
       </c>
       <c r="D340">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="341">
       <c r="A341">
-        <v>11600008</v>
+        <v>10700016</v>
       </c>
       <c r="B341" t="str">
-        <v>ملکشاهی</v>
+        <v>بوانات</v>
       </c>
       <c r="C341" t="str">
-        <v>ملکشاهی</v>
+        <v>بوانات</v>
       </c>
       <c r="D341">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="342">
       <c r="A342">
-        <v>11600009</v>
+        <v>10700017</v>
       </c>
       <c r="B342" t="str">
-        <v>سیروان</v>
+        <v>ارسنجان</v>
       </c>
       <c r="C342" t="str">
-        <v>سیروان</v>
+        <v>ارسنجان</v>
       </c>
       <c r="D342">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="343">
       <c r="A343">
-        <v>11600010</v>
+        <v>10700018</v>
       </c>
       <c r="B343" t="str">
-        <v>بدره</v>
+        <v>خرم بید</v>
       </c>
       <c r="C343" t="str">
-        <v>بدره</v>
+        <v>خرم-بید</v>
       </c>
       <c r="D343">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="344">
       <c r="A344">
-        <v>11600011</v>
+        <v>10700019</v>
       </c>
       <c r="B344" t="str">
-        <v>هلیلان</v>
+        <v>زرین دشت</v>
       </c>
       <c r="C344" t="str">
-        <v>هلیلان</v>
+        <v>زرین-دشت</v>
       </c>
       <c r="D344">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="345">
       <c r="A345">
-        <v>11600012</v>
+        <v>10700020</v>
       </c>
       <c r="B345" t="str">
-        <v>چوار</v>
+        <v>قیرو کارزین</v>
       </c>
       <c r="C345" t="str">
-        <v>چوار</v>
+        <v>قیروکارزین</v>
       </c>
       <c r="D345">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="346">
       <c r="A346">
-        <v>11700001</v>
+        <v>10700021</v>
       </c>
       <c r="B346" t="str">
-        <v>بویراحمد</v>
+        <v>مهر</v>
       </c>
       <c r="C346" t="str">
-        <v>بویراحمد</v>
+        <v>مهر</v>
       </c>
       <c r="D346">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="347">
       <c r="A347">
-        <v>11700002</v>
+        <v>10700022</v>
       </c>
       <c r="B347" t="str">
-        <v>کهگیلویه</v>
+        <v>فراشبند</v>
       </c>
       <c r="C347" t="str">
-        <v>کهگیلویه</v>
+        <v>فراشبند</v>
       </c>
       <c r="D347">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="348">
       <c r="A348">
-        <v>11700003</v>
+        <v>10700023</v>
       </c>
       <c r="B348" t="str">
-        <v>گچساران</v>
+        <v>پاسارگاد</v>
       </c>
       <c r="C348" t="str">
-        <v>گچساران</v>
+        <v>پاسارگاد</v>
       </c>
       <c r="D348">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="349">
       <c r="A349">
-        <v>11700004</v>
+        <v>10700024</v>
       </c>
       <c r="B349" t="str">
-        <v>دنا</v>
+        <v>خنج</v>
       </c>
       <c r="C349" t="str">
-        <v>دنا</v>
+        <v>خنج</v>
       </c>
       <c r="D349">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="350">
       <c r="A350">
-        <v>11700005</v>
+        <v>10700025</v>
       </c>
       <c r="B350" t="str">
-        <v>بهمیی</v>
+        <v>سروستان</v>
       </c>
       <c r="C350" t="str">
-        <v>بهمیی</v>
+        <v>سروستان</v>
       </c>
       <c r="D350">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="351">
       <c r="A351">
-        <v>11700006</v>
+        <v>10700026</v>
       </c>
       <c r="B351" t="str">
-        <v>چرام</v>
+        <v>رستم</v>
       </c>
       <c r="C351" t="str">
-        <v>چرام</v>
+        <v>رستم</v>
       </c>
       <c r="D351">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="352">
       <c r="A352">
-        <v>11700007</v>
+        <v>10700027</v>
       </c>
       <c r="B352" t="str">
-        <v>باشت</v>
+        <v>گراش</v>
       </c>
       <c r="C352" t="str">
-        <v>باشت</v>
+        <v>گراش</v>
       </c>
       <c r="D352">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="353">
       <c r="A353">
-        <v>11700008</v>
+        <v>10700028</v>
       </c>
       <c r="B353" t="str">
-        <v>لنده</v>
+        <v>کوار</v>
       </c>
       <c r="C353" t="str">
-        <v>لنده</v>
+        <v>کوار</v>
       </c>
       <c r="D353">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="354">
       <c r="A354">
-        <v>11700009</v>
+        <v>10700029</v>
       </c>
       <c r="B354" t="str">
-        <v>مارگون</v>
+        <v>خرامه</v>
       </c>
       <c r="C354" t="str">
-        <v>مارگون</v>
+        <v>خرامه</v>
       </c>
       <c r="D354">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="355">
       <c r="A355">
-        <v>11800001</v>
+        <v>10700030</v>
       </c>
       <c r="B355" t="str">
-        <v>بوشهر</v>
+        <v>زرقان</v>
       </c>
       <c r="C355" t="str">
-        <v>بوشهر</v>
+        <v>زرقان</v>
       </c>
       <c r="D355">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="356">
       <c r="A356">
-        <v>11800002</v>
+        <v>10700031</v>
       </c>
       <c r="B356" t="str">
-        <v>تنگستان</v>
+        <v>بیضاء</v>
       </c>
       <c r="C356" t="str">
-        <v>تنگستان</v>
+        <v>بیضا</v>
       </c>
       <c r="D356">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="357">
       <c r="A357">
-        <v>11800003</v>
+        <v>10700032</v>
       </c>
       <c r="B357" t="str">
-        <v>دشتستان</v>
+        <v>سرچهان</v>
       </c>
       <c r="C357" t="str">
-        <v>دشتستان</v>
+        <v>سرچهان</v>
       </c>
       <c r="D357">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="358">
       <c r="A358">
-        <v>11800004</v>
+        <v>10700033</v>
       </c>
       <c r="B358" t="str">
-        <v>دشتی</v>
+        <v>کوه چنار</v>
       </c>
       <c r="C358" t="str">
-        <v>دشتی</v>
+        <v>کوه-چنار</v>
       </c>
       <c r="D358">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="359">
       <c r="A359">
-        <v>11800005</v>
+        <v>10700034</v>
       </c>
       <c r="B359" t="str">
-        <v>دیر</v>
+        <v>خفر</v>
       </c>
       <c r="C359" t="str">
-        <v>دیر</v>
+        <v>خفر</v>
       </c>
       <c r="D359">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="360">
       <c r="A360">
-        <v>11800006</v>
+        <v>10700035</v>
       </c>
       <c r="B360" t="str">
-        <v>کنگان</v>
+        <v>بختگان</v>
       </c>
       <c r="C360" t="str">
-        <v>کنگان</v>
+        <v>بختگان</v>
       </c>
       <c r="D360">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="361">
       <c r="A361">
-        <v>11800007</v>
+        <v>10700036</v>
       </c>
       <c r="B361" t="str">
-        <v>گناوه</v>
+        <v>اوز</v>
       </c>
       <c r="C361" t="str">
-        <v>گناوه</v>
+        <v>اوز</v>
       </c>
       <c r="D361">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="362">
       <c r="A362">
-        <v>11800008</v>
+        <v>10700037</v>
       </c>
       <c r="B362" t="str">
-        <v>دیلم</v>
+        <v>جویم</v>
       </c>
       <c r="C362" t="str">
-        <v>دیلم</v>
+        <v>جویم</v>
       </c>
       <c r="D362">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="363">
       <c r="A363">
-        <v>11800009</v>
+        <v>10800010</v>
       </c>
       <c r="B363" t="str">
-        <v>جم</v>
+        <v>بردسیر</v>
       </c>
       <c r="C363" t="str">
-        <v>جم</v>
+        <v>بردسیر</v>
       </c>
       <c r="D363">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="364">
       <c r="A364">
-        <v>11800010</v>
+        <v>10800011</v>
       </c>
       <c r="B364" t="str">
-        <v>عسلویه</v>
+        <v>راور</v>
       </c>
       <c r="C364" t="str">
-        <v>عسلویه</v>
+        <v>راور</v>
       </c>
       <c r="D364">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="365">
       <c r="A365">
-        <v>11900001</v>
+        <v>10800012</v>
       </c>
       <c r="B365" t="str">
-        <v>ابهر</v>
+        <v>عنبرآباد</v>
       </c>
       <c r="C365" t="str">
-        <v>ابهر</v>
+        <v>عنبرآباد</v>
       </c>
       <c r="D365">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="366">
       <c r="A366">
-        <v>11900003</v>
+        <v>10800013</v>
       </c>
       <c r="B366" t="str">
-        <v>خدابنده</v>
+        <v>منوجان</v>
       </c>
       <c r="C366" t="str">
-        <v>خدابنده</v>
+        <v>منوجان</v>
       </c>
       <c r="D366">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="367">
       <c r="A367">
-        <v>11900004</v>
+        <v>10800014</v>
       </c>
       <c r="B367" t="str">
-        <v>زنجان</v>
+        <v>کوهبنان</v>
       </c>
       <c r="C367" t="str">
-        <v>زنجان</v>
+        <v>کوهبنان</v>
       </c>
       <c r="D367">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="368">
       <c r="A368">
-        <v>11900006</v>
+        <v>10800015</v>
       </c>
       <c r="B368" t="str">
-        <v>ایجرود</v>
+        <v>رودبارجنوب</v>
       </c>
       <c r="C368" t="str">
-        <v>ایجرود</v>
+        <v>رودبارجنوب</v>
       </c>
       <c r="D368">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="369">
       <c r="A369">
-        <v>11900007</v>
+        <v>10800016</v>
       </c>
       <c r="B369" t="str">
-        <v>خرمدره</v>
+        <v>قلعه گنج</v>
       </c>
       <c r="C369" t="str">
-        <v>خرمدره</v>
+        <v>قلعه-گنج</v>
       </c>
       <c r="D369">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="370">
       <c r="A370">
-        <v>11900008</v>
+        <v>10800017</v>
       </c>
       <c r="B370" t="str">
-        <v>طارم</v>
+        <v>ریگان</v>
       </c>
       <c r="C370" t="str">
-        <v>طارم</v>
+        <v>ریگان</v>
       </c>
       <c r="D370">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="371">
       <c r="A371">
-        <v>11900009</v>
+        <v>10800018</v>
       </c>
       <c r="B371" t="str">
-        <v>ماهنشان</v>
+        <v>رابر</v>
       </c>
       <c r="C371" t="str">
-        <v>ماهنشان</v>
+        <v>رابر</v>
       </c>
       <c r="D371">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="372">
       <c r="A372">
-        <v>11900010</v>
+        <v>10800019</v>
       </c>
       <c r="B372" t="str">
-        <v>سلطانیه</v>
+        <v>فهرج</v>
       </c>
       <c r="C372" t="str">
-        <v>سلطانیه</v>
+        <v>فهرج</v>
       </c>
       <c r="D372">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="373">
       <c r="A373">
-        <v>12000001</v>
+        <v>10800020</v>
       </c>
       <c r="B373" t="str">
-        <v>دامغان</v>
+        <v>انار</v>
       </c>
       <c r="C373" t="str">
-        <v>دامغان</v>
+        <v>انار</v>
       </c>
       <c r="D373">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="374">
       <c r="A374">
-        <v>12000002</v>
+        <v>10800021</v>
       </c>
       <c r="B374" t="str">
-        <v>سمنان</v>
+        <v>نرماشیر</v>
       </c>
       <c r="C374" t="str">
-        <v>سمنان</v>
+        <v>نرماشیر</v>
       </c>
       <c r="D374">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="375">
       <c r="A375">
-        <v>12000003</v>
+        <v>10800022</v>
       </c>
       <c r="B375" t="str">
-        <v>شاهرود</v>
+        <v>فاریاب</v>
       </c>
       <c r="C375" t="str">
-        <v>شاهرود</v>
+        <v>فاریاب</v>
       </c>
       <c r="D375">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="376">
       <c r="A376">
-        <v>12000004</v>
+        <v>10800023</v>
       </c>
       <c r="B376" t="str">
-        <v>گرمسار</v>
+        <v>ارزوییه</v>
       </c>
       <c r="C376" t="str">
-        <v>گرمسار</v>
+        <v>ارزوییه</v>
       </c>
       <c r="D376">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="377">
       <c r="A377">
-        <v>12000005</v>
+        <v>10800024</v>
       </c>
       <c r="B377" t="str">
-        <v>مهدی شهر</v>
+        <v>گنبکی</v>
       </c>
       <c r="C377" t="str">
-        <v>مهدی-شهر</v>
+        <v>گنبکی</v>
       </c>
       <c r="D377">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="378">
       <c r="A378">
-        <v>12000006</v>
+        <v>10800025</v>
       </c>
       <c r="B378" t="str">
-        <v>آرادان</v>
+        <v>جازموریان</v>
       </c>
       <c r="C378" t="str">
-        <v>آرادان</v>
+        <v>جازموریان</v>
       </c>
       <c r="D378">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="379">
       <c r="A379">
-        <v>12000007</v>
+        <v>10900013</v>
       </c>
       <c r="B379" t="str">
-        <v>میامی</v>
+        <v>قوچان</v>
       </c>
       <c r="C379" t="str">
-        <v>میامی</v>
+        <v>قوچان</v>
       </c>
       <c r="D379">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="380">
       <c r="A380">
-        <v>12000008</v>
+        <v>10900014</v>
       </c>
       <c r="B380" t="str">
-        <v>سرخه</v>
+        <v>کاشمر</v>
       </c>
       <c r="C380" t="str">
-        <v>سرخه</v>
+        <v>کاشمر</v>
       </c>
       <c r="D380">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="381">
       <c r="A381">
-        <v>12100001</v>
+        <v>10900015</v>
       </c>
       <c r="B381" t="str">
-        <v>اردکان</v>
+        <v>گناباد</v>
       </c>
       <c r="C381" t="str">
-        <v>اردکان</v>
+        <v>گناباد</v>
       </c>
       <c r="D381">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="382">
       <c r="A382">
-        <v>12100002</v>
+        <v>10900016</v>
       </c>
       <c r="B382" t="str">
-        <v>بافق</v>
+        <v>مشهد</v>
       </c>
       <c r="C382" t="str">
-        <v>بافق</v>
+        <v>مشهد</v>
       </c>
       <c r="D382">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="383">
       <c r="A383">
-        <v>12100003</v>
+        <v>10900017</v>
       </c>
       <c r="B383" t="str">
-        <v>تفت</v>
+        <v>نیشابور</v>
       </c>
       <c r="C383" t="str">
-        <v>تفت</v>
+        <v>نیشابور</v>
       </c>
       <c r="D383">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="384">
       <c r="A384">
-        <v>12100004</v>
+        <v>10900018</v>
       </c>
       <c r="B384" t="str">
-        <v>مهریز</v>
+        <v>چناران</v>
       </c>
       <c r="C384" t="str">
-        <v>مهریز</v>
+        <v>چناران</v>
       </c>
       <c r="D384">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="385">
       <c r="A385">
-        <v>12100005</v>
+        <v>10900019</v>
       </c>
       <c r="B385" t="str">
-        <v>یزد</v>
+        <v>خواف</v>
       </c>
       <c r="C385" t="str">
-        <v>یزد</v>
+        <v>خواف</v>
       </c>
       <c r="D385">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="386">
       <c r="A386">
-        <v>12100006</v>
+        <v>10900020</v>
       </c>
       <c r="B386" t="str">
-        <v>میبد</v>
+        <v>سرخس</v>
       </c>
       <c r="C386" t="str">
-        <v>میبد</v>
+        <v>سرخس</v>
       </c>
       <c r="D386">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="387">
       <c r="A387">
-        <v>12100007</v>
+        <v>10900022</v>
       </c>
       <c r="B387" t="str">
-        <v>ابرکوه</v>
+        <v>فریمان</v>
       </c>
       <c r="C387" t="str">
-        <v>ابرکوه</v>
+        <v>فریمان</v>
       </c>
       <c r="D387">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="388">
       <c r="A388">
-        <v>12100008</v>
+        <v>10900023</v>
       </c>
       <c r="B388" t="str">
-        <v>اشکذر</v>
+        <v>بردسکن</v>
       </c>
       <c r="C388" t="str">
-        <v>اشکذر</v>
+        <v>بردسکن</v>
       </c>
       <c r="D388">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="389">
       <c r="A389">
-        <v>12100009</v>
+        <v>10900027</v>
       </c>
       <c r="B389" t="str">
-        <v>خاتم</v>
+        <v>رشتخوار</v>
       </c>
       <c r="C389" t="str">
-        <v>خاتم</v>
+        <v>رشتخوار</v>
       </c>
       <c r="D389">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="390">
       <c r="A390">
-        <v>12100011</v>
+        <v>10900028</v>
       </c>
       <c r="B390" t="str">
-        <v>بهاباد</v>
+        <v>کلات</v>
       </c>
       <c r="C390" t="str">
-        <v>بهاباد</v>
+        <v>کلات</v>
       </c>
       <c r="D390">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="391">
       <c r="A391">
-        <v>12100012</v>
+        <v>10900029</v>
       </c>
       <c r="B391" t="str">
-        <v>مروست</v>
+        <v>خلیل آباد</v>
       </c>
       <c r="C391" t="str">
-        <v>مروست</v>
+        <v>خلیل-آباد</v>
       </c>
       <c r="D391">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="392">
       <c r="A392">
-        <v>12100013</v>
+        <v>10900030</v>
       </c>
       <c r="B392" t="str">
-        <v>زارچ</v>
+        <v>مه ولات</v>
       </c>
       <c r="C392" t="str">
-        <v>زارچ</v>
+        <v>مه-ولات</v>
       </c>
       <c r="D392">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="393">
       <c r="A393">
-        <v>12200001</v>
+        <v>10900031</v>
       </c>
       <c r="B393" t="str">
-        <v>ابوموسی</v>
+        <v>بجستان</v>
       </c>
       <c r="C393" t="str">
-        <v>ابوموسی</v>
+        <v>بجستان</v>
       </c>
       <c r="D393">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="394">
       <c r="A394">
-        <v>12200002</v>
+        <v>10900032</v>
       </c>
       <c r="B394" t="str">
-        <v>بندر عباس</v>
+        <v>طرقبه شاندیز</v>
       </c>
       <c r="C394" t="str">
-        <v>بندر-عباس</v>
+        <v>طرقبه-شاندیز</v>
       </c>
       <c r="D394">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="395">
       <c r="A395">
-        <v>12200003</v>
+        <v>10900033</v>
       </c>
       <c r="B395" t="str">
-        <v>بندر لنگه</v>
+        <v>فیروزه</v>
       </c>
       <c r="C395" t="str">
-        <v>بندر-لنگه</v>
+        <v>فیروزه</v>
       </c>
       <c r="D395">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="396">
       <c r="A396">
-        <v>12200004</v>
+        <v>10900034</v>
       </c>
       <c r="B396" t="str">
-        <v>قشم</v>
+        <v>جغتای</v>
       </c>
       <c r="C396" t="str">
-        <v>قشم</v>
+        <v>جغتای</v>
       </c>
       <c r="D396">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="397">
       <c r="A397">
-        <v>12200005</v>
+        <v>10900035</v>
       </c>
       <c r="B397" t="str">
-        <v>میناب</v>
+        <v>زاوه</v>
       </c>
       <c r="C397" t="str">
-        <v>میناب</v>
+        <v>زاوه</v>
       </c>
       <c r="D397">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="398">
       <c r="A398">
-        <v>12200006</v>
+        <v>10900036</v>
       </c>
       <c r="B398" t="str">
-        <v>جاسک</v>
+        <v>جوین</v>
       </c>
       <c r="C398" t="str">
-        <v>جاسک</v>
+        <v>جوین</v>
       </c>
       <c r="D398">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="399">
       <c r="A399">
-        <v>12200007</v>
+        <v>10900037</v>
       </c>
       <c r="B399" t="str">
-        <v>رودان</v>
+        <v>باخرز</v>
       </c>
       <c r="C399" t="str">
-        <v>رودان</v>
+        <v>باخرز</v>
       </c>
       <c r="D399">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="400">
       <c r="A400">
-        <v>12200008</v>
+        <v>10900038</v>
       </c>
       <c r="B400" t="str">
-        <v>حاجی آباد</v>
+        <v>خوشاب</v>
       </c>
       <c r="C400" t="str">
-        <v>حاجی-آباد</v>
+        <v>خوشاب</v>
       </c>
       <c r="D400">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="401">
       <c r="A401">
-        <v>12200009</v>
+        <v>10900039</v>
       </c>
       <c r="B401" t="str">
-        <v>بستک</v>
+        <v>داورزن</v>
       </c>
       <c r="C401" t="str">
-        <v>بستک</v>
+        <v>داورزن</v>
       </c>
       <c r="D401">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="402">
       <c r="A402">
-        <v>12200010</v>
+        <v>10900040</v>
       </c>
       <c r="B402" t="str">
-        <v>خمیر</v>
+        <v>صالح آباد</v>
       </c>
       <c r="C402" t="str">
-        <v>خمیر</v>
+        <v>صالح-آباد</v>
       </c>
       <c r="D402">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="403">
       <c r="A403">
-        <v>12200011</v>
+        <v>10900041</v>
       </c>
       <c r="B403" t="str">
-        <v>پارسیان</v>
+        <v>کوهسرخ</v>
       </c>
       <c r="C403" t="str">
-        <v>پارسیان</v>
+        <v>کوهسرخ</v>
       </c>
       <c r="D403">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="404">
       <c r="A404">
-        <v>12200012</v>
+        <v>10900042</v>
       </c>
       <c r="B404" t="str">
-        <v>سیریک</v>
+        <v>زبرخان</v>
       </c>
       <c r="C404" t="str">
-        <v>سیریک</v>
+        <v>زبرخان</v>
       </c>
       <c r="D404">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="405">
       <c r="A405">
-        <v>12200013</v>
+        <v>10900043</v>
       </c>
       <c r="B405" t="str">
-        <v>بشاگرد</v>
+        <v>ششتمد</v>
       </c>
       <c r="C405" t="str">
-        <v>بشاگرد</v>
+        <v>ششتمد</v>
       </c>
       <c r="D405">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="406">
       <c r="A406">
-        <v>12300001</v>
+        <v>10900044</v>
       </c>
       <c r="B406" t="str">
-        <v>تهران</v>
+        <v>گلبهار</v>
       </c>
       <c r="C406" t="str">
-        <v>تهران</v>
+        <v>گلبهار</v>
       </c>
       <c r="D406">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="407">
       <c r="A407">
-        <v>12300002</v>
+        <v>10900045</v>
       </c>
       <c r="B407" t="str">
-        <v>دماوند</v>
+        <v>میان جلگه</v>
       </c>
       <c r="C407" t="str">
-        <v>دماوند</v>
+        <v>میان-جلگه</v>
       </c>
       <c r="D407">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="408">
       <c r="A408">
-        <v>12300003</v>
+        <v>11000010</v>
       </c>
       <c r="B408" t="str">
-        <v>ری</v>
+        <v>کاشان</v>
       </c>
       <c r="C408" t="str">
-        <v>ری</v>
+        <v>کاشان</v>
       </c>
       <c r="D408">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="409">
       <c r="A409">
-        <v>12300004</v>
+        <v>11000011</v>
       </c>
       <c r="B409" t="str">
-        <v>شمیرانات</v>
+        <v>گلپایگان</v>
       </c>
       <c r="C409" t="str">
-        <v>شمیرانات</v>
+        <v>گلپایگان</v>
       </c>
       <c r="D409">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="410">
       <c r="A410">
-        <v>12300006</v>
+        <v>11000012</v>
       </c>
       <c r="B410" t="str">
-        <v>ورامین</v>
+        <v>لنجان</v>
       </c>
       <c r="C410" t="str">
-        <v>ورامین</v>
+        <v>لنجان</v>
       </c>
       <c r="D410">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="411">
       <c r="A411">
-        <v>12300009</v>
+        <v>11000013</v>
       </c>
       <c r="B411" t="str">
-        <v>شهریار</v>
+        <v>نایین</v>
       </c>
       <c r="C411" t="str">
-        <v>شهریار</v>
+        <v>نایین</v>
       </c>
       <c r="D411">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="412">
       <c r="A412">
-        <v>12300010</v>
+        <v>11000014</v>
       </c>
       <c r="B412" t="str">
-        <v>اسلامشهر</v>
+        <v>نجف آباد</v>
       </c>
       <c r="C412" t="str">
-        <v>اسلامشهر</v>
+        <v>نجف-آباد</v>
       </c>
       <c r="D412">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="413">
       <c r="A413">
-        <v>12300012</v>
+        <v>11000015</v>
       </c>
       <c r="B413" t="str">
-        <v>رباط‌کریم</v>
+        <v>نطنز</v>
       </c>
       <c r="C413" t="str">
-        <v>رباطکریم</v>
+        <v>نطنز</v>
       </c>
       <c r="D413">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="414">
       <c r="A414">
-        <v>12300013</v>
+        <v>11000016</v>
       </c>
       <c r="B414" t="str">
-        <v>پاکدشت</v>
+        <v>شاهین شهرو میمه</v>
       </c>
       <c r="C414" t="str">
-        <v>پاکدشت</v>
+        <v>شاهین-شهرو-میمه</v>
       </c>
       <c r="D414">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="415">
       <c r="A415">
-        <v>12300014</v>
+        <v>11000017</v>
       </c>
       <c r="B415" t="str">
-        <v>فیروزکوه</v>
+        <v>مبارکه</v>
       </c>
       <c r="C415" t="str">
-        <v>فیروزکوه</v>
+        <v>مبارکه</v>
       </c>
       <c r="D415">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="416">
       <c r="A416">
-        <v>12300016</v>
+        <v>11000018</v>
       </c>
       <c r="B416" t="str">
-        <v>قدس</v>
+        <v>آران و بیدگل</v>
       </c>
       <c r="C416" t="str">
-        <v>قدس</v>
+        <v>آران-و-بیدگل</v>
       </c>
       <c r="D416">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="417">
       <c r="A417">
-        <v>12300017</v>
+        <v>11000019</v>
       </c>
       <c r="B417" t="str">
-        <v>ملارد</v>
+        <v>تیران وکرون</v>
       </c>
       <c r="C417" t="str">
-        <v>ملارد</v>
+        <v>تیران-وکرون</v>
       </c>
       <c r="D417">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="418">
       <c r="A418">
-        <v>12300018</v>
+        <v>11000020</v>
       </c>
       <c r="B418" t="str">
-        <v>پیشوا</v>
+        <v>چادگان</v>
       </c>
       <c r="C418" t="str">
-        <v>پیشوا</v>
+        <v>چادگان</v>
       </c>
       <c r="D418">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="419">
       <c r="A419">
-        <v>12300019</v>
+        <v>11000021</v>
       </c>
       <c r="B419" t="str">
-        <v>بهارستان</v>
+        <v>دهاقان</v>
       </c>
       <c r="C419" t="str">
-        <v>بهارستان</v>
+        <v>دهاقان</v>
       </c>
       <c r="D419">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="420">
       <c r="A420">
-        <v>12300020</v>
+        <v>11000022</v>
       </c>
       <c r="B420" t="str">
-        <v>پردیس</v>
+        <v>برخوار</v>
       </c>
       <c r="C420" t="str">
-        <v>پردیس</v>
+        <v>برخوار</v>
       </c>
       <c r="D420">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="421">
       <c r="A421">
-        <v>12300021</v>
+        <v>11000023</v>
       </c>
       <c r="B421" t="str">
-        <v>قرچک</v>
+        <v>خور و بیابانک</v>
       </c>
       <c r="C421" t="str">
-        <v>قرچک</v>
+        <v>خور-و-بیابانک</v>
       </c>
       <c r="D421">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="422">
       <c r="A422">
-        <v>12400001</v>
+        <v>11000024</v>
       </c>
       <c r="B422" t="str">
-        <v>اردبیل</v>
+        <v>بویین و میاندشت</v>
       </c>
       <c r="C422" t="str">
-        <v>اردبیل</v>
+        <v>بویین-و-میاندشت</v>
       </c>
       <c r="D422">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="423">
       <c r="A423">
-        <v>12400002</v>
+        <v>11000025</v>
       </c>
       <c r="B423" t="str">
-        <v>بیله سوار</v>
+        <v>کوهپایه</v>
       </c>
       <c r="C423" t="str">
-        <v>بیله-سوار</v>
+        <v>کوهپایه</v>
       </c>
       <c r="D423">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="424">
       <c r="A424">
-        <v>12400003</v>
+        <v>11000026</v>
       </c>
       <c r="B424" t="str">
-        <v>خلخال</v>
+        <v>جرقویه</v>
       </c>
       <c r="C424" t="str">
-        <v>خلخال</v>
+        <v>جرقویه</v>
       </c>
       <c r="D424">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="425">
       <c r="A425">
-        <v>12400004</v>
+        <v>11000027</v>
       </c>
       <c r="B425" t="str">
-        <v>مشگین شهر</v>
+        <v>ورزنه</v>
       </c>
       <c r="C425" t="str">
-        <v>مشگین-شهر</v>
+        <v>ورزنه</v>
       </c>
       <c r="D425">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="426">
       <c r="A426">
-        <v>12400005</v>
+        <v>11000028</v>
       </c>
       <c r="B426" t="str">
-        <v>گرمی</v>
+        <v>هرند</v>
       </c>
       <c r="C426" t="str">
-        <v>گرمی</v>
+        <v>هرند</v>
       </c>
       <c r="D426">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="427">
       <c r="A427">
-        <v>12400006</v>
+        <v>11100010</v>
       </c>
       <c r="B427" t="str">
-        <v>پارس آباد</v>
+        <v>زهک</v>
       </c>
       <c r="C427" t="str">
-        <v>پارس-آباد</v>
+        <v>زهک</v>
       </c>
       <c r="D427">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="428">
       <c r="A428">
-        <v>12400007</v>
+        <v>11100011</v>
       </c>
       <c r="B428" t="str">
-        <v>کوثر</v>
+        <v>هیرمند</v>
       </c>
       <c r="C428" t="str">
-        <v>کوثر</v>
+        <v>هیرمند</v>
       </c>
       <c r="D428">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="429">
       <c r="A429">
-        <v>12400008</v>
+        <v>11100012</v>
       </c>
       <c r="B429" t="str">
-        <v>نمین</v>
+        <v>دلگان</v>
       </c>
       <c r="C429" t="str">
-        <v>نمین</v>
+        <v>دلگان</v>
       </c>
       <c r="D429">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="430">
       <c r="A430">
-        <v>12400009</v>
+        <v>11100013</v>
       </c>
       <c r="B430" t="str">
-        <v>نیر</v>
+        <v>مهرستان</v>
       </c>
       <c r="C430" t="str">
-        <v>نیر</v>
+        <v>مهرستان</v>
       </c>
       <c r="D430">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="431">
       <c r="A431">
-        <v>12400010</v>
+        <v>11100014</v>
       </c>
       <c r="B431" t="str">
-        <v>سرعین</v>
+        <v>سیب و سوران</v>
       </c>
       <c r="C431" t="str">
-        <v>سرعین</v>
+        <v>سیب-و-سوران</v>
       </c>
       <c r="D431">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="432">
       <c r="A432">
-        <v>12400011</v>
+        <v>11100015</v>
       </c>
       <c r="B432" t="str">
-        <v>اصلاندوز</v>
+        <v>نیمروز</v>
       </c>
       <c r="C432" t="str">
-        <v>اصلاندوز</v>
+        <v>نیمروز</v>
       </c>
       <c r="D432">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="433">
       <c r="A433">
-        <v>12400012</v>
+        <v>11100016</v>
       </c>
       <c r="B433" t="str">
-        <v>انگوت</v>
+        <v>هامون</v>
       </c>
       <c r="C433" t="str">
-        <v>انگوت</v>
+        <v>هامون</v>
       </c>
       <c r="D433">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="434">
       <c r="A434">
-        <v>12500001</v>
+        <v>11100017</v>
       </c>
       <c r="B434" t="str">
-        <v>قم</v>
+        <v>میرجاوه</v>
       </c>
       <c r="C434" t="str">
-        <v>قم</v>
+        <v>میرجاوه</v>
       </c>
       <c r="D434">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="435">
       <c r="A435">
-        <v>12500002</v>
+        <v>11100018</v>
       </c>
       <c r="B435" t="str">
-        <v>جعفرآباد</v>
+        <v>قصرقند</v>
       </c>
       <c r="C435" t="str">
-        <v>جعفرآباد</v>
+        <v>قصرقند</v>
       </c>
       <c r="D435">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="436">
       <c r="A436">
-        <v>12500003</v>
+        <v>11100019</v>
       </c>
       <c r="B436" t="str">
-        <v>کهک</v>
+        <v>فنوج</v>
       </c>
       <c r="C436" t="str">
-        <v>کهک</v>
+        <v>فنوج</v>
       </c>
       <c r="D436">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="437">
       <c r="A437">
-        <v>12600001</v>
+        <v>11100020</v>
       </c>
       <c r="B437" t="str">
-        <v>بویین زهرا</v>
+        <v>بمپور</v>
       </c>
       <c r="C437" t="str">
-        <v>بویین-زهرا</v>
+        <v>بمپور</v>
       </c>
       <c r="D437">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="438">
       <c r="A438">
-        <v>12600002</v>
+        <v>11100021</v>
       </c>
       <c r="B438" t="str">
-        <v>تاکستان</v>
+        <v>تفتان</v>
       </c>
       <c r="C438" t="str">
-        <v>تاکستان</v>
+        <v>تفتان</v>
       </c>
       <c r="D438">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="439">
       <c r="A439">
-        <v>12600003</v>
+        <v>11100022</v>
       </c>
       <c r="B439" t="str">
-        <v>قزوین</v>
+        <v>دشتیاری</v>
       </c>
       <c r="C439" t="str">
-        <v>قزوین</v>
+        <v>دشتیاری</v>
       </c>
       <c r="D439">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="440">
       <c r="A440">
-        <v>12600004</v>
+        <v>11100023</v>
       </c>
       <c r="B440" t="str">
-        <v>آبیک</v>
+        <v>سرباز</v>
       </c>
       <c r="C440" t="str">
-        <v>آبیک</v>
+        <v>سرباز</v>
       </c>
       <c r="D440">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="441">
       <c r="A441">
-        <v>12600005</v>
+        <v>11100024</v>
       </c>
       <c r="B441" t="str">
-        <v>البرز</v>
+        <v>گلشن</v>
       </c>
       <c r="C441" t="str">
-        <v>البرز</v>
+        <v>گلشن</v>
       </c>
       <c r="D441">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="442">
       <c r="A442">
-        <v>12600006</v>
+        <v>11100025</v>
       </c>
       <c r="B442" t="str">
-        <v>آوج</v>
+        <v>لاشار</v>
       </c>
       <c r="C442" t="str">
-        <v>آوج</v>
+        <v>لاشار</v>
       </c>
       <c r="D442">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="443">
       <c r="A443">
-        <v>12700001</v>
+        <v>11100026</v>
       </c>
       <c r="B443" t="str">
-        <v>بندرگز</v>
+        <v>زرآباد</v>
       </c>
       <c r="C443" t="str">
-        <v>بندرگز</v>
+        <v>زرآباد</v>
       </c>
       <c r="D443">
-        <v>127</v>
+        <v>111</v>
       </c>
     </row>
     <row r="444">
       <c r="A444">
-        <v>12700002</v>
+        <v>11200010</v>
       </c>
       <c r="B444" t="str">
-        <v>ترکمن</v>
+        <v>دهگلان</v>
       </c>
       <c r="C444" t="str">
-        <v>ترکمن</v>
+        <v>دهگلان</v>
       </c>
       <c r="D444">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="445">
       <c r="A445">
-        <v>12700003</v>
+        <v>11300010</v>
       </c>
       <c r="B445" t="str">
-        <v>علی آباد کتول</v>
+        <v>درگزین</v>
       </c>
       <c r="C445" t="str">
-        <v>علی-آباد-کتول</v>
+        <v>درگزین</v>
       </c>
       <c r="D445">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="446">
       <c r="A446">
-        <v>12700004</v>
+        <v>11400010</v>
       </c>
       <c r="B446" t="str">
-        <v>کردکوی</v>
+        <v>خانمیرزا</v>
       </c>
       <c r="C446" t="str">
-        <v>کردکوی</v>
+        <v>خانمیرزا</v>
       </c>
       <c r="D446">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="447">
       <c r="A447">
-        <v>12700005</v>
+        <v>11400011</v>
       </c>
       <c r="B447" t="str">
-        <v>گرگان</v>
+        <v>فلارد</v>
       </c>
       <c r="C447" t="str">
-        <v>گرگان</v>
+        <v>فلارد</v>
       </c>
       <c r="D447">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="448">
       <c r="A448">
-        <v>12700006</v>
+        <v>11400012</v>
       </c>
       <c r="B448" t="str">
-        <v>گنبدکاووس</v>
+        <v>فرخ شهر</v>
       </c>
       <c r="C448" t="str">
-        <v>گنبدکاووس</v>
+        <v>فرخ-شهر</v>
       </c>
       <c r="D448">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="449">
       <c r="A449">
-        <v>12700007</v>
+        <v>11500010</v>
       </c>
       <c r="B449" t="str">
-        <v>مینودشت</v>
+        <v>چگنی</v>
       </c>
       <c r="C449" t="str">
-        <v>مینودشت</v>
+        <v>چگنی</v>
       </c>
       <c r="D449">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="450">
       <c r="A450">
-        <v>12700008</v>
+        <v>11500011</v>
       </c>
       <c r="B450" t="str">
-        <v>آق قلا</v>
+        <v>رومشکان</v>
       </c>
       <c r="C450" t="str">
-        <v>آق-قلا</v>
+        <v>رومشکان</v>
       </c>
       <c r="D450">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="451">
       <c r="A451">
-        <v>12700009</v>
+        <v>11500012</v>
       </c>
       <c r="B451" t="str">
-        <v>کلاله</v>
+        <v>معمولان</v>
       </c>
       <c r="C451" t="str">
-        <v>کلاله</v>
+        <v>معمولان</v>
       </c>
       <c r="D451">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="452">
       <c r="A452">
-        <v>12700010</v>
+        <v>11600010</v>
       </c>
       <c r="B452" t="str">
-        <v>آزادشهر</v>
+        <v>بدره</v>
       </c>
       <c r="C452" t="str">
-        <v>آزادشهر</v>
+        <v>بدره</v>
       </c>
       <c r="D452">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="453">
       <c r="A453">
-        <v>12700011</v>
+        <v>11600011</v>
       </c>
       <c r="B453" t="str">
-        <v>رامیان</v>
+        <v>هلیلان</v>
       </c>
       <c r="C453" t="str">
-        <v>رامیان</v>
+        <v>هلیلان</v>
       </c>
       <c r="D453">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="454">
       <c r="A454">
-        <v>12700012</v>
+        <v>11600012</v>
       </c>
       <c r="B454" t="str">
-        <v>مراوه تپه</v>
+        <v>چوار</v>
       </c>
       <c r="C454" t="str">
-        <v>مراوه-تپه</v>
+        <v>چوار</v>
       </c>
       <c r="D454">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="455">
       <c r="A455">
-        <v>12700013</v>
+        <v>11800010</v>
       </c>
       <c r="B455" t="str">
-        <v>گمیشان</v>
+        <v>عسلویه</v>
       </c>
       <c r="C455" t="str">
-        <v>گمیشان</v>
+        <v>عسلویه</v>
       </c>
       <c r="D455">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="456">
       <c r="A456">
-        <v>12700014</v>
+        <v>11900010</v>
       </c>
       <c r="B456" t="str">
-        <v>گالیکش</v>
+        <v>سلطانیه</v>
       </c>
       <c r="C456" t="str">
-        <v>گالیکش</v>
+        <v>سلطانیه</v>
       </c>
       <c r="D456">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="457">
       <c r="A457">
-        <v>12800001</v>
+        <v>12100011</v>
       </c>
       <c r="B457" t="str">
-        <v>اسفراین</v>
+        <v>بهاباد</v>
       </c>
       <c r="C457" t="str">
-        <v>اسفراین</v>
+        <v>بهاباد</v>
       </c>
       <c r="D457">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="458">
       <c r="A458">
-        <v>12800002</v>
+        <v>12100012</v>
       </c>
       <c r="B458" t="str">
-        <v>بجنورد</v>
+        <v>مروست</v>
       </c>
       <c r="C458" t="str">
-        <v>بجنورد</v>
+        <v>مروست</v>
       </c>
       <c r="D458">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="459">
       <c r="A459">
-        <v>12800003</v>
+        <v>12100013</v>
       </c>
       <c r="B459" t="str">
-        <v>جاجرم</v>
+        <v>زارچ</v>
       </c>
       <c r="C459" t="str">
-        <v>جاجرم</v>
+        <v>زارچ</v>
       </c>
       <c r="D459">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="460">
       <c r="A460">
-        <v>12800004</v>
+        <v>12200010</v>
       </c>
       <c r="B460" t="str">
-        <v>شیروان</v>
+        <v>خمیر</v>
       </c>
       <c r="C460" t="str">
-        <v>شیروان</v>
+        <v>خمیر</v>
       </c>
       <c r="D460">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="461">
       <c r="A461">
-        <v>12800005</v>
+        <v>12200011</v>
       </c>
       <c r="B461" t="str">
-        <v>فاروج</v>
+        <v>پارسیان</v>
       </c>
       <c r="C461" t="str">
-        <v>فاروج</v>
+        <v>پارسیان</v>
       </c>
       <c r="D461">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="462">
       <c r="A462">
-        <v>12800006</v>
+        <v>12200012</v>
       </c>
       <c r="B462" t="str">
-        <v>سملقان</v>
+        <v>سیریک</v>
       </c>
       <c r="C462" t="str">
-        <v>سملقان</v>
+        <v>سیریک</v>
       </c>
       <c r="D462">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="463">
       <c r="A463">
-        <v>12800007</v>
+        <v>12200013</v>
       </c>
       <c r="B463" t="str">
-        <v>گرمه</v>
+        <v>بشاگرد</v>
       </c>
       <c r="C463" t="str">
-        <v>گرمه</v>
+        <v>بشاگرد</v>
       </c>
       <c r="D463">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="464">
       <c r="A464">
-        <v>12800008</v>
+        <v>12300010</v>
       </c>
       <c r="B464" t="str">
-        <v>راز و جرگلان</v>
+        <v>اسلامشهر</v>
       </c>
       <c r="C464" t="str">
-        <v>راز-و-جرگلان</v>
+        <v>اسلامشهر</v>
       </c>
       <c r="D464">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="465">
       <c r="A465">
-        <v>12800009</v>
+        <v>12300012</v>
       </c>
       <c r="B465" t="str">
-        <v>بام و صفی آباد</v>
+        <v>رباط‌کریم</v>
       </c>
       <c r="C465" t="str">
-        <v>بام-و-صفی-آباد</v>
+        <v>رباط-کریم</v>
       </c>
       <c r="D465">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="466">
       <c r="A466">
-        <v>12800010</v>
+        <v>12300013</v>
       </c>
       <c r="B466" t="str">
-        <v>مانه</v>
+        <v>پاکدشت</v>
       </c>
       <c r="C466" t="str">
-        <v>مانه</v>
+        <v>پاکدشت</v>
       </c>
       <c r="D466">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="467">
       <c r="A467">
-        <v>12900001</v>
+        <v>12300014</v>
       </c>
       <c r="B467" t="str">
-        <v>بیرجند</v>
+        <v>فیروزکوه</v>
       </c>
       <c r="C467" t="str">
-        <v>بیرجند</v>
+        <v>فیروزکوه</v>
       </c>
       <c r="D467">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="468">
       <c r="A468">
-        <v>12900002</v>
+        <v>12300016</v>
       </c>
       <c r="B468" t="str">
-        <v>درمیان</v>
+        <v>قدس</v>
       </c>
       <c r="C468" t="str">
-        <v>درمیان</v>
+        <v>قدس</v>
       </c>
       <c r="D468">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="469">
       <c r="A469">
-        <v>12900003</v>
+        <v>12300017</v>
       </c>
       <c r="B469" t="str">
-        <v>سربیشه</v>
+        <v>ملارد</v>
       </c>
       <c r="C469" t="str">
-        <v>سربیشه</v>
+        <v>ملارد</v>
       </c>
       <c r="D469">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="470">
       <c r="A470">
-        <v>12900004</v>
+        <v>12300018</v>
       </c>
       <c r="B470" t="str">
-        <v>قاینات</v>
+        <v>پیشوا</v>
       </c>
       <c r="C470" t="str">
-        <v>قاینات</v>
+        <v>پیشوا</v>
       </c>
       <c r="D470">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="471">
       <c r="A471">
-        <v>12900005</v>
+        <v>12300019</v>
       </c>
       <c r="B471" t="str">
-        <v>نهبندان</v>
+        <v>بهارستان</v>
       </c>
       <c r="C471" t="str">
-        <v>نهبندان</v>
+        <v>بهارستان</v>
       </c>
       <c r="D471">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="472">
       <c r="A472">
-        <v>12900006</v>
+        <v>12300020</v>
       </c>
       <c r="B472" t="str">
-        <v>سرایان</v>
+        <v>پردیس</v>
       </c>
       <c r="C472" t="str">
-        <v>سرایان</v>
+        <v>پردیس</v>
       </c>
       <c r="D472">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="473">
       <c r="A473">
-        <v>12900007</v>
+        <v>12300021</v>
       </c>
       <c r="B473" t="str">
-        <v>فردوس</v>
+        <v>قرچک</v>
       </c>
       <c r="C473" t="str">
-        <v>فردوس</v>
+        <v>قرچک</v>
       </c>
       <c r="D473">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="474">
       <c r="A474">
-        <v>12900008</v>
+        <v>12400010</v>
       </c>
       <c r="B474" t="str">
-        <v>بشرویه</v>
+        <v>سرعین</v>
       </c>
       <c r="C474" t="str">
-        <v>بشرویه</v>
+        <v>سرعین</v>
       </c>
       <c r="D474">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="475">
       <c r="A475">
-        <v>12900009</v>
+        <v>12400011</v>
       </c>
       <c r="B475" t="str">
-        <v>زیرکوه</v>
+        <v>اصلاندوز</v>
       </c>
       <c r="C475" t="str">
-        <v>زیرکوه</v>
+        <v>اصلاندوز</v>
       </c>
       <c r="D475">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="476">
       <c r="A476">
-        <v>12900010</v>
+        <v>12400012</v>
       </c>
       <c r="B476" t="str">
-        <v>خوسف</v>
+        <v>انگوت</v>
       </c>
       <c r="C476" t="str">
-        <v>خوسف</v>
+        <v>انگوت</v>
       </c>
       <c r="D476">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="477">
       <c r="A477">
-        <v>12900011</v>
+        <v>12700010</v>
       </c>
       <c r="B477" t="str">
-        <v>طبس</v>
+        <v>آزادشهر</v>
       </c>
       <c r="C477" t="str">
-        <v>طبس</v>
+        <v>آزادشهر</v>
       </c>
       <c r="D477">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="478">
       <c r="A478">
-        <v>12900012</v>
+        <v>12700011</v>
       </c>
       <c r="B478" t="str">
-        <v>عشق آباد</v>
+        <v>رامیان</v>
       </c>
       <c r="C478" t="str">
-        <v>عشق-آباد</v>
+        <v>رامیان</v>
       </c>
       <c r="D478">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="479">
       <c r="A479">
-        <v>13000001</v>
+        <v>12700012</v>
       </c>
       <c r="B479" t="str">
-        <v>کرج</v>
+        <v>مراوه تپه</v>
       </c>
       <c r="C479" t="str">
-        <v>کرج</v>
+        <v>مراوه-تپه</v>
       </c>
       <c r="D479">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="480">
       <c r="A480">
-        <v>13000002</v>
+        <v>12700013</v>
       </c>
       <c r="B480" t="str">
-        <v>ساوجبلاغ</v>
+        <v>گمیشان</v>
       </c>
       <c r="C480" t="str">
-        <v>ساوجبلاغ</v>
+        <v>گمیشان</v>
       </c>
       <c r="D480">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="481">
       <c r="A481">
-        <v>13000003</v>
+        <v>12700014</v>
       </c>
       <c r="B481" t="str">
-        <v>نظرآباد</v>
+        <v>گالیکش</v>
       </c>
       <c r="C481" t="str">
-        <v>نظرآباد</v>
+        <v>گالیکش</v>
       </c>
       <c r="D481">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="482">
       <c r="A482">
-        <v>13000004</v>
+        <v>12800010</v>
       </c>
       <c r="B482" t="str">
-        <v>طالقان</v>
+        <v>مانه</v>
       </c>
       <c r="C482" t="str">
-        <v>طالقان</v>
+        <v>مانه</v>
       </c>
       <c r="D482">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="483">
       <c r="A483">
-        <v>13000005</v>
+        <v>12900010</v>
       </c>
       <c r="B483" t="str">
-        <v>اشتهارد</v>
+        <v>خوسف</v>
       </c>
       <c r="C483" t="str">
-        <v>اشتهارد</v>
+        <v>خوسف</v>
       </c>
       <c r="D483">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="484">
       <c r="A484">
-        <v>13000006</v>
+        <v>12900011</v>
       </c>
       <c r="B484" t="str">
-        <v>فردیس</v>
+        <v>طبس</v>
       </c>
       <c r="C484" t="str">
-        <v>فردیس</v>
+        <v>طبس</v>
       </c>
       <c r="D484">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="485">
       <c r="A485">
-        <v>13000007</v>
+        <v>12900012</v>
       </c>
       <c r="B485" t="str">
-        <v>چهارباغ</v>
+        <v>عشق آباد</v>
       </c>
       <c r="C485" t="str">
-        <v>چهارباغ</v>
+        <v>عشق-آباد</v>
       </c>
       <c r="D485">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/dist/xlsx/counties.xlsx
+++ b/dist/xlsx/counties.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D483"/>
+  <dimension ref="A1:D485"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1132,7 +1132,7 @@
         <v>1060005</v>
       </c>
       <c r="B53" t="str">
-        <v>بندرماهشهر</v>
+        <v>بندر ماهشهر</v>
       </c>
       <c r="C53" t="str">
         <v>بندرماهشهر</v>
@@ -4506,7 +4506,7 @@
         <v>10300026</v>
       </c>
       <c r="B294" t="str">
-        <v>خداآفرین</v>
+        <v>خدا آفرین</v>
       </c>
       <c r="C294" t="str">
         <v>خداآفرین</v>
@@ -4545,27 +4545,27 @@
     </row>
     <row r="297">
       <c r="A297">
-        <v>10400010</v>
+        <v>10300029</v>
       </c>
       <c r="B297" t="str">
-        <v>بوکان</v>
+        <v>ترکمانچای</v>
       </c>
       <c r="C297" t="str">
-        <v>بوکان</v>
+        <v>ترکمانچای</v>
       </c>
       <c r="D297">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="298">
       <c r="A298">
-        <v>10400011</v>
+        <v>10400010</v>
       </c>
       <c r="B298" t="str">
-        <v>شاهین دژ</v>
+        <v>بوکان</v>
       </c>
       <c r="C298" t="str">
-        <v>شاهین-دژ</v>
+        <v>بوکان</v>
       </c>
       <c r="D298">
         <v>104</v>
@@ -4573,13 +4573,13 @@
     </row>
     <row r="299">
       <c r="A299">
-        <v>10400012</v>
+        <v>10400011</v>
       </c>
       <c r="B299" t="str">
-        <v>تکاب</v>
+        <v>شاهین دژ</v>
       </c>
       <c r="C299" t="str">
-        <v>تکاب</v>
+        <v>شاهین-دژ</v>
       </c>
       <c r="D299">
         <v>104</v>
@@ -4587,13 +4587,13 @@
     </row>
     <row r="300">
       <c r="A300">
-        <v>10400013</v>
+        <v>10400012</v>
       </c>
       <c r="B300" t="str">
-        <v>اشنویه</v>
+        <v>تکاب</v>
       </c>
       <c r="C300" t="str">
-        <v>اشنویه</v>
+        <v>تکاب</v>
       </c>
       <c r="D300">
         <v>104</v>
@@ -4601,13 +4601,13 @@
     </row>
     <row r="301">
       <c r="A301">
-        <v>10400014</v>
+        <v>10400013</v>
       </c>
       <c r="B301" t="str">
-        <v>چالدران</v>
+        <v>اشنویه</v>
       </c>
       <c r="C301" t="str">
-        <v>چالدران</v>
+        <v>اشنویه</v>
       </c>
       <c r="D301">
         <v>104</v>
@@ -4615,13 +4615,13 @@
     </row>
     <row r="302">
       <c r="A302">
-        <v>10400015</v>
+        <v>10400014</v>
       </c>
       <c r="B302" t="str">
-        <v>پلدشت</v>
+        <v>چالدران</v>
       </c>
       <c r="C302" t="str">
-        <v>پلدشت</v>
+        <v>چالدران</v>
       </c>
       <c r="D302">
         <v>104</v>
@@ -4629,13 +4629,13 @@
     </row>
     <row r="303">
       <c r="A303">
-        <v>10400016</v>
+        <v>10400015</v>
       </c>
       <c r="B303" t="str">
-        <v>چایپاره</v>
+        <v>پلدشت</v>
       </c>
       <c r="C303" t="str">
-        <v>چایپاره</v>
+        <v>پلدشت</v>
       </c>
       <c r="D303">
         <v>104</v>
@@ -4643,13 +4643,13 @@
     </row>
     <row r="304">
       <c r="A304">
-        <v>10400017</v>
+        <v>10400016</v>
       </c>
       <c r="B304" t="str">
-        <v>شوط</v>
+        <v>چایپاره</v>
       </c>
       <c r="C304" t="str">
-        <v>شوط</v>
+        <v>چایپاره</v>
       </c>
       <c r="D304">
         <v>104</v>
@@ -4657,13 +4657,13 @@
     </row>
     <row r="305">
       <c r="A305">
-        <v>10400018</v>
+        <v>10400017</v>
       </c>
       <c r="B305" t="str">
-        <v>چهاربرج</v>
+        <v>شوط</v>
       </c>
       <c r="C305" t="str">
-        <v>چهاربرج</v>
+        <v>شوط</v>
       </c>
       <c r="D305">
         <v>104</v>
@@ -4671,13 +4671,13 @@
     </row>
     <row r="306">
       <c r="A306">
-        <v>10400019</v>
+        <v>10400018</v>
       </c>
       <c r="B306" t="str">
-        <v>باروق</v>
+        <v>چهاربرج</v>
       </c>
       <c r="C306" t="str">
-        <v>باروق</v>
+        <v>چهاربرج</v>
       </c>
       <c r="D306">
         <v>104</v>
@@ -4685,13 +4685,13 @@
     </row>
     <row r="307">
       <c r="A307">
-        <v>10400020</v>
+        <v>10400019</v>
       </c>
       <c r="B307" t="str">
-        <v>میرآباد</v>
+        <v>باروق</v>
       </c>
       <c r="C307" t="str">
-        <v>میرآباد</v>
+        <v>باروق</v>
       </c>
       <c r="D307">
         <v>104</v>
@@ -4699,27 +4699,27 @@
     </row>
     <row r="308">
       <c r="A308">
-        <v>10500010</v>
+        <v>10400020</v>
       </c>
       <c r="B308" t="str">
-        <v>صحنه</v>
+        <v>میرآباد</v>
       </c>
       <c r="C308" t="str">
-        <v>صحنه</v>
+        <v>میرآباد</v>
       </c>
       <c r="D308">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="309">
       <c r="A309">
-        <v>10500011</v>
+        <v>10500010</v>
       </c>
       <c r="B309" t="str">
-        <v>هرسین</v>
+        <v>صحنه</v>
       </c>
       <c r="C309" t="str">
-        <v>هرسین</v>
+        <v>صحنه</v>
       </c>
       <c r="D309">
         <v>105</v>
@@ -4727,13 +4727,13 @@
     </row>
     <row r="310">
       <c r="A310">
-        <v>10500012</v>
+        <v>10500011</v>
       </c>
       <c r="B310" t="str">
-        <v>ثلاث باباجانی</v>
+        <v>هرسین</v>
       </c>
       <c r="C310" t="str">
-        <v>ثلاث-باباجانی</v>
+        <v>هرسین</v>
       </c>
       <c r="D310">
         <v>105</v>
@@ -4741,13 +4741,13 @@
     </row>
     <row r="311">
       <c r="A311">
-        <v>10500013</v>
+        <v>10500012</v>
       </c>
       <c r="B311" t="str">
-        <v>دالاهو</v>
+        <v>ثلاث باباجانی</v>
       </c>
       <c r="C311" t="str">
-        <v>دالاهو</v>
+        <v>ثلاث-باباجانی</v>
       </c>
       <c r="D311">
         <v>105</v>
@@ -4755,13 +4755,13 @@
     </row>
     <row r="312">
       <c r="A312">
-        <v>10500014</v>
+        <v>10500013</v>
       </c>
       <c r="B312" t="str">
-        <v>روانسر</v>
+        <v>دالاهو</v>
       </c>
       <c r="C312" t="str">
-        <v>روانسر</v>
+        <v>دالاهو</v>
       </c>
       <c r="D312">
         <v>105</v>
@@ -4769,27 +4769,27 @@
     </row>
     <row r="313">
       <c r="A313">
-        <v>10600010</v>
+        <v>10500014</v>
       </c>
       <c r="B313" t="str">
-        <v>رامهرمز</v>
+        <v>روانسر</v>
       </c>
       <c r="C313" t="str">
-        <v>رامهرمز</v>
+        <v>روانسر</v>
       </c>
       <c r="D313">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="314">
       <c r="A314">
-        <v>10600011</v>
+        <v>10600010</v>
       </c>
       <c r="B314" t="str">
-        <v>شادگان</v>
+        <v>رامهرمز</v>
       </c>
       <c r="C314" t="str">
-        <v>شادگان</v>
+        <v>رامهرمز</v>
       </c>
       <c r="D314">
         <v>106</v>
@@ -4797,13 +4797,13 @@
     </row>
     <row r="315">
       <c r="A315">
-        <v>10600012</v>
+        <v>10600011</v>
       </c>
       <c r="B315" t="str">
-        <v>شوشتر</v>
+        <v>شادگان</v>
       </c>
       <c r="C315" t="str">
-        <v>شوشتر</v>
+        <v>شادگان</v>
       </c>
       <c r="D315">
         <v>106</v>
@@ -4811,13 +4811,13 @@
     </row>
     <row r="316">
       <c r="A316">
-        <v>10600013</v>
+        <v>10600012</v>
       </c>
       <c r="B316" t="str">
-        <v>مسجدسلیمان</v>
+        <v>شوشتر</v>
       </c>
       <c r="C316" t="str">
-        <v>مسجدسلیمان</v>
+        <v>شوشتر</v>
       </c>
       <c r="D316">
         <v>106</v>
@@ -4825,13 +4825,13 @@
     </row>
     <row r="317">
       <c r="A317">
-        <v>10600014</v>
+        <v>10600013</v>
       </c>
       <c r="B317" t="str">
-        <v>شوش</v>
+        <v>مسجدسلیمان</v>
       </c>
       <c r="C317" t="str">
-        <v>شوش</v>
+        <v>مسجدسلیمان</v>
       </c>
       <c r="D317">
         <v>106</v>
@@ -4839,13 +4839,13 @@
     </row>
     <row r="318">
       <c r="A318">
-        <v>10600015</v>
+        <v>10600014</v>
       </c>
       <c r="B318" t="str">
-        <v>باغ ملک</v>
+        <v>شوش</v>
       </c>
       <c r="C318" t="str">
-        <v>باغ-ملک</v>
+        <v>شوش</v>
       </c>
       <c r="D318">
         <v>106</v>
@@ -4853,13 +4853,13 @@
     </row>
     <row r="319">
       <c r="A319">
-        <v>10600016</v>
+        <v>10600015</v>
       </c>
       <c r="B319" t="str">
-        <v>امیدیه</v>
+        <v>باغ ملک</v>
       </c>
       <c r="C319" t="str">
-        <v>امیدیه</v>
+        <v>باغ-ملک</v>
       </c>
       <c r="D319">
         <v>106</v>
@@ -4867,13 +4867,13 @@
     </row>
     <row r="320">
       <c r="A320">
-        <v>10600017</v>
+        <v>10600016</v>
       </c>
       <c r="B320" t="str">
-        <v>لالی</v>
+        <v>امیدیه</v>
       </c>
       <c r="C320" t="str">
-        <v>لالی</v>
+        <v>امیدیه</v>
       </c>
       <c r="D320">
         <v>106</v>
@@ -4881,13 +4881,13 @@
     </row>
     <row r="321">
       <c r="A321">
-        <v>10600018</v>
+        <v>10600017</v>
       </c>
       <c r="B321" t="str">
-        <v>هندیجان</v>
+        <v>لالی</v>
       </c>
       <c r="C321" t="str">
-        <v>هندیجان</v>
+        <v>لالی</v>
       </c>
       <c r="D321">
         <v>106</v>
@@ -4895,13 +4895,13 @@
     </row>
     <row r="322">
       <c r="A322">
-        <v>10600019</v>
+        <v>10600018</v>
       </c>
       <c r="B322" t="str">
-        <v>رامشیر</v>
+        <v>هندیجان</v>
       </c>
       <c r="C322" t="str">
-        <v>رامشیر</v>
+        <v>هندیجان</v>
       </c>
       <c r="D322">
         <v>106</v>
@@ -4909,13 +4909,13 @@
     </row>
     <row r="323">
       <c r="A323">
-        <v>10600020</v>
+        <v>10600019</v>
       </c>
       <c r="B323" t="str">
-        <v>گتوند</v>
+        <v>رامشیر</v>
       </c>
       <c r="C323" t="str">
-        <v>گتوند</v>
+        <v>رامشیر</v>
       </c>
       <c r="D323">
         <v>106</v>
@@ -4923,13 +4923,13 @@
     </row>
     <row r="324">
       <c r="A324">
-        <v>10600021</v>
+        <v>10600020</v>
       </c>
       <c r="B324" t="str">
-        <v>اندیکا</v>
+        <v>گتوند</v>
       </c>
       <c r="C324" t="str">
-        <v>اندیکا</v>
+        <v>گتوند</v>
       </c>
       <c r="D324">
         <v>106</v>
@@ -4937,13 +4937,13 @@
     </row>
     <row r="325">
       <c r="A325">
-        <v>10600022</v>
+        <v>10600021</v>
       </c>
       <c r="B325" t="str">
-        <v>هفتکل</v>
+        <v>اندیکا</v>
       </c>
       <c r="C325" t="str">
-        <v>هفتکل</v>
+        <v>اندیکا</v>
       </c>
       <c r="D325">
         <v>106</v>
@@ -4951,13 +4951,13 @@
     </row>
     <row r="326">
       <c r="A326">
-        <v>10600023</v>
+        <v>10600022</v>
       </c>
       <c r="B326" t="str">
-        <v>هویزه</v>
+        <v>هفتکل</v>
       </c>
       <c r="C326" t="str">
-        <v>هویزه</v>
+        <v>هفتکل</v>
       </c>
       <c r="D326">
         <v>106</v>
@@ -4965,13 +4965,13 @@
     </row>
     <row r="327">
       <c r="A327">
-        <v>10600024</v>
+        <v>10600023</v>
       </c>
       <c r="B327" t="str">
-        <v>باوی</v>
+        <v>هویزه</v>
       </c>
       <c r="C327" t="str">
-        <v>باوی</v>
+        <v>هویزه</v>
       </c>
       <c r="D327">
         <v>106</v>
@@ -4979,13 +4979,13 @@
     </row>
     <row r="328">
       <c r="A328">
-        <v>10600025</v>
+        <v>10600024</v>
       </c>
       <c r="B328" t="str">
-        <v>حمیدیه</v>
+        <v>باوی</v>
       </c>
       <c r="C328" t="str">
-        <v>حمیدیه</v>
+        <v>باوی</v>
       </c>
       <c r="D328">
         <v>106</v>
@@ -4993,13 +4993,13 @@
     </row>
     <row r="329">
       <c r="A329">
-        <v>10600026</v>
+        <v>10600025</v>
       </c>
       <c r="B329" t="str">
-        <v>آغاجاری</v>
+        <v>حمیدیه</v>
       </c>
       <c r="C329" t="str">
-        <v>آغاجاری</v>
+        <v>حمیدیه</v>
       </c>
       <c r="D329">
         <v>106</v>
@@ -5007,13 +5007,13 @@
     </row>
     <row r="330">
       <c r="A330">
-        <v>10600027</v>
+        <v>10600026</v>
       </c>
       <c r="B330" t="str">
-        <v>کارون</v>
+        <v>آغاجاری</v>
       </c>
       <c r="C330" t="str">
-        <v>کارون</v>
+        <v>آغاجاری</v>
       </c>
       <c r="D330">
         <v>106</v>
@@ -5021,13 +5021,13 @@
     </row>
     <row r="331">
       <c r="A331">
-        <v>10600028</v>
+        <v>10600027</v>
       </c>
       <c r="B331" t="str">
-        <v>کرخه</v>
+        <v>کارون</v>
       </c>
       <c r="C331" t="str">
-        <v>کرخه</v>
+        <v>کارون</v>
       </c>
       <c r="D331">
         <v>106</v>
@@ -5035,13 +5035,13 @@
     </row>
     <row r="332">
       <c r="A332">
-        <v>10600029</v>
+        <v>10600028</v>
       </c>
       <c r="B332" t="str">
-        <v>دزپارت</v>
+        <v>کرخه</v>
       </c>
       <c r="C332" t="str">
-        <v>دزپارت</v>
+        <v>کرخه</v>
       </c>
       <c r="D332">
         <v>106</v>
@@ -5049,13 +5049,13 @@
     </row>
     <row r="333">
       <c r="A333">
-        <v>10600030</v>
+        <v>10600029</v>
       </c>
       <c r="B333" t="str">
-        <v>صیدون</v>
+        <v>دزپارت</v>
       </c>
       <c r="C333" t="str">
-        <v>صیدون</v>
+        <v>دزپارت</v>
       </c>
       <c r="D333">
         <v>106</v>
@@ -5063,27 +5063,27 @@
     </row>
     <row r="334">
       <c r="A334">
-        <v>10700010</v>
+        <v>10600030</v>
       </c>
       <c r="B334" t="str">
-        <v>کازرون</v>
+        <v>صیدون</v>
       </c>
       <c r="C334" t="str">
-        <v>کازرون</v>
+        <v>صیدون</v>
       </c>
       <c r="D334">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="335">
       <c r="A335">
-        <v>10700011</v>
+        <v>10700010</v>
       </c>
       <c r="B335" t="str">
-        <v>لارستان</v>
+        <v>کازرون</v>
       </c>
       <c r="C335" t="str">
-        <v>لارستان</v>
+        <v>کازرون</v>
       </c>
       <c r="D335">
         <v>107</v>
@@ -5091,13 +5091,13 @@
     </row>
     <row r="336">
       <c r="A336">
-        <v>10700012</v>
+        <v>10700011</v>
       </c>
       <c r="B336" t="str">
-        <v>مرودشت</v>
+        <v>لارستان</v>
       </c>
       <c r="C336" t="str">
-        <v>مرودشت</v>
+        <v>لارستان</v>
       </c>
       <c r="D336">
         <v>107</v>
@@ -5105,13 +5105,13 @@
     </row>
     <row r="337">
       <c r="A337">
-        <v>10700013</v>
+        <v>10700012</v>
       </c>
       <c r="B337" t="str">
-        <v>ممسنی</v>
+        <v>مرودشت</v>
       </c>
       <c r="C337" t="str">
-        <v>ممسنی</v>
+        <v>مرودشت</v>
       </c>
       <c r="D337">
         <v>107</v>
@@ -5119,13 +5119,13 @@
     </row>
     <row r="338">
       <c r="A338">
-        <v>10700014</v>
+        <v>10700013</v>
       </c>
       <c r="B338" t="str">
-        <v>نی ریز</v>
+        <v>ممسنی</v>
       </c>
       <c r="C338" t="str">
-        <v>نی-ریز</v>
+        <v>ممسنی</v>
       </c>
       <c r="D338">
         <v>107</v>
@@ -5133,13 +5133,13 @@
     </row>
     <row r="339">
       <c r="A339">
-        <v>10700015</v>
+        <v>10700014</v>
       </c>
       <c r="B339" t="str">
-        <v>لامرد</v>
+        <v>نی ریز</v>
       </c>
       <c r="C339" t="str">
-        <v>لامرد</v>
+        <v>نی-ریز</v>
       </c>
       <c r="D339">
         <v>107</v>
@@ -5147,13 +5147,13 @@
     </row>
     <row r="340">
       <c r="A340">
-        <v>10700016</v>
+        <v>10700015</v>
       </c>
       <c r="B340" t="str">
-        <v>بوانات</v>
+        <v>لامرد</v>
       </c>
       <c r="C340" t="str">
-        <v>بوانات</v>
+        <v>لامرد</v>
       </c>
       <c r="D340">
         <v>107</v>
@@ -5161,13 +5161,13 @@
     </row>
     <row r="341">
       <c r="A341">
-        <v>10700017</v>
+        <v>10700016</v>
       </c>
       <c r="B341" t="str">
-        <v>ارسنجان</v>
+        <v>بوانات</v>
       </c>
       <c r="C341" t="str">
-        <v>ارسنجان</v>
+        <v>بوانات</v>
       </c>
       <c r="D341">
         <v>107</v>
@@ -5175,13 +5175,13 @@
     </row>
     <row r="342">
       <c r="A342">
-        <v>10700018</v>
+        <v>10700017</v>
       </c>
       <c r="B342" t="str">
-        <v>خرم بید</v>
+        <v>ارسنجان</v>
       </c>
       <c r="C342" t="str">
-        <v>خرم-بید</v>
+        <v>ارسنجان</v>
       </c>
       <c r="D342">
         <v>107</v>
@@ -5189,13 +5189,13 @@
     </row>
     <row r="343">
       <c r="A343">
-        <v>10700019</v>
+        <v>10700018</v>
       </c>
       <c r="B343" t="str">
-        <v>زرین دشت</v>
+        <v>خرم بید</v>
       </c>
       <c r="C343" t="str">
-        <v>زرین-دشت</v>
+        <v>خرم-بید</v>
       </c>
       <c r="D343">
         <v>107</v>
@@ -5203,13 +5203,13 @@
     </row>
     <row r="344">
       <c r="A344">
-        <v>10700020</v>
+        <v>10700019</v>
       </c>
       <c r="B344" t="str">
-        <v>قیروکارزین</v>
+        <v>زرین دشت</v>
       </c>
       <c r="C344" t="str">
-        <v>قیروکارزین</v>
+        <v>زرین-دشت</v>
       </c>
       <c r="D344">
         <v>107</v>
@@ -5217,13 +5217,13 @@
     </row>
     <row r="345">
       <c r="A345">
-        <v>10700021</v>
+        <v>10700020</v>
       </c>
       <c r="B345" t="str">
-        <v>مهر</v>
+        <v>قیرو کارزین</v>
       </c>
       <c r="C345" t="str">
-        <v>مهر</v>
+        <v>قیروکارزین</v>
       </c>
       <c r="D345">
         <v>107</v>
@@ -5231,13 +5231,13 @@
     </row>
     <row r="346">
       <c r="A346">
-        <v>10700022</v>
+        <v>10700021</v>
       </c>
       <c r="B346" t="str">
-        <v>فراشبند</v>
+        <v>مهر</v>
       </c>
       <c r="C346" t="str">
-        <v>فراشبند</v>
+        <v>مهر</v>
       </c>
       <c r="D346">
         <v>107</v>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="347">
       <c r="A347">
-        <v>10700023</v>
+        <v>10700022</v>
       </c>
       <c r="B347" t="str">
-        <v>پاسارگاد</v>
+        <v>فراشبند</v>
       </c>
       <c r="C347" t="str">
-        <v>پاسارگاد</v>
+        <v>فراشبند</v>
       </c>
       <c r="D347">
         <v>107</v>
@@ -5259,13 +5259,13 @@
     </row>
     <row r="348">
       <c r="A348">
-        <v>10700024</v>
+        <v>10700023</v>
       </c>
       <c r="B348" t="str">
-        <v>خنج</v>
+        <v>پاسارگاد</v>
       </c>
       <c r="C348" t="str">
-        <v>خنج</v>
+        <v>پاسارگاد</v>
       </c>
       <c r="D348">
         <v>107</v>
@@ -5273,13 +5273,13 @@
     </row>
     <row r="349">
       <c r="A349">
-        <v>10700025</v>
+        <v>10700024</v>
       </c>
       <c r="B349" t="str">
-        <v>سروستان</v>
+        <v>خنج</v>
       </c>
       <c r="C349" t="str">
-        <v>سروستان</v>
+        <v>خنج</v>
       </c>
       <c r="D349">
         <v>107</v>
@@ -5287,13 +5287,13 @@
     </row>
     <row r="350">
       <c r="A350">
-        <v>10700026</v>
+        <v>10700025</v>
       </c>
       <c r="B350" t="str">
-        <v>رستم</v>
+        <v>سروستان</v>
       </c>
       <c r="C350" t="str">
-        <v>رستم</v>
+        <v>سروستان</v>
       </c>
       <c r="D350">
         <v>107</v>
@@ -5301,13 +5301,13 @@
     </row>
     <row r="351">
       <c r="A351">
-        <v>10700027</v>
+        <v>10700026</v>
       </c>
       <c r="B351" t="str">
-        <v>گراش</v>
+        <v>رستم</v>
       </c>
       <c r="C351" t="str">
-        <v>گراش</v>
+        <v>رستم</v>
       </c>
       <c r="D351">
         <v>107</v>
@@ -5315,13 +5315,13 @@
     </row>
     <row r="352">
       <c r="A352">
-        <v>10700028</v>
+        <v>10700027</v>
       </c>
       <c r="B352" t="str">
-        <v>کوار</v>
+        <v>گراش</v>
       </c>
       <c r="C352" t="str">
-        <v>کوار</v>
+        <v>گراش</v>
       </c>
       <c r="D352">
         <v>107</v>
@@ -5329,13 +5329,13 @@
     </row>
     <row r="353">
       <c r="A353">
-        <v>10700029</v>
+        <v>10700028</v>
       </c>
       <c r="B353" t="str">
-        <v>خرامه</v>
+        <v>کوار</v>
       </c>
       <c r="C353" t="str">
-        <v>خرامه</v>
+        <v>کوار</v>
       </c>
       <c r="D353">
         <v>107</v>
@@ -5343,13 +5343,13 @@
     </row>
     <row r="354">
       <c r="A354">
-        <v>10700030</v>
+        <v>10700029</v>
       </c>
       <c r="B354" t="str">
-        <v>زرقان</v>
+        <v>خرامه</v>
       </c>
       <c r="C354" t="str">
-        <v>زرقان</v>
+        <v>خرامه</v>
       </c>
       <c r="D354">
         <v>107</v>
@@ -5357,13 +5357,13 @@
     </row>
     <row r="355">
       <c r="A355">
-        <v>10700031</v>
+        <v>10700030</v>
       </c>
       <c r="B355" t="str">
-        <v>بیضا</v>
+        <v>زرقان</v>
       </c>
       <c r="C355" t="str">
-        <v>بیضا</v>
+        <v>زرقان</v>
       </c>
       <c r="D355">
         <v>107</v>
@@ -5371,13 +5371,13 @@
     </row>
     <row r="356">
       <c r="A356">
-        <v>10700032</v>
+        <v>10700031</v>
       </c>
       <c r="B356" t="str">
-        <v>سرچهان</v>
+        <v>بیضاء</v>
       </c>
       <c r="C356" t="str">
-        <v>سرچهان</v>
+        <v>بیضا</v>
       </c>
       <c r="D356">
         <v>107</v>
@@ -5385,13 +5385,13 @@
     </row>
     <row r="357">
       <c r="A357">
-        <v>10700033</v>
+        <v>10700032</v>
       </c>
       <c r="B357" t="str">
-        <v>کوه چنار</v>
+        <v>سرچهان</v>
       </c>
       <c r="C357" t="str">
-        <v>کوه-چنار</v>
+        <v>سرچهان</v>
       </c>
       <c r="D357">
         <v>107</v>
@@ -5399,13 +5399,13 @@
     </row>
     <row r="358">
       <c r="A358">
-        <v>10700034</v>
+        <v>10700033</v>
       </c>
       <c r="B358" t="str">
-        <v>خفر</v>
+        <v>کوه چنار</v>
       </c>
       <c r="C358" t="str">
-        <v>خفر</v>
+        <v>کوه-چنار</v>
       </c>
       <c r="D358">
         <v>107</v>
@@ -5413,13 +5413,13 @@
     </row>
     <row r="359">
       <c r="A359">
-        <v>10700035</v>
+        <v>10700034</v>
       </c>
       <c r="B359" t="str">
-        <v>بختگان</v>
+        <v>خفر</v>
       </c>
       <c r="C359" t="str">
-        <v>بختگان</v>
+        <v>خفر</v>
       </c>
       <c r="D359">
         <v>107</v>
@@ -5427,13 +5427,13 @@
     </row>
     <row r="360">
       <c r="A360">
-        <v>10700036</v>
+        <v>10700035</v>
       </c>
       <c r="B360" t="str">
-        <v>اوز</v>
+        <v>بختگان</v>
       </c>
       <c r="C360" t="str">
-        <v>اوز</v>
+        <v>بختگان</v>
       </c>
       <c r="D360">
         <v>107</v>
@@ -5441,13 +5441,13 @@
     </row>
     <row r="361">
       <c r="A361">
-        <v>10700037</v>
+        <v>10700036</v>
       </c>
       <c r="B361" t="str">
-        <v>جویم</v>
+        <v>اوز</v>
       </c>
       <c r="C361" t="str">
-        <v>جویم</v>
+        <v>اوز</v>
       </c>
       <c r="D361">
         <v>107</v>
@@ -5455,27 +5455,27 @@
     </row>
     <row r="362">
       <c r="A362">
-        <v>10800010</v>
+        <v>10700037</v>
       </c>
       <c r="B362" t="str">
-        <v>بردسیر</v>
+        <v>جویم</v>
       </c>
       <c r="C362" t="str">
-        <v>بردسیر</v>
+        <v>جویم</v>
       </c>
       <c r="D362">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="363">
       <c r="A363">
-        <v>10800011</v>
+        <v>10800010</v>
       </c>
       <c r="B363" t="str">
-        <v>راور</v>
+        <v>بردسیر</v>
       </c>
       <c r="C363" t="str">
-        <v>راور</v>
+        <v>بردسیر</v>
       </c>
       <c r="D363">
         <v>108</v>
@@ -5483,13 +5483,13 @@
     </row>
     <row r="364">
       <c r="A364">
-        <v>10800012</v>
+        <v>10800011</v>
       </c>
       <c r="B364" t="str">
-        <v>عنبرآباد</v>
+        <v>راور</v>
       </c>
       <c r="C364" t="str">
-        <v>عنبرآباد</v>
+        <v>راور</v>
       </c>
       <c r="D364">
         <v>108</v>
@@ -5497,13 +5497,13 @@
     </row>
     <row r="365">
       <c r="A365">
-        <v>10800013</v>
+        <v>10800012</v>
       </c>
       <c r="B365" t="str">
-        <v>منوجان</v>
+        <v>عنبرآباد</v>
       </c>
       <c r="C365" t="str">
-        <v>منوجان</v>
+        <v>عنبرآباد</v>
       </c>
       <c r="D365">
         <v>108</v>
@@ -5511,13 +5511,13 @@
     </row>
     <row r="366">
       <c r="A366">
-        <v>10800014</v>
+        <v>10800013</v>
       </c>
       <c r="B366" t="str">
-        <v>کوهبنان</v>
+        <v>منوجان</v>
       </c>
       <c r="C366" t="str">
-        <v>کوهبنان</v>
+        <v>منوجان</v>
       </c>
       <c r="D366">
         <v>108</v>
@@ -5525,13 +5525,13 @@
     </row>
     <row r="367">
       <c r="A367">
-        <v>10800015</v>
+        <v>10800014</v>
       </c>
       <c r="B367" t="str">
-        <v>رودبارجنوب</v>
+        <v>کوهبنان</v>
       </c>
       <c r="C367" t="str">
-        <v>رودبارجنوب</v>
+        <v>کوهبنان</v>
       </c>
       <c r="D367">
         <v>108</v>
@@ -5539,13 +5539,13 @@
     </row>
     <row r="368">
       <c r="A368">
-        <v>10800016</v>
+        <v>10800015</v>
       </c>
       <c r="B368" t="str">
-        <v>قلعه گنج</v>
+        <v>رودبارجنوب</v>
       </c>
       <c r="C368" t="str">
-        <v>قلعه-گنج</v>
+        <v>رودبارجنوب</v>
       </c>
       <c r="D368">
         <v>108</v>
@@ -5553,13 +5553,13 @@
     </row>
     <row r="369">
       <c r="A369">
-        <v>10800017</v>
+        <v>10800016</v>
       </c>
       <c r="B369" t="str">
-        <v>ریگان</v>
+        <v>قلعه گنج</v>
       </c>
       <c r="C369" t="str">
-        <v>ریگان</v>
+        <v>قلعه-گنج</v>
       </c>
       <c r="D369">
         <v>108</v>
@@ -5567,13 +5567,13 @@
     </row>
     <row r="370">
       <c r="A370">
-        <v>10800018</v>
+        <v>10800017</v>
       </c>
       <c r="B370" t="str">
-        <v>رابر</v>
+        <v>ریگان</v>
       </c>
       <c r="C370" t="str">
-        <v>رابر</v>
+        <v>ریگان</v>
       </c>
       <c r="D370">
         <v>108</v>
@@ -5581,13 +5581,13 @@
     </row>
     <row r="371">
       <c r="A371">
-        <v>10800019</v>
+        <v>10800018</v>
       </c>
       <c r="B371" t="str">
-        <v>فهرج</v>
+        <v>رابر</v>
       </c>
       <c r="C371" t="str">
-        <v>فهرج</v>
+        <v>رابر</v>
       </c>
       <c r="D371">
         <v>108</v>
@@ -5595,13 +5595,13 @@
     </row>
     <row r="372">
       <c r="A372">
-        <v>10800020</v>
+        <v>10800019</v>
       </c>
       <c r="B372" t="str">
-        <v>انار</v>
+        <v>فهرج</v>
       </c>
       <c r="C372" t="str">
-        <v>انار</v>
+        <v>فهرج</v>
       </c>
       <c r="D372">
         <v>108</v>
@@ -5609,13 +5609,13 @@
     </row>
     <row r="373">
       <c r="A373">
-        <v>10800021</v>
+        <v>10800020</v>
       </c>
       <c r="B373" t="str">
-        <v>نرماشیر</v>
+        <v>انار</v>
       </c>
       <c r="C373" t="str">
-        <v>نرماشیر</v>
+        <v>انار</v>
       </c>
       <c r="D373">
         <v>108</v>
@@ -5623,13 +5623,13 @@
     </row>
     <row r="374">
       <c r="A374">
-        <v>10800022</v>
+        <v>10800021</v>
       </c>
       <c r="B374" t="str">
-        <v>فاریاب</v>
+        <v>نرماشیر</v>
       </c>
       <c r="C374" t="str">
-        <v>فاریاب</v>
+        <v>نرماشیر</v>
       </c>
       <c r="D374">
         <v>108</v>
@@ -5637,13 +5637,13 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>10800023</v>
+        <v>10800022</v>
       </c>
       <c r="B375" t="str">
-        <v>ارزوییه</v>
+        <v>فاریاب</v>
       </c>
       <c r="C375" t="str">
-        <v>ارزوییه</v>
+        <v>فاریاب</v>
       </c>
       <c r="D375">
         <v>108</v>
@@ -5651,13 +5651,13 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>10800024</v>
+        <v>10800023</v>
       </c>
       <c r="B376" t="str">
-        <v>گنبکی</v>
+        <v>ارزوییه</v>
       </c>
       <c r="C376" t="str">
-        <v>گنبکی</v>
+        <v>ارزوییه</v>
       </c>
       <c r="D376">
         <v>108</v>
@@ -5665,13 +5665,13 @@
     </row>
     <row r="377">
       <c r="A377">
-        <v>10800025</v>
+        <v>10800024</v>
       </c>
       <c r="B377" t="str">
-        <v>جازموریان</v>
+        <v>گنبکی</v>
       </c>
       <c r="C377" t="str">
-        <v>جازموریان</v>
+        <v>گنبکی</v>
       </c>
       <c r="D377">
         <v>108</v>
@@ -5679,27 +5679,27 @@
     </row>
     <row r="378">
       <c r="A378">
-        <v>10900013</v>
+        <v>10800025</v>
       </c>
       <c r="B378" t="str">
-        <v>قوچان</v>
+        <v>جازموریان</v>
       </c>
       <c r="C378" t="str">
-        <v>قوچان</v>
+        <v>جازموریان</v>
       </c>
       <c r="D378">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="379">
       <c r="A379">
-        <v>10900014</v>
+        <v>10900013</v>
       </c>
       <c r="B379" t="str">
-        <v>کاشمر</v>
+        <v>قوچان</v>
       </c>
       <c r="C379" t="str">
-        <v>کاشمر</v>
+        <v>قوچان</v>
       </c>
       <c r="D379">
         <v>109</v>
@@ -5707,13 +5707,13 @@
     </row>
     <row r="380">
       <c r="A380">
-        <v>10900015</v>
+        <v>10900014</v>
       </c>
       <c r="B380" t="str">
-        <v>گناباد</v>
+        <v>کاشمر</v>
       </c>
       <c r="C380" t="str">
-        <v>گناباد</v>
+        <v>کاشمر</v>
       </c>
       <c r="D380">
         <v>109</v>
@@ -5721,13 +5721,13 @@
     </row>
     <row r="381">
       <c r="A381">
-        <v>10900016</v>
+        <v>10900015</v>
       </c>
       <c r="B381" t="str">
-        <v>مشهد</v>
+        <v>گناباد</v>
       </c>
       <c r="C381" t="str">
-        <v>مشهد</v>
+        <v>گناباد</v>
       </c>
       <c r="D381">
         <v>109</v>
@@ -5735,13 +5735,13 @@
     </row>
     <row r="382">
       <c r="A382">
-        <v>10900017</v>
+        <v>10900016</v>
       </c>
       <c r="B382" t="str">
-        <v>نیشابور</v>
+        <v>مشهد</v>
       </c>
       <c r="C382" t="str">
-        <v>نیشابور</v>
+        <v>مشهد</v>
       </c>
       <c r="D382">
         <v>109</v>
@@ -5749,13 +5749,13 @@
     </row>
     <row r="383">
       <c r="A383">
-        <v>10900018</v>
+        <v>10900017</v>
       </c>
       <c r="B383" t="str">
-        <v>چناران</v>
+        <v>نیشابور</v>
       </c>
       <c r="C383" t="str">
-        <v>چناران</v>
+        <v>نیشابور</v>
       </c>
       <c r="D383">
         <v>109</v>
@@ -5763,13 +5763,13 @@
     </row>
     <row r="384">
       <c r="A384">
-        <v>10900019</v>
+        <v>10900018</v>
       </c>
       <c r="B384" t="str">
-        <v>خواف</v>
+        <v>چناران</v>
       </c>
       <c r="C384" t="str">
-        <v>خواف</v>
+        <v>چناران</v>
       </c>
       <c r="D384">
         <v>109</v>
@@ -5777,13 +5777,13 @@
     </row>
     <row r="385">
       <c r="A385">
-        <v>10900020</v>
+        <v>10900019</v>
       </c>
       <c r="B385" t="str">
-        <v>سرخس</v>
+        <v>خواف</v>
       </c>
       <c r="C385" t="str">
-        <v>سرخس</v>
+        <v>خواف</v>
       </c>
       <c r="D385">
         <v>109</v>
@@ -5791,13 +5791,13 @@
     </row>
     <row r="386">
       <c r="A386">
-        <v>10900022</v>
+        <v>10900020</v>
       </c>
       <c r="B386" t="str">
-        <v>فریمان</v>
+        <v>سرخس</v>
       </c>
       <c r="C386" t="str">
-        <v>فریمان</v>
+        <v>سرخس</v>
       </c>
       <c r="D386">
         <v>109</v>
@@ -5805,13 +5805,13 @@
     </row>
     <row r="387">
       <c r="A387">
-        <v>10900023</v>
+        <v>10900022</v>
       </c>
       <c r="B387" t="str">
-        <v>بردسکن</v>
+        <v>فریمان</v>
       </c>
       <c r="C387" t="str">
-        <v>بردسکن</v>
+        <v>فریمان</v>
       </c>
       <c r="D387">
         <v>109</v>
@@ -5819,13 +5819,13 @@
     </row>
     <row r="388">
       <c r="A388">
-        <v>10900027</v>
+        <v>10900023</v>
       </c>
       <c r="B388" t="str">
-        <v>رشتخوار</v>
+        <v>بردسکن</v>
       </c>
       <c r="C388" t="str">
-        <v>رشتخوار</v>
+        <v>بردسکن</v>
       </c>
       <c r="D388">
         <v>109</v>
@@ -5833,13 +5833,13 @@
     </row>
     <row r="389">
       <c r="A389">
-        <v>10900028</v>
+        <v>10900027</v>
       </c>
       <c r="B389" t="str">
-        <v>کلات</v>
+        <v>رشتخوار</v>
       </c>
       <c r="C389" t="str">
-        <v>کلات</v>
+        <v>رشتخوار</v>
       </c>
       <c r="D389">
         <v>109</v>
@@ -5847,13 +5847,13 @@
     </row>
     <row r="390">
       <c r="A390">
-        <v>10900029</v>
+        <v>10900028</v>
       </c>
       <c r="B390" t="str">
-        <v>خلیل آباد</v>
+        <v>کلات</v>
       </c>
       <c r="C390" t="str">
-        <v>خلیل-آباد</v>
+        <v>کلات</v>
       </c>
       <c r="D390">
         <v>109</v>
@@ -5861,13 +5861,13 @@
     </row>
     <row r="391">
       <c r="A391">
-        <v>10900030</v>
+        <v>10900029</v>
       </c>
       <c r="B391" t="str">
-        <v>مه ولات</v>
+        <v>خلیل آباد</v>
       </c>
       <c r="C391" t="str">
-        <v>مه-ولات</v>
+        <v>خلیل-آباد</v>
       </c>
       <c r="D391">
         <v>109</v>
@@ -5875,13 +5875,13 @@
     </row>
     <row r="392">
       <c r="A392">
-        <v>10900031</v>
+        <v>10900030</v>
       </c>
       <c r="B392" t="str">
-        <v>بجستان</v>
+        <v>مه ولات</v>
       </c>
       <c r="C392" t="str">
-        <v>بجستان</v>
+        <v>مه-ولات</v>
       </c>
       <c r="D392">
         <v>109</v>
@@ -5889,13 +5889,13 @@
     </row>
     <row r="393">
       <c r="A393">
-        <v>10900032</v>
+        <v>10900031</v>
       </c>
       <c r="B393" t="str">
-        <v>طرقبه شاندیز</v>
+        <v>بجستان</v>
       </c>
       <c r="C393" t="str">
-        <v>طرقبه-شاندیز</v>
+        <v>بجستان</v>
       </c>
       <c r="D393">
         <v>109</v>
@@ -5903,13 +5903,13 @@
     </row>
     <row r="394">
       <c r="A394">
-        <v>10900033</v>
+        <v>10900032</v>
       </c>
       <c r="B394" t="str">
-        <v>فیروزه</v>
+        <v>طرقبه شاندیز</v>
       </c>
       <c r="C394" t="str">
-        <v>فیروزه</v>
+        <v>طرقبه-شاندیز</v>
       </c>
       <c r="D394">
         <v>109</v>
@@ -5917,13 +5917,13 @@
     </row>
     <row r="395">
       <c r="A395">
-        <v>10900034</v>
+        <v>10900033</v>
       </c>
       <c r="B395" t="str">
-        <v>جغتای</v>
+        <v>فیروزه</v>
       </c>
       <c r="C395" t="str">
-        <v>جغتای</v>
+        <v>فیروزه</v>
       </c>
       <c r="D395">
         <v>109</v>
@@ -5931,13 +5931,13 @@
     </row>
     <row r="396">
       <c r="A396">
-        <v>10900035</v>
+        <v>10900034</v>
       </c>
       <c r="B396" t="str">
-        <v>زاوه</v>
+        <v>جغتای</v>
       </c>
       <c r="C396" t="str">
-        <v>زاوه</v>
+        <v>جغتای</v>
       </c>
       <c r="D396">
         <v>109</v>
@@ -5945,13 +5945,13 @@
     </row>
     <row r="397">
       <c r="A397">
-        <v>10900036</v>
+        <v>10900035</v>
       </c>
       <c r="B397" t="str">
-        <v>جوین</v>
+        <v>زاوه</v>
       </c>
       <c r="C397" t="str">
-        <v>جوین</v>
+        <v>زاوه</v>
       </c>
       <c r="D397">
         <v>109</v>
@@ -5959,13 +5959,13 @@
     </row>
     <row r="398">
       <c r="A398">
-        <v>10900037</v>
+        <v>10900036</v>
       </c>
       <c r="B398" t="str">
-        <v>باخرز</v>
+        <v>جوین</v>
       </c>
       <c r="C398" t="str">
-        <v>باخرز</v>
+        <v>جوین</v>
       </c>
       <c r="D398">
         <v>109</v>
@@ -5973,13 +5973,13 @@
     </row>
     <row r="399">
       <c r="A399">
-        <v>10900038</v>
+        <v>10900037</v>
       </c>
       <c r="B399" t="str">
-        <v>خوشاب</v>
+        <v>باخرز</v>
       </c>
       <c r="C399" t="str">
-        <v>خوشاب</v>
+        <v>باخرز</v>
       </c>
       <c r="D399">
         <v>109</v>
@@ -5987,13 +5987,13 @@
     </row>
     <row r="400">
       <c r="A400">
-        <v>10900039</v>
+        <v>10900038</v>
       </c>
       <c r="B400" t="str">
-        <v>داورزن</v>
+        <v>خوشاب</v>
       </c>
       <c r="C400" t="str">
-        <v>داورزن</v>
+        <v>خوشاب</v>
       </c>
       <c r="D400">
         <v>109</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="401">
       <c r="A401">
-        <v>10900040</v>
+        <v>10900039</v>
       </c>
       <c r="B401" t="str">
-        <v>صالح آباد</v>
+        <v>داورزن</v>
       </c>
       <c r="C401" t="str">
-        <v>صالح-آباد</v>
+        <v>داورزن</v>
       </c>
       <c r="D401">
         <v>109</v>
@@ -6015,13 +6015,13 @@
     </row>
     <row r="402">
       <c r="A402">
-        <v>10900041</v>
+        <v>10900040</v>
       </c>
       <c r="B402" t="str">
-        <v>کوهسرخ</v>
+        <v>صالح آباد</v>
       </c>
       <c r="C402" t="str">
-        <v>کوهسرخ</v>
+        <v>صالح-آباد</v>
       </c>
       <c r="D402">
         <v>109</v>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="403">
       <c r="A403">
-        <v>10900042</v>
+        <v>10900041</v>
       </c>
       <c r="B403" t="str">
-        <v>زبرخان</v>
+        <v>کوهسرخ</v>
       </c>
       <c r="C403" t="str">
-        <v>زبرخان</v>
+        <v>کوهسرخ</v>
       </c>
       <c r="D403">
         <v>109</v>
@@ -6043,13 +6043,13 @@
     </row>
     <row r="404">
       <c r="A404">
-        <v>10900043</v>
+        <v>10900042</v>
       </c>
       <c r="B404" t="str">
-        <v>ششتمد</v>
+        <v>زبرخان</v>
       </c>
       <c r="C404" t="str">
-        <v>ششتمد</v>
+        <v>زبرخان</v>
       </c>
       <c r="D404">
         <v>109</v>
@@ -6057,13 +6057,13 @@
     </row>
     <row r="405">
       <c r="A405">
-        <v>10900044</v>
+        <v>10900043</v>
       </c>
       <c r="B405" t="str">
-        <v>گلبهار</v>
+        <v>ششتمد</v>
       </c>
       <c r="C405" t="str">
-        <v>گلبهار</v>
+        <v>ششتمد</v>
       </c>
       <c r="D405">
         <v>109</v>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="406">
       <c r="A406">
-        <v>10900045</v>
+        <v>10900044</v>
       </c>
       <c r="B406" t="str">
-        <v>میان جلگه</v>
+        <v>گلبهار</v>
       </c>
       <c r="C406" t="str">
-        <v>میان-جلگه</v>
+        <v>گلبهار</v>
       </c>
       <c r="D406">
         <v>109</v>
@@ -6085,27 +6085,27 @@
     </row>
     <row r="407">
       <c r="A407">
-        <v>11000010</v>
+        <v>10900045</v>
       </c>
       <c r="B407" t="str">
-        <v>کاشان</v>
+        <v>میان جلگه</v>
       </c>
       <c r="C407" t="str">
-        <v>کاشان</v>
+        <v>میان-جلگه</v>
       </c>
       <c r="D407">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="408">
       <c r="A408">
-        <v>11000011</v>
+        <v>11000010</v>
       </c>
       <c r="B408" t="str">
-        <v>گلپایگان</v>
+        <v>کاشان</v>
       </c>
       <c r="C408" t="str">
-        <v>گلپایگان</v>
+        <v>کاشان</v>
       </c>
       <c r="D408">
         <v>110</v>
@@ -6113,13 +6113,13 @@
     </row>
     <row r="409">
       <c r="A409">
-        <v>11000012</v>
+        <v>11000011</v>
       </c>
       <c r="B409" t="str">
-        <v>لنجان</v>
+        <v>گلپایگان</v>
       </c>
       <c r="C409" t="str">
-        <v>لنجان</v>
+        <v>گلپایگان</v>
       </c>
       <c r="D409">
         <v>110</v>
@@ -6127,13 +6127,13 @@
     </row>
     <row r="410">
       <c r="A410">
-        <v>11000013</v>
+        <v>11000012</v>
       </c>
       <c r="B410" t="str">
-        <v>نایین</v>
+        <v>لنجان</v>
       </c>
       <c r="C410" t="str">
-        <v>نایین</v>
+        <v>لنجان</v>
       </c>
       <c r="D410">
         <v>110</v>
@@ -6141,13 +6141,13 @@
     </row>
     <row r="411">
       <c r="A411">
-        <v>11000014</v>
+        <v>11000013</v>
       </c>
       <c r="B411" t="str">
-        <v>نجف آباد</v>
+        <v>نایین</v>
       </c>
       <c r="C411" t="str">
-        <v>نجف-آباد</v>
+        <v>نایین</v>
       </c>
       <c r="D411">
         <v>110</v>
@@ -6155,13 +6155,13 @@
     </row>
     <row r="412">
       <c r="A412">
-        <v>11000015</v>
+        <v>11000014</v>
       </c>
       <c r="B412" t="str">
-        <v>نطنز</v>
+        <v>نجف آباد</v>
       </c>
       <c r="C412" t="str">
-        <v>نطنز</v>
+        <v>نجف-آباد</v>
       </c>
       <c r="D412">
         <v>110</v>
@@ -6169,13 +6169,13 @@
     </row>
     <row r="413">
       <c r="A413">
-        <v>11000016</v>
+        <v>11000015</v>
       </c>
       <c r="B413" t="str">
-        <v>شاهین شهرو میمه</v>
+        <v>نطنز</v>
       </c>
       <c r="C413" t="str">
-        <v>شاهین-شهرو-میمه</v>
+        <v>نطنز</v>
       </c>
       <c r="D413">
         <v>110</v>
@@ -6183,13 +6183,13 @@
     </row>
     <row r="414">
       <c r="A414">
-        <v>11000017</v>
+        <v>11000016</v>
       </c>
       <c r="B414" t="str">
-        <v>مبارکه</v>
+        <v>شاهین شهرو میمه</v>
       </c>
       <c r="C414" t="str">
-        <v>مبارکه</v>
+        <v>شاهین-شهرو-میمه</v>
       </c>
       <c r="D414">
         <v>110</v>
@@ -6197,13 +6197,13 @@
     </row>
     <row r="415">
       <c r="A415">
-        <v>11000018</v>
+        <v>11000017</v>
       </c>
       <c r="B415" t="str">
-        <v>آران و بیدگل</v>
+        <v>مبارکه</v>
       </c>
       <c r="C415" t="str">
-        <v>آران-و-بیدگل</v>
+        <v>مبارکه</v>
       </c>
       <c r="D415">
         <v>110</v>
@@ -6211,13 +6211,13 @@
     </row>
     <row r="416">
       <c r="A416">
-        <v>11000019</v>
+        <v>11000018</v>
       </c>
       <c r="B416" t="str">
-        <v>تیران وکرون</v>
+        <v>آران و بیدگل</v>
       </c>
       <c r="C416" t="str">
-        <v>تیران-وکرون</v>
+        <v>آران-و-بیدگل</v>
       </c>
       <c r="D416">
         <v>110</v>
@@ -6225,13 +6225,13 @@
     </row>
     <row r="417">
       <c r="A417">
-        <v>11000020</v>
+        <v>11000019</v>
       </c>
       <c r="B417" t="str">
-        <v>چادگان</v>
+        <v>تیران وکرون</v>
       </c>
       <c r="C417" t="str">
-        <v>چادگان</v>
+        <v>تیران-وکرون</v>
       </c>
       <c r="D417">
         <v>110</v>
@@ -6239,13 +6239,13 @@
     </row>
     <row r="418">
       <c r="A418">
-        <v>11000021</v>
+        <v>11000020</v>
       </c>
       <c r="B418" t="str">
-        <v>دهاقان</v>
+        <v>چادگان</v>
       </c>
       <c r="C418" t="str">
-        <v>دهاقان</v>
+        <v>چادگان</v>
       </c>
       <c r="D418">
         <v>110</v>
@@ -6253,13 +6253,13 @@
     </row>
     <row r="419">
       <c r="A419">
-        <v>11000022</v>
+        <v>11000021</v>
       </c>
       <c r="B419" t="str">
-        <v>برخوار</v>
+        <v>دهاقان</v>
       </c>
       <c r="C419" t="str">
-        <v>برخوار</v>
+        <v>دهاقان</v>
       </c>
       <c r="D419">
         <v>110</v>
@@ -6267,13 +6267,13 @@
     </row>
     <row r="420">
       <c r="A420">
-        <v>11000023</v>
+        <v>11000022</v>
       </c>
       <c r="B420" t="str">
-        <v>خور و بیابانک</v>
+        <v>برخوار</v>
       </c>
       <c r="C420" t="str">
-        <v>خور-و-بیابانک</v>
+        <v>برخوار</v>
       </c>
       <c r="D420">
         <v>110</v>
@@ -6281,13 +6281,13 @@
     </row>
     <row r="421">
       <c r="A421">
-        <v>11000024</v>
+        <v>11000023</v>
       </c>
       <c r="B421" t="str">
-        <v>بویین و میاندشت</v>
+        <v>خور و بیابانک</v>
       </c>
       <c r="C421" t="str">
-        <v>بویین-و-میاندشت</v>
+        <v>خور-و-بیابانک</v>
       </c>
       <c r="D421">
         <v>110</v>
@@ -6295,13 +6295,13 @@
     </row>
     <row r="422">
       <c r="A422">
-        <v>11000025</v>
+        <v>11000024</v>
       </c>
       <c r="B422" t="str">
-        <v>کوهپایه</v>
+        <v>بویین و میاندشت</v>
       </c>
       <c r="C422" t="str">
-        <v>کوهپایه</v>
+        <v>بویین-و-میاندشت</v>
       </c>
       <c r="D422">
         <v>110</v>
@@ -6309,13 +6309,13 @@
     </row>
     <row r="423">
       <c r="A423">
-        <v>11000026</v>
+        <v>11000025</v>
       </c>
       <c r="B423" t="str">
-        <v>جرقویه</v>
+        <v>کوهپایه</v>
       </c>
       <c r="C423" t="str">
-        <v>جرقویه</v>
+        <v>کوهپایه</v>
       </c>
       <c r="D423">
         <v>110</v>
@@ -6323,13 +6323,13 @@
     </row>
     <row r="424">
       <c r="A424">
-        <v>11000027</v>
+        <v>11000026</v>
       </c>
       <c r="B424" t="str">
-        <v>ورزنه</v>
+        <v>جرقویه</v>
       </c>
       <c r="C424" t="str">
-        <v>ورزنه</v>
+        <v>جرقویه</v>
       </c>
       <c r="D424">
         <v>110</v>
@@ -6337,13 +6337,13 @@
     </row>
     <row r="425">
       <c r="A425">
-        <v>11000028</v>
+        <v>11000027</v>
       </c>
       <c r="B425" t="str">
-        <v>هرند</v>
+        <v>ورزنه</v>
       </c>
       <c r="C425" t="str">
-        <v>هرند</v>
+        <v>ورزنه</v>
       </c>
       <c r="D425">
         <v>110</v>
@@ -6351,27 +6351,27 @@
     </row>
     <row r="426">
       <c r="A426">
-        <v>11100010</v>
+        <v>11000028</v>
       </c>
       <c r="B426" t="str">
-        <v>زهک</v>
+        <v>هرند</v>
       </c>
       <c r="C426" t="str">
-        <v>زهک</v>
+        <v>هرند</v>
       </c>
       <c r="D426">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="427">
       <c r="A427">
-        <v>11100011</v>
+        <v>11100010</v>
       </c>
       <c r="B427" t="str">
-        <v>هیرمند</v>
+        <v>زهک</v>
       </c>
       <c r="C427" t="str">
-        <v>هیرمند</v>
+        <v>زهک</v>
       </c>
       <c r="D427">
         <v>111</v>
@@ -6379,13 +6379,13 @@
     </row>
     <row r="428">
       <c r="A428">
-        <v>11100012</v>
+        <v>11100011</v>
       </c>
       <c r="B428" t="str">
-        <v>دلگان</v>
+        <v>هیرمند</v>
       </c>
       <c r="C428" t="str">
-        <v>دلگان</v>
+        <v>هیرمند</v>
       </c>
       <c r="D428">
         <v>111</v>
@@ -6393,13 +6393,13 @@
     </row>
     <row r="429">
       <c r="A429">
-        <v>11100013</v>
+        <v>11100012</v>
       </c>
       <c r="B429" t="str">
-        <v>مهرستان</v>
+        <v>دلگان</v>
       </c>
       <c r="C429" t="str">
-        <v>مهرستان</v>
+        <v>دلگان</v>
       </c>
       <c r="D429">
         <v>111</v>
@@ -6407,13 +6407,13 @@
     </row>
     <row r="430">
       <c r="A430">
-        <v>11100014</v>
+        <v>11100013</v>
       </c>
       <c r="B430" t="str">
-        <v>سیب و سوران</v>
+        <v>مهرستان</v>
       </c>
       <c r="C430" t="str">
-        <v>سیب-و-سوران</v>
+        <v>مهرستان</v>
       </c>
       <c r="D430">
         <v>111</v>
@@ -6421,13 +6421,13 @@
     </row>
     <row r="431">
       <c r="A431">
-        <v>11100015</v>
+        <v>11100014</v>
       </c>
       <c r="B431" t="str">
-        <v>نیمروز</v>
+        <v>سیب و سوران</v>
       </c>
       <c r="C431" t="str">
-        <v>نیمروز</v>
+        <v>سیب-و-سوران</v>
       </c>
       <c r="D431">
         <v>111</v>
@@ -6435,13 +6435,13 @@
     </row>
     <row r="432">
       <c r="A432">
-        <v>11100016</v>
+        <v>11100015</v>
       </c>
       <c r="B432" t="str">
-        <v>هامون</v>
+        <v>نیمروز</v>
       </c>
       <c r="C432" t="str">
-        <v>هامون</v>
+        <v>نیمروز</v>
       </c>
       <c r="D432">
         <v>111</v>
@@ -6449,13 +6449,13 @@
     </row>
     <row r="433">
       <c r="A433">
-        <v>11100017</v>
+        <v>11100016</v>
       </c>
       <c r="B433" t="str">
-        <v>میرجاوه</v>
+        <v>هامون</v>
       </c>
       <c r="C433" t="str">
-        <v>میرجاوه</v>
+        <v>هامون</v>
       </c>
       <c r="D433">
         <v>111</v>
@@ -6463,13 +6463,13 @@
     </row>
     <row r="434">
       <c r="A434">
-        <v>11100018</v>
+        <v>11100017</v>
       </c>
       <c r="B434" t="str">
-        <v>قصرقند</v>
+        <v>میرجاوه</v>
       </c>
       <c r="C434" t="str">
-        <v>قصرقند</v>
+        <v>میرجاوه</v>
       </c>
       <c r="D434">
         <v>111</v>
@@ -6477,13 +6477,13 @@
     </row>
     <row r="435">
       <c r="A435">
-        <v>11100019</v>
+        <v>11100018</v>
       </c>
       <c r="B435" t="str">
-        <v>فنوج</v>
+        <v>قصرقند</v>
       </c>
       <c r="C435" t="str">
-        <v>فنوج</v>
+        <v>قصرقند</v>
       </c>
       <c r="D435">
         <v>111</v>
@@ -6491,13 +6491,13 @@
     </row>
     <row r="436">
       <c r="A436">
-        <v>11100020</v>
+        <v>11100019</v>
       </c>
       <c r="B436" t="str">
-        <v>بمپور</v>
+        <v>فنوج</v>
       </c>
       <c r="C436" t="str">
-        <v>بمپور</v>
+        <v>فنوج</v>
       </c>
       <c r="D436">
         <v>111</v>
@@ -6505,13 +6505,13 @@
     </row>
     <row r="437">
       <c r="A437">
-        <v>11100021</v>
+        <v>11100020</v>
       </c>
       <c r="B437" t="str">
-        <v>تفتان</v>
+        <v>بمپور</v>
       </c>
       <c r="C437" t="str">
-        <v>تفتان</v>
+        <v>بمپور</v>
       </c>
       <c r="D437">
         <v>111</v>
@@ -6519,13 +6519,13 @@
     </row>
     <row r="438">
       <c r="A438">
-        <v>11100022</v>
+        <v>11100021</v>
       </c>
       <c r="B438" t="str">
-        <v>دشتیاری</v>
+        <v>تفتان</v>
       </c>
       <c r="C438" t="str">
-        <v>دشتیاری</v>
+        <v>تفتان</v>
       </c>
       <c r="D438">
         <v>111</v>
@@ -6533,13 +6533,13 @@
     </row>
     <row r="439">
       <c r="A439">
-        <v>11100023</v>
+        <v>11100022</v>
       </c>
       <c r="B439" t="str">
-        <v>سرباز</v>
+        <v>دشتیاری</v>
       </c>
       <c r="C439" t="str">
-        <v>سرباز</v>
+        <v>دشتیاری</v>
       </c>
       <c r="D439">
         <v>111</v>
@@ -6547,13 +6547,13 @@
     </row>
     <row r="440">
       <c r="A440">
-        <v>11100024</v>
+        <v>11100023</v>
       </c>
       <c r="B440" t="str">
-        <v>گلشن</v>
+        <v>سرباز</v>
       </c>
       <c r="C440" t="str">
-        <v>گلشن</v>
+        <v>سرباز</v>
       </c>
       <c r="D440">
         <v>111</v>
@@ -6561,13 +6561,13 @@
     </row>
     <row r="441">
       <c r="A441">
-        <v>11100025</v>
+        <v>11100024</v>
       </c>
       <c r="B441" t="str">
-        <v>لاشار</v>
+        <v>گلشن</v>
       </c>
       <c r="C441" t="str">
-        <v>لاشار</v>
+        <v>گلشن</v>
       </c>
       <c r="D441">
         <v>111</v>
@@ -6575,13 +6575,13 @@
     </row>
     <row r="442">
       <c r="A442">
-        <v>11100026</v>
+        <v>11100025</v>
       </c>
       <c r="B442" t="str">
-        <v>زرآباد</v>
+        <v>لاشار</v>
       </c>
       <c r="C442" t="str">
-        <v>زرآباد</v>
+        <v>لاشار</v>
       </c>
       <c r="D442">
         <v>111</v>
@@ -6589,55 +6589,55 @@
     </row>
     <row r="443">
       <c r="A443">
-        <v>11200010</v>
+        <v>11100026</v>
       </c>
       <c r="B443" t="str">
-        <v>دهگلان</v>
+        <v>زرآباد</v>
       </c>
       <c r="C443" t="str">
-        <v>دهگلان</v>
+        <v>زرآباد</v>
       </c>
       <c r="D443">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="444">
       <c r="A444">
-        <v>11300010</v>
+        <v>11200010</v>
       </c>
       <c r="B444" t="str">
-        <v>درگزین</v>
+        <v>دهگلان</v>
       </c>
       <c r="C444" t="str">
-        <v>درگزین</v>
+        <v>دهگلان</v>
       </c>
       <c r="D444">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="445">
       <c r="A445">
-        <v>11400010</v>
+        <v>11300010</v>
       </c>
       <c r="B445" t="str">
-        <v>خانمیرزا</v>
+        <v>درگزین</v>
       </c>
       <c r="C445" t="str">
-        <v>خانمیرزا</v>
+        <v>درگزین</v>
       </c>
       <c r="D445">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="446">
       <c r="A446">
-        <v>11400011</v>
+        <v>11400010</v>
       </c>
       <c r="B446" t="str">
-        <v>فلارد</v>
+        <v>خانمیرزا</v>
       </c>
       <c r="C446" t="str">
-        <v>فلارد</v>
+        <v>خانمیرزا</v>
       </c>
       <c r="D446">
         <v>114</v>
@@ -6645,13 +6645,13 @@
     </row>
     <row r="447">
       <c r="A447">
-        <v>11400012</v>
+        <v>11400011</v>
       </c>
       <c r="B447" t="str">
-        <v>فرخ شهر</v>
+        <v>فلارد</v>
       </c>
       <c r="C447" t="str">
-        <v>فرخ-شهر</v>
+        <v>فلارد</v>
       </c>
       <c r="D447">
         <v>114</v>
@@ -6659,27 +6659,27 @@
     </row>
     <row r="448">
       <c r="A448">
-        <v>11500010</v>
+        <v>11400012</v>
       </c>
       <c r="B448" t="str">
-        <v>چگنی</v>
+        <v>فرخ شهر</v>
       </c>
       <c r="C448" t="str">
-        <v>چگنی</v>
+        <v>فرخ-شهر</v>
       </c>
       <c r="D448">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="449">
       <c r="A449">
-        <v>11500011</v>
+        <v>11500010</v>
       </c>
       <c r="B449" t="str">
-        <v>رومشکان</v>
+        <v>چگنی</v>
       </c>
       <c r="C449" t="str">
-        <v>رومشکان</v>
+        <v>چگنی</v>
       </c>
       <c r="D449">
         <v>115</v>
@@ -6687,13 +6687,13 @@
     </row>
     <row r="450">
       <c r="A450">
-        <v>11500012</v>
+        <v>11500011</v>
       </c>
       <c r="B450" t="str">
-        <v>معمولان</v>
+        <v>رومشکان</v>
       </c>
       <c r="C450" t="str">
-        <v>معمولان</v>
+        <v>رومشکان</v>
       </c>
       <c r="D450">
         <v>115</v>
@@ -6701,27 +6701,27 @@
     </row>
     <row r="451">
       <c r="A451">
-        <v>11600010</v>
+        <v>11500012</v>
       </c>
       <c r="B451" t="str">
-        <v>بدره</v>
+        <v>معمولان</v>
       </c>
       <c r="C451" t="str">
-        <v>بدره</v>
+        <v>معمولان</v>
       </c>
       <c r="D451">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="452">
       <c r="A452">
-        <v>11600011</v>
+        <v>11600010</v>
       </c>
       <c r="B452" t="str">
-        <v>هلیلان</v>
+        <v>بدره</v>
       </c>
       <c r="C452" t="str">
-        <v>هلیلان</v>
+        <v>بدره</v>
       </c>
       <c r="D452">
         <v>116</v>
@@ -6729,13 +6729,13 @@
     </row>
     <row r="453">
       <c r="A453">
-        <v>11600012</v>
+        <v>11600011</v>
       </c>
       <c r="B453" t="str">
-        <v>چوار</v>
+        <v>هلیلان</v>
       </c>
       <c r="C453" t="str">
-        <v>چوار</v>
+        <v>هلیلان</v>
       </c>
       <c r="D453">
         <v>116</v>
@@ -6743,55 +6743,55 @@
     </row>
     <row r="454">
       <c r="A454">
-        <v>11800010</v>
+        <v>11600012</v>
       </c>
       <c r="B454" t="str">
-        <v>عسلویه</v>
+        <v>چوار</v>
       </c>
       <c r="C454" t="str">
-        <v>عسلویه</v>
+        <v>چوار</v>
       </c>
       <c r="D454">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="455">
       <c r="A455">
-        <v>11900010</v>
+        <v>11800010</v>
       </c>
       <c r="B455" t="str">
-        <v>سلطانیه</v>
+        <v>عسلویه</v>
       </c>
       <c r="C455" t="str">
-        <v>سلطانیه</v>
+        <v>عسلویه</v>
       </c>
       <c r="D455">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="456">
       <c r="A456">
-        <v>12100011</v>
+        <v>11900010</v>
       </c>
       <c r="B456" t="str">
-        <v>بهاباد</v>
+        <v>سلطانیه</v>
       </c>
       <c r="C456" t="str">
-        <v>بهاباد</v>
+        <v>سلطانیه</v>
       </c>
       <c r="D456">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="457">
       <c r="A457">
-        <v>12100012</v>
+        <v>12100011</v>
       </c>
       <c r="B457" t="str">
-        <v>مروست</v>
+        <v>بهاباد</v>
       </c>
       <c r="C457" t="str">
-        <v>مروست</v>
+        <v>بهاباد</v>
       </c>
       <c r="D457">
         <v>121</v>
@@ -6799,13 +6799,13 @@
     </row>
     <row r="458">
       <c r="A458">
-        <v>12100013</v>
+        <v>12100012</v>
       </c>
       <c r="B458" t="str">
-        <v>زارچ</v>
+        <v>مروست</v>
       </c>
       <c r="C458" t="str">
-        <v>زارچ</v>
+        <v>مروست</v>
       </c>
       <c r="D458">
         <v>121</v>
@@ -6813,27 +6813,27 @@
     </row>
     <row r="459">
       <c r="A459">
-        <v>12200010</v>
+        <v>12100013</v>
       </c>
       <c r="B459" t="str">
-        <v>خمیر</v>
+        <v>زارچ</v>
       </c>
       <c r="C459" t="str">
-        <v>خمیر</v>
+        <v>زارچ</v>
       </c>
       <c r="D459">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="460">
       <c r="A460">
-        <v>12200011</v>
+        <v>12200010</v>
       </c>
       <c r="B460" t="str">
-        <v>پارسیان</v>
+        <v>خمیر</v>
       </c>
       <c r="C460" t="str">
-        <v>پارسیان</v>
+        <v>خمیر</v>
       </c>
       <c r="D460">
         <v>122</v>
@@ -6841,13 +6841,13 @@
     </row>
     <row r="461">
       <c r="A461">
-        <v>12200012</v>
+        <v>12200011</v>
       </c>
       <c r="B461" t="str">
-        <v>سیریک</v>
+        <v>پارسیان</v>
       </c>
       <c r="C461" t="str">
-        <v>سیریک</v>
+        <v>پارسیان</v>
       </c>
       <c r="D461">
         <v>122</v>
@@ -6855,13 +6855,13 @@
     </row>
     <row r="462">
       <c r="A462">
-        <v>12200013</v>
+        <v>12200012</v>
       </c>
       <c r="B462" t="str">
-        <v>بشاگرد</v>
+        <v>سیریک</v>
       </c>
       <c r="C462" t="str">
-        <v>بشاگرد</v>
+        <v>سیریک</v>
       </c>
       <c r="D462">
         <v>122</v>
@@ -6869,27 +6869,27 @@
     </row>
     <row r="463">
       <c r="A463">
-        <v>12300010</v>
+        <v>12200013</v>
       </c>
       <c r="B463" t="str">
-        <v>اسلامشهر</v>
+        <v>بشاگرد</v>
       </c>
       <c r="C463" t="str">
-        <v>اسلامشهر</v>
+        <v>بشاگرد</v>
       </c>
       <c r="D463">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="464">
       <c r="A464">
-        <v>12300012</v>
+        <v>12300010</v>
       </c>
       <c r="B464" t="str">
-        <v>رباط کریم</v>
+        <v>اسلامشهر</v>
       </c>
       <c r="C464" t="str">
-        <v>رباط-کریم</v>
+        <v>اسلامشهر</v>
       </c>
       <c r="D464">
         <v>123</v>
@@ -6897,13 +6897,13 @@
     </row>
     <row r="465">
       <c r="A465">
-        <v>12300013</v>
+        <v>12300012</v>
       </c>
       <c r="B465" t="str">
-        <v>پاکدشت</v>
+        <v>رباط‌کریم</v>
       </c>
       <c r="C465" t="str">
-        <v>پاکدشت</v>
+        <v>رباط-کریم</v>
       </c>
       <c r="D465">
         <v>123</v>
@@ -6911,13 +6911,13 @@
     </row>
     <row r="466">
       <c r="A466">
-        <v>12300014</v>
+        <v>12300013</v>
       </c>
       <c r="B466" t="str">
-        <v>فیروزکوه</v>
+        <v>پاکدشت</v>
       </c>
       <c r="C466" t="str">
-        <v>فیروزکوه</v>
+        <v>پاکدشت</v>
       </c>
       <c r="D466">
         <v>123</v>
@@ -6925,13 +6925,13 @@
     </row>
     <row r="467">
       <c r="A467">
-        <v>12300016</v>
+        <v>12300014</v>
       </c>
       <c r="B467" t="str">
-        <v>قدس</v>
+        <v>فیروزکوه</v>
       </c>
       <c r="C467" t="str">
-        <v>قدس</v>
+        <v>فیروزکوه</v>
       </c>
       <c r="D467">
         <v>123</v>
@@ -6939,13 +6939,13 @@
     </row>
     <row r="468">
       <c r="A468">
-        <v>12300017</v>
+        <v>12300016</v>
       </c>
       <c r="B468" t="str">
-        <v>ملارد</v>
+        <v>قدس</v>
       </c>
       <c r="C468" t="str">
-        <v>ملارد</v>
+        <v>قدس</v>
       </c>
       <c r="D468">
         <v>123</v>
@@ -6953,13 +6953,13 @@
     </row>
     <row r="469">
       <c r="A469">
-        <v>12300018</v>
+        <v>12300017</v>
       </c>
       <c r="B469" t="str">
-        <v>پیشوا</v>
+        <v>ملارد</v>
       </c>
       <c r="C469" t="str">
-        <v>پیشوا</v>
+        <v>ملارد</v>
       </c>
       <c r="D469">
         <v>123</v>
@@ -6967,13 +6967,13 @@
     </row>
     <row r="470">
       <c r="A470">
-        <v>12300019</v>
+        <v>12300018</v>
       </c>
       <c r="B470" t="str">
-        <v>بهارستان</v>
+        <v>پیشوا</v>
       </c>
       <c r="C470" t="str">
-        <v>بهارستان</v>
+        <v>پیشوا</v>
       </c>
       <c r="D470">
         <v>123</v>
@@ -6981,13 +6981,13 @@
     </row>
     <row r="471">
       <c r="A471">
-        <v>12300020</v>
+        <v>12300019</v>
       </c>
       <c r="B471" t="str">
-        <v>پردیس</v>
+        <v>بهارستان</v>
       </c>
       <c r="C471" t="str">
-        <v>پردیس</v>
+        <v>بهارستان</v>
       </c>
       <c r="D471">
         <v>123</v>
@@ -6995,13 +6995,13 @@
     </row>
     <row r="472">
       <c r="A472">
-        <v>12300021</v>
+        <v>12300020</v>
       </c>
       <c r="B472" t="str">
-        <v>قرچک</v>
+        <v>پردیس</v>
       </c>
       <c r="C472" t="str">
-        <v>قرچک</v>
+        <v>پردیس</v>
       </c>
       <c r="D472">
         <v>123</v>
@@ -7009,27 +7009,27 @@
     </row>
     <row r="473">
       <c r="A473">
-        <v>12400010</v>
+        <v>12300021</v>
       </c>
       <c r="B473" t="str">
-        <v>سرعین</v>
+        <v>قرچک</v>
       </c>
       <c r="C473" t="str">
-        <v>سرعین</v>
+        <v>قرچک</v>
       </c>
       <c r="D473">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="474">
       <c r="A474">
-        <v>12400011</v>
+        <v>12400010</v>
       </c>
       <c r="B474" t="str">
-        <v>اصلاندوز</v>
+        <v>سرعین</v>
       </c>
       <c r="C474" t="str">
-        <v>اصلاندوز</v>
+        <v>سرعین</v>
       </c>
       <c r="D474">
         <v>124</v>
@@ -7037,13 +7037,13 @@
     </row>
     <row r="475">
       <c r="A475">
-        <v>12400012</v>
+        <v>12400011</v>
       </c>
       <c r="B475" t="str">
-        <v>انگوت</v>
+        <v>اصلاندوز</v>
       </c>
       <c r="C475" t="str">
-        <v>انگوت</v>
+        <v>اصلاندوز</v>
       </c>
       <c r="D475">
         <v>124</v>
@@ -7051,27 +7051,27 @@
     </row>
     <row r="476">
       <c r="A476">
-        <v>12700010</v>
+        <v>12400012</v>
       </c>
       <c r="B476" t="str">
-        <v>آزادشهر</v>
+        <v>انگوت</v>
       </c>
       <c r="C476" t="str">
-        <v>آزادشهر</v>
+        <v>انگوت</v>
       </c>
       <c r="D476">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="477">
       <c r="A477">
-        <v>12700011</v>
+        <v>12700010</v>
       </c>
       <c r="B477" t="str">
-        <v>رامیان</v>
+        <v>آزادشهر</v>
       </c>
       <c r="C477" t="str">
-        <v>رامیان</v>
+        <v>آزادشهر</v>
       </c>
       <c r="D477">
         <v>127</v>
@@ -7079,13 +7079,13 @@
     </row>
     <row r="478">
       <c r="A478">
-        <v>12700012</v>
+        <v>12700011</v>
       </c>
       <c r="B478" t="str">
-        <v>مراوه تپه</v>
+        <v>رامیان</v>
       </c>
       <c r="C478" t="str">
-        <v>مراوه-تپه</v>
+        <v>رامیان</v>
       </c>
       <c r="D478">
         <v>127</v>
@@ -7093,13 +7093,13 @@
     </row>
     <row r="479">
       <c r="A479">
-        <v>12700013</v>
+        <v>12700012</v>
       </c>
       <c r="B479" t="str">
-        <v>گمیشان</v>
+        <v>مراوه تپه</v>
       </c>
       <c r="C479" t="str">
-        <v>گمیشان</v>
+        <v>مراوه-تپه</v>
       </c>
       <c r="D479">
         <v>127</v>
@@ -7107,13 +7107,13 @@
     </row>
     <row r="480">
       <c r="A480">
-        <v>12700014</v>
+        <v>12700013</v>
       </c>
       <c r="B480" t="str">
-        <v>گالیکش</v>
+        <v>گمیشان</v>
       </c>
       <c r="C480" t="str">
-        <v>گالیکش</v>
+        <v>گمیشان</v>
       </c>
       <c r="D480">
         <v>127</v>
@@ -7121,49 +7121,77 @@
     </row>
     <row r="481">
       <c r="A481">
-        <v>12800010</v>
+        <v>12700014</v>
       </c>
       <c r="B481" t="str">
-        <v>مانه</v>
+        <v>گالیکش</v>
       </c>
       <c r="C481" t="str">
-        <v>مانه</v>
+        <v>گالیکش</v>
       </c>
       <c r="D481">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="482">
       <c r="A482">
-        <v>12900010</v>
+        <v>12800010</v>
       </c>
       <c r="B482" t="str">
-        <v>خوسف</v>
+        <v>مانه</v>
       </c>
       <c r="C482" t="str">
-        <v>خوسف</v>
+        <v>مانه</v>
       </c>
       <c r="D482">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="483">
       <c r="A483">
-        <v>12900011</v>
+        <v>12900010</v>
       </c>
       <c r="B483" t="str">
-        <v>طبس</v>
+        <v>خوسف</v>
       </c>
       <c r="C483" t="str">
-        <v>طبس</v>
+        <v>خوسف</v>
       </c>
       <c r="D483">
         <v>129</v>
       </c>
     </row>
+    <row r="484">
+      <c r="A484">
+        <v>12900011</v>
+      </c>
+      <c r="B484" t="str">
+        <v>طبس</v>
+      </c>
+      <c r="C484" t="str">
+        <v>طبس</v>
+      </c>
+      <c r="D484">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485">
+        <v>12900012</v>
+      </c>
+      <c r="B485" t="str">
+        <v>عشق آباد</v>
+      </c>
+      <c r="C485" t="str">
+        <v>عشق-آباد</v>
+      </c>
+      <c r="D485">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D483"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D485"/>
   </ignoredErrors>
 </worksheet>
 </file>